--- a/database/event/6070/event_6070_evp_summary.xlsx
+++ b/database/event/6070/event_6070_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.3743</v>
+        <v>6.4635</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6424</v>
+        <v>1.6653</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1537</v>
+        <v>2.1311</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3743</v>
+        <v>6.4635</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3743</v>
+        <v>6.4635</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.6918</v>
+        <v>8.674099999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>8.057399999999999</v>
+        <v>9.432399999999999</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>8.057399999999999</v>
+        <v>9.432399999999999</v>
       </c>
       <c r="N2" t="n">
         <v>249</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.8246</v>
+        <v>6.0138</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2431</v>
+        <v>1.5495</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5277</v>
+        <v>1.952</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8246</v>
+        <v>6.0138</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8246</v>
+        <v>6.0138</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2619</v>
+        <v>7.1266</v>
       </c>
       <c r="I3" t="n">
-        <v>5.512</v>
+        <v>7.7496</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.512</v>
+        <v>7.7496</v>
       </c>
       <c r="N3" t="n">
         <v>249</v>
@@ -584,124 +584,124 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.585</v>
+        <v>5.6835</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1813</v>
+        <v>1.4644</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4309</v>
+        <v>1.8204</v>
       </c>
       <c r="E4" t="n">
-        <v>4.585</v>
+        <v>5.6835</v>
       </c>
       <c r="F4" t="n">
-        <v>4.585</v>
+        <v>5.6835</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8862</v>
+        <v>6.6086</v>
       </c>
       <c r="I4" t="n">
-        <v>5.0476</v>
+        <v>6.9494</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0476</v>
+        <v>6.9494</v>
       </c>
       <c r="N4" t="n">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1426</v>
+        <v>5.3591</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0674</v>
+        <v>1.3808</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2522</v>
+        <v>1.6912</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1426</v>
+        <v>5.3591</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1426</v>
+        <v>5.3591</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1925</v>
+        <v>6.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3109</v>
+        <v>6.4686</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>277</v>
+        <v>206</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3109</v>
+        <v>6.4686</v>
       </c>
       <c r="N5" t="n">
-        <v>277</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1415</v>
+        <v>5.0966</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0671</v>
+        <v>1.3132</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2517</v>
+        <v>1.5866</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1415</v>
+        <v>5.0966</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1415</v>
+        <v>5.0966</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1908</v>
+        <v>5.6883</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3293</v>
+        <v>6.0321</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3293</v>
+        <v>6.0321</v>
       </c>
       <c r="N6" t="n">
         <v>206</v>
@@ -722,369 +722,369 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1085</v>
+        <v>4.9511</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0586</v>
+        <v>1.2757</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2384</v>
+        <v>1.5286</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1085</v>
+        <v>4.9511</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1085</v>
+        <v>4.9511</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1391</v>
+        <v>5.4603</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2758</v>
+        <v>5.7902</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2758</v>
+        <v>5.7902</v>
       </c>
       <c r="N7" t="n">
-        <v>206</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6946</v>
+        <v>4.9248</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9519</v>
+        <v>1.2689</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0712</v>
+        <v>1.5181</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6946</v>
+        <v>4.9248</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6946</v>
+        <v>4.9248</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6946</v>
+        <v>5.419</v>
       </c>
       <c r="I8" t="n">
-        <v>3.799</v>
+        <v>5.7465</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>277</v>
+        <v>206</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.799</v>
+        <v>5.7465</v>
       </c>
       <c r="N8" t="n">
-        <v>277</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2948</v>
+        <v>4.6196</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8489</v>
+        <v>1.1903</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9097</v>
+        <v>1.3965</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2948</v>
+        <v>4.6196</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2948</v>
+        <v>4.6196</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2948</v>
+        <v>4.9405</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4037</v>
+        <v>5.1953</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>206</v>
+        <v>277</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4037</v>
+        <v>5.1953</v>
       </c>
       <c r="N9" t="n">
-        <v>206</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lack1</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2641</v>
+        <v>4.2955</v>
       </c>
       <c r="C10" t="n">
-        <v>0.841</v>
+        <v>1.1068</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8973</v>
+        <v>1.2674</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2641</v>
+        <v>4.2955</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2641</v>
+        <v>4.2955</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2641</v>
+        <v>4.4323</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3876</v>
+        <v>4.8198</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3876</v>
+        <v>4.8198</v>
       </c>
       <c r="N10" t="n">
-        <v>280</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2211</v>
+        <v>4.2071</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8299</v>
+        <v>1.084</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8799</v>
+        <v>1.2322</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2211</v>
+        <v>4.2071</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2211</v>
+        <v>4.2071</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2211</v>
+        <v>4.2936</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3275</v>
+        <v>4.669</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3275</v>
+        <v>4.669</v>
       </c>
       <c r="N11" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>lollipop21k</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2119</v>
+        <v>3.8833</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8276</v>
+        <v>1.0005</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8762</v>
+        <v>1.1032</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2119</v>
+        <v>3.8833</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2119</v>
+        <v>3.8833</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2119</v>
+        <v>3.8833</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3645</v>
+        <v>4.0157</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>249</v>
+        <v>166</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3645</v>
+        <v>4.0157</v>
       </c>
       <c r="N12" t="n">
-        <v>249</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0233</v>
+        <v>3.8733</v>
       </c>
       <c r="C13" t="n">
-        <v>0.779</v>
+        <v>0.998</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1.0992</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0233</v>
+        <v>3.8733</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0233</v>
+        <v>3.8733</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0233</v>
+        <v>3.8733</v>
       </c>
       <c r="I13" t="n">
-        <v>3.167</v>
+        <v>4.1073</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.167</v>
+        <v>4.1073</v>
       </c>
       <c r="N13" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lollipop21k</t>
+          <t>Lack1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4802</v>
+        <v>3.7545</v>
       </c>
       <c r="C14" t="n">
-        <v>0.639</v>
+        <v>0.9674</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5806</v>
+        <v>1.0519</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4802</v>
+        <v>3.7545</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4802</v>
+        <v>3.7545</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4802</v>
+        <v>3.7545</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5267</v>
+        <v>4.0149</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>166</v>
+        <v>280</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5267</v>
+        <v>4.0149</v>
       </c>
       <c r="N14" t="n">
-        <v>166</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4337</v>
+        <v>3.3762</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6271</v>
+        <v>0.8699</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5618</v>
+        <v>0.9012</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4337</v>
+        <v>3.3762</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4337</v>
+        <v>3.3762</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4337</v>
+        <v>3.3762</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5258</v>
+        <v>3.6104</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5258</v>
+        <v>3.6104</v>
       </c>
       <c r="N15" t="n">
         <v>280</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4124</v>
+        <v>3.2413</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6216</v>
+        <v>0.8351</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5532</v>
+        <v>0.8474</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4124</v>
+        <v>3.2413</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4124</v>
+        <v>3.2413</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4124</v>
+        <v>3.2413</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4576</v>
+        <v>3.3518</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4576</v>
+        <v>3.3518</v>
       </c>
       <c r="N16" t="n">
         <v>216</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3045</v>
+        <v>3.1184</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5938</v>
+        <v>0.8035</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.7985</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3045</v>
+        <v>3.1184</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3045</v>
+        <v>3.1184</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3045</v>
+        <v>3.1184</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3807</v>
+        <v>3.3068</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3807</v>
+        <v>3.3068</v>
       </c>
       <c r="N17" t="n">
         <v>251</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2378</v>
+        <v>2.9087</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5766</v>
+        <v>0.7494</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4827</v>
+        <v>0.7149</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2378</v>
+        <v>2.9087</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2378</v>
+        <v>2.9087</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2378</v>
+        <v>2.9087</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3442</v>
+        <v>2.9579</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>249</v>
+        <v>151</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3442</v>
+        <v>2.9579</v>
       </c>
       <c r="N18" t="n">
-        <v>249</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1253</v>
+        <v>2.8097</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5476</v>
+        <v>0.7239</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4372</v>
+        <v>0.6755</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1253</v>
+        <v>2.8097</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1253</v>
+        <v>2.8097</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1253</v>
+        <v>2.8097</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2057</v>
+        <v>3.0045</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2057</v>
+        <v>3.0045</v>
       </c>
       <c r="N19" t="n">
         <v>280</v>
@@ -1320,262 +1320,262 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>boX</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.895</v>
+        <v>2.6882</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4883</v>
+        <v>0.6926</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3442</v>
+        <v>0.6271</v>
       </c>
       <c r="E20" t="n">
-        <v>1.895</v>
+        <v>2.6882</v>
       </c>
       <c r="F20" t="n">
-        <v>1.895</v>
+        <v>2.6882</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.895</v>
+        <v>2.6882</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9306</v>
+        <v>2.9232</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.9306</v>
+        <v>2.9232</v>
       </c>
       <c r="N20" t="n">
-        <v>166</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Forester</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.727</v>
+        <v>2.4627</v>
       </c>
       <c r="C21" t="n">
-        <v>0.445</v>
+        <v>0.6345</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2763</v>
+        <v>0.5372</v>
       </c>
       <c r="E21" t="n">
-        <v>1.727</v>
+        <v>2.4627</v>
       </c>
       <c r="F21" t="n">
-        <v>1.727</v>
+        <v>2.4627</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.727</v>
+        <v>2.4627</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7431</v>
+        <v>2.6335</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>151</v>
+        <v>280</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7431</v>
+        <v>2.6335</v>
       </c>
       <c r="N21" t="n">
-        <v>151</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Forester</t>
+          <t>boX</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6455</v>
+        <v>2.3101</v>
       </c>
       <c r="C22" t="n">
-        <v>0.424</v>
+        <v>0.5952</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2434</v>
+        <v>0.4764</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6455</v>
+        <v>2.3101</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6455</v>
+        <v>2.3101</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6455</v>
+        <v>2.3101</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7078</v>
+        <v>2.3889</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>280</v>
+        <v>166</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7078</v>
+        <v>2.3889</v>
       </c>
       <c r="N22" t="n">
-        <v>280</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>dukefissura</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3972</v>
+        <v>2.0051</v>
       </c>
       <c r="C23" t="n">
-        <v>0.36</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1431</v>
+        <v>0.3549</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3972</v>
+        <v>2.0051</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3972</v>
+        <v>2.0051</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3972</v>
+        <v>2.0051</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4433</v>
+        <v>2.0562</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4433</v>
+        <v>2.0562</v>
       </c>
       <c r="N23" t="n">
-        <v>206</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KENSI</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0062</v>
+        <v>1.8892</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2593</v>
+        <v>0.4868</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0149</v>
+        <v>0.3087</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0062</v>
+        <v>1.8892</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0062</v>
+        <v>1.8892</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0062</v>
+        <v>1.8892</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0109</v>
+        <v>2.0033</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0109</v>
+        <v>2.0033</v>
       </c>
       <c r="N24" t="n">
-        <v>157</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>KENSI</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9927</v>
+        <v>1.4805</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2558</v>
+        <v>0.3815</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0203</v>
+        <v>0.1459</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9927</v>
+        <v>1.4805</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9927</v>
+        <v>1.4805</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9927</v>
+        <v>1.4805</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9973</v>
+        <v>1.493</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9973</v>
+        <v>1.493</v>
       </c>
       <c r="N25" t="n">
         <v>157</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.0633</v>
       </c>
       <c r="C26" t="n">
-        <v>0.229</v>
+        <v>0.274</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0624</v>
+        <v>-0.0203</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.0633</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.0633</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.0633</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8969</v>
+        <v>1.0812</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8969</v>
+        <v>1.0812</v>
       </c>
       <c r="N26" t="n">
         <v>151</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8077</v>
+        <v>1.047</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2081</v>
+        <v>0.2698</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0951</v>
+        <v>-0.0268</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8077</v>
+        <v>1.047</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8077</v>
+        <v>1.047</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8077</v>
+        <v>1.047</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8153</v>
+        <v>1.0647</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8153</v>
+        <v>1.0647</v>
       </c>
       <c r="N27" t="n">
         <v>151</v>
@@ -1688,216 +1688,216 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jyo</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7574</v>
+        <v>0.989</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1951</v>
+        <v>0.2548</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1154</v>
+        <v>-0.0499</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7574</v>
+        <v>0.989</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7574</v>
+        <v>0.989</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7574</v>
+        <v>0.989</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7716</v>
+        <v>0.9973</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7716</v>
+        <v>0.9973</v>
       </c>
       <c r="N28" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dukefissura</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6844</v>
+        <v>0.9252</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1763</v>
+        <v>0.2384</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1449</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6844</v>
+        <v>0.9252</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6844</v>
+        <v>0.9252</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6844</v>
+        <v>0.9252</v>
       </c>
       <c r="I29" t="n">
-        <v>0.694</v>
+        <v>0.9811</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>131</v>
+        <v>206</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.694</v>
+        <v>0.9811</v>
       </c>
       <c r="N29" t="n">
-        <v>131</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Porya</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6201</v>
+        <v>0.882</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1598</v>
+        <v>0.2273</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1709</v>
+        <v>-0.0925</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6201</v>
+        <v>0.882</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6201</v>
+        <v>0.882</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6201</v>
+        <v>0.882</v>
       </c>
       <c r="I30" t="n">
-        <v>0.623</v>
+        <v>0.8969</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.623</v>
+        <v>0.8969</v>
       </c>
       <c r="N30" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SENSEi</t>
+          <t>Jyo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3442</v>
+        <v>0.7462</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0887</v>
+        <v>0.1923</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2823</v>
+        <v>-0.1466</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3442</v>
+        <v>0.7462</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3442</v>
+        <v>0.7462</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3442</v>
+        <v>0.7462</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3442</v>
+        <v>0.7716</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3442</v>
+        <v>0.7716</v>
       </c>
       <c r="N31" t="n">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>svyat</t>
+          <t>Porya</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2908</v>
+        <v>0.6179</v>
       </c>
       <c r="C32" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.1592</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3039</v>
+        <v>-0.1977</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2908</v>
+        <v>0.6179</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2908</v>
+        <v>0.6179</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2908</v>
+        <v>0.6179</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2922</v>
+        <v>0.6231</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2922</v>
+        <v>0.6231</v>
       </c>
       <c r="N32" t="n">
         <v>139</v>
@@ -1918,277 +1918,277 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>SENSEi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2067</v>
+        <v>0.3442</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0533</v>
+        <v>0.0887</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3379</v>
+        <v>-0.3068</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2067</v>
+        <v>0.3442</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2067</v>
+        <v>0.3442</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2067</v>
+        <v>0.3442</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2086</v>
+        <v>0.3442</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2086</v>
+        <v>0.3442</v>
       </c>
       <c r="N33" t="n">
-        <v>151</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Raijin</t>
+          <t>iDISBALANCE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1517</v>
+        <v>0.3391</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0391</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3601</v>
+        <v>-0.3088</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1517</v>
+        <v>0.3391</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1517</v>
+        <v>0.3391</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1517</v>
+        <v>0.3391</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1525</v>
+        <v>0.3507</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1525</v>
+        <v>0.3507</v>
       </c>
       <c r="N34" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>svyat</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0385</v>
+        <v>0.3288</v>
       </c>
       <c r="C35" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0847</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4058</v>
+        <v>-0.3129</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0385</v>
+        <v>0.3288</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0385</v>
+        <v>0.3288</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0385</v>
+        <v>0.3288</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0387</v>
+        <v>0.3316</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0387</v>
+        <v>0.3316</v>
       </c>
       <c r="N35" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iDISBALANCE</t>
+          <t>Raijin</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0323</v>
+        <v>0.1513</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0083</v>
+        <v>0.039</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4083</v>
+        <v>-0.3836</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0323</v>
+        <v>0.1513</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0323</v>
+        <v>0.1513</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0323</v>
+        <v>0.1513</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0329</v>
+        <v>0.1526</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0329</v>
+        <v>0.1526</v>
       </c>
       <c r="N36" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>waterfaLLZ</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.031</v>
+        <v>0.0384</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.008</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4339</v>
+        <v>-0.4286</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.031</v>
+        <v>0.0384</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.031</v>
+        <v>0.0384</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.031</v>
+        <v>0.0384</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0311</v>
+        <v>0.0387</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0311</v>
+        <v>0.0387</v>
       </c>
       <c r="N37" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>waterfaLLZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.2937</v>
+        <v>-0.0308</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0757</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.54</v>
+        <v>-0.4562</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.2937</v>
+        <v>-0.0308</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2937</v>
+        <v>-0.0308</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2937</v>
+        <v>-0.0308</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3034</v>
+        <v>-0.0311</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.3034</v>
+        <v>-0.0311</v>
       </c>
       <c r="N38" t="n">
-        <v>206</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.359</v>
+        <v>-0.2533</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.0925</v>
+        <v>-0.0653</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5664</v>
+        <v>-0.5448</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.359</v>
+        <v>-0.2533</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.359</v>
+        <v>-0.2533</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.359</v>
+        <v>-0.2533</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3607</v>
+        <v>-0.2554</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.3607</v>
+        <v>-0.2554</v>
       </c>
       <c r="N39" t="n">
         <v>139</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.8256</v>
+        <v>-0.5369</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2127</v>
+        <v>-0.1383</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.7549</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.8256</v>
+        <v>-0.5369</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.8256</v>
+        <v>-0.5369</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8256</v>
+        <v>-0.5369</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8489</v>
+        <v>-0.5646</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.8489</v>
+        <v>-0.5646</v>
       </c>
       <c r="N40" t="n">
         <v>277</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>ice</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.905</v>
+        <v>-0.5372</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2332</v>
+        <v>-0.1384</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.787</v>
+        <v>-0.6579</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.905</v>
+        <v>-0.5372</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.905</v>
+        <v>-0.5372</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.905</v>
+        <v>-0.5372</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9349</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9349</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>251</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>j3kie</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.9116</v>
+        <v>-0.7593</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.2349</v>
+        <v>-0.1956</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.7896</v>
+        <v>-0.7464</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.9116</v>
+        <v>-0.7593</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.9116</v>
+        <v>-0.7593</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.9116</v>
+        <v>-0.7593</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.9116</v>
+        <v>-0.8052</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>125</v>
+        <v>251</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.9116</v>
+        <v>-0.8052</v>
       </c>
       <c r="N42" t="n">
-        <v>125</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.965</v>
+        <v>-0.7639</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.2486</v>
+        <v>-0.1968</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.8112</v>
+        <v>-0.7482</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.965</v>
+        <v>-0.7639</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.965</v>
+        <v>-0.7639</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.965</v>
+        <v>-0.7639</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.9831</v>
+        <v>-0.7899</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.9831</v>
+        <v>-0.7899</v>
       </c>
       <c r="N43" t="n">
         <v>216</v>
@@ -2424,139 +2424,139 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ice</t>
+          <t>j3kie</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-1.0355</v>
+        <v>-0.9116</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.2668</v>
+        <v>-0.2349</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.8397</v>
+        <v>-0.8071</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.0355</v>
+        <v>-0.9116</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.0355</v>
+        <v>-0.9116</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.0355</v>
+        <v>-0.9116</v>
       </c>
       <c r="I44" t="n">
-        <v>-1.05</v>
+        <v>-0.9116</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-1.05</v>
+        <v>-0.9116</v>
       </c>
       <c r="N44" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sergiz</t>
+          <t>DavCost</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-1.075</v>
+        <v>-1.0436</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.277</v>
+        <v>-0.2689</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.8556</v>
+        <v>-0.8597</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.075</v>
+        <v>-1.0436</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.075</v>
+        <v>-1.0436</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.075</v>
+        <v>-1.0436</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.075</v>
+        <v>-1.0792</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>125</v>
+        <v>216</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-1.075</v>
+        <v>-1.0792</v>
       </c>
       <c r="N45" t="n">
-        <v>125</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DavCost</t>
+          <t>Sergiz</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.1115</v>
+        <v>-1.075</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2864</v>
+        <v>-0.277</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.8704</v>
+        <v>-0.8722</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.1115</v>
+        <v>-1.075</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.1115</v>
+        <v>-1.075</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.1115</v>
+        <v>-1.075</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.1324</v>
+        <v>-1.075</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-1.1324</v>
+        <v>-1.075</v>
       </c>
       <c r="N46" t="n">
-        <v>216</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.4772</v>
+        <v>-1.4378</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.3806</v>
+        <v>-0.3705</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.0181</v>
+        <v>-1.0167</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.4772</v>
+        <v>-1.4378</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.4772</v>
+        <v>-1.4378</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.4772</v>
+        <v>-1.4378</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.5189</v>
+        <v>-1.512</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-1.5189</v>
+        <v>-1.512</v>
       </c>
       <c r="N47" t="n">
         <v>277</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-1.494</v>
+        <v>-1.4885</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.3849</v>
+        <v>-0.3835</v>
       </c>
       <c r="D48" t="n">
-        <v>-1.0249</v>
+        <v>-1.0369</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.494</v>
+        <v>-1.4885</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.494</v>
+        <v>-1.4885</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.494</v>
+        <v>-1.4885</v>
       </c>
       <c r="I48" t="n">
         <v>-1.501</v>
@@ -2654,599 +2654,599 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1.6658</v>
+        <v>-1.5358</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.4292</v>
+        <v>-0.3957</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.0943</v>
+        <v>-1.0558</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.6658</v>
+        <v>-1.5358</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.6658</v>
+        <v>-1.5358</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.6658</v>
+        <v>-1.5358</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.6658</v>
+        <v>-1.5487</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-1.6658</v>
+        <v>-1.5487</v>
       </c>
       <c r="N49" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>neaLaN</t>
+          <t>RAiLWAY</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.6694</v>
+        <v>-1.5967</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.4301</v>
+        <v>-0.4114</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.0958</v>
+        <v>-1.08</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.6694</v>
+        <v>-1.5967</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.6694</v>
+        <v>-1.5967</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.6694</v>
+        <v>-1.5967</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.685</v>
+        <v>-1.6511</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-1.685</v>
+        <v>-1.6511</v>
       </c>
       <c r="N50" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RAiLWAY</t>
+          <t>neaLaN</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.6995</v>
+        <v>-1.657</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4379</v>
+        <v>-0.4269</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.1079</v>
+        <v>-1.1041</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.6995</v>
+        <v>-1.657</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.6995</v>
+        <v>-1.657</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.6995</v>
+        <v>-1.657</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.7314</v>
+        <v>-1.685</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>216</v>
+        <v>151</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-1.7314</v>
+        <v>-1.685</v>
       </c>
       <c r="N51" t="n">
-        <v>216</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.9357</v>
+        <v>-1.6658</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.4987</v>
+        <v>-0.4292</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.2033</v>
+        <v>-1.1076</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.9357</v>
+        <v>-1.6658</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.9357</v>
+        <v>-1.6658</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.9357</v>
+        <v>-1.6658</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.9904</v>
+        <v>-1.6658</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>277</v>
+        <v>125</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.9904</v>
+        <v>-1.6658</v>
       </c>
       <c r="N52" t="n">
-        <v>277</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>smiley</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-2.031</v>
+        <v>-1.8928</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.5233</v>
+        <v>-0.4877</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.2418</v>
+        <v>-1.198</v>
       </c>
       <c r="E53" t="n">
-        <v>-2.031</v>
+        <v>-1.8928</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.031</v>
+        <v>-1.8928</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-2.031</v>
+        <v>-1.8928</v>
       </c>
       <c r="I53" t="n">
-        <v>-2.0595</v>
+        <v>-1.9904</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>131</v>
+        <v>277</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-2.0595</v>
+        <v>-1.9904</v>
       </c>
       <c r="N53" t="n">
-        <v>131</v>
+        <v>277</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>floweaN</t>
+          <t>smiley</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-2.0949</v>
+        <v>-2.0084</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5175</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.2677</v>
+        <v>-1.2441</v>
       </c>
       <c r="E54" t="n">
-        <v>-2.0949</v>
+        <v>-2.0084</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.0949</v>
+        <v>-2.0084</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-2.0949</v>
+        <v>-2.0084</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.1342</v>
+        <v>-2.0595</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>216</v>
+        <v>131</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-2.1342</v>
+        <v>-2.0595</v>
       </c>
       <c r="N54" t="n">
-        <v>216</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sorrow</t>
+          <t>floweaN</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-2.1342</v>
+        <v>-2.0638</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.5317</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.2835</v>
+        <v>-1.2661</v>
       </c>
       <c r="E55" t="n">
-        <v>-2.1342</v>
+        <v>-2.0638</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.1342</v>
+        <v>-2.0638</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
+        <v>-2.0638</v>
+      </c>
+      <c r="I55" t="n">
         <v>-2.1342</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-2.1642</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>131</v>
+        <v>216</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-2.1642</v>
+        <v>-2.1342</v>
       </c>
       <c r="N55" t="n">
-        <v>131</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Psycho</t>
+          <t>sorrow</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-2.2077</v>
+        <v>-2.1088</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.5688</v>
+        <v>-0.5433</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.3132</v>
+        <v>-1.2841</v>
       </c>
       <c r="E56" t="n">
-        <v>-2.2077</v>
+        <v>-2.1088</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.2077</v>
+        <v>-2.1088</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.2077</v>
+        <v>-2.1088</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.2077</v>
+        <v>-2.1625</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-2.2077</v>
+        <v>-2.1625</v>
       </c>
       <c r="N56" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>Psycho</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-2.2102</v>
+        <v>-2.2077</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.5695</v>
+        <v>-0.5688</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.3142</v>
+        <v>-1.3235</v>
       </c>
       <c r="E57" t="n">
-        <v>-2.2102</v>
+        <v>-2.2077</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.2102</v>
+        <v>-2.2077</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.2102</v>
+        <v>-2.2077</v>
       </c>
       <c r="I57" t="n">
-        <v>-2.2205</v>
+        <v>-2.2077</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-2.2205</v>
+        <v>-2.2077</v>
       </c>
       <c r="N57" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1eeR</t>
+          <t>w1nt3r</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-2.7674</v>
+        <v>-2.6393</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.713</v>
+        <v>-0.68</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.5393</v>
+        <v>-1.4954</v>
       </c>
       <c r="E58" t="n">
-        <v>-2.7674</v>
+        <v>-2.6393</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.7674</v>
+        <v>-2.6393</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.7674</v>
+        <v>-2.6393</v>
       </c>
       <c r="I58" t="n">
-        <v>-2.8193</v>
+        <v>-2.7065</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-2.8193</v>
+        <v>-2.7065</v>
       </c>
       <c r="N58" t="n">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>1eeR</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-2.8992</v>
+        <v>-2.6935</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.747</v>
+        <v>-0.694</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.5926</v>
+        <v>-1.517</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.8992</v>
+        <v>-2.6935</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.8992</v>
+        <v>-2.6935</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.8992</v>
+        <v>-2.6935</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.995</v>
+        <v>-2.7853</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>251</v>
+        <v>166</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-2.995</v>
+        <v>-2.7853</v>
       </c>
       <c r="N59" t="n">
-        <v>251</v>
+        <v>166</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NickelBack</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-3.0161</v>
+        <v>-2.8243</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.7771</v>
+        <v>-0.7277</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.6398</v>
+        <v>-1.5691</v>
       </c>
       <c r="E60" t="n">
-        <v>-3.0161</v>
+        <v>-2.8243</v>
       </c>
       <c r="F60" t="n">
-        <v>-3.0161</v>
+        <v>-2.8243</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-3.0161</v>
+        <v>-2.8243</v>
       </c>
       <c r="I60" t="n">
-        <v>-3.1302</v>
+        <v>-2.995</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-3.1302</v>
+        <v>-2.995</v>
       </c>
       <c r="N60" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>w1nt3r</t>
+          <t>NickelBack</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-3.1727</v>
+        <v>-2.9151</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.8175</v>
+        <v>-0.7511</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.7031</v>
+        <v>-1.6053</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.1727</v>
+        <v>-2.9151</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.1727</v>
+        <v>-2.9151</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-3.1727</v>
+        <v>-2.9151</v>
       </c>
       <c r="I61" t="n">
-        <v>-3.2172</v>
+        <v>-3.1173</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>131</v>
+        <v>280</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-3.2172</v>
+        <v>-3.1173</v>
       </c>
       <c r="N61" t="n">
-        <v>131</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6070/event_6070_evp_summary.xlsx
+++ b/database/event/6070/event_6070_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.0775</v>
+        <v>5.2999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3082</v>
+        <v>1.3655</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6542</v>
+        <v>1.7884</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0775</v>
+        <v>5.2999</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0775</v>
+        <v>5.2999</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.7894</v>
+        <v>8.8748</v>
       </c>
       <c r="I2" t="n">
-        <v>11.6557</v>
+        <v>11.446</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>11.6557</v>
+        <v>11.446</v>
       </c>
       <c r="N2" t="n">
         <v>249</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.1112</v>
+        <v>4.1164</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0593</v>
+        <v>1.0606</v>
       </c>
       <c r="D3" t="n">
-        <v>1.218</v>
+        <v>1.2497</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1112</v>
+        <v>4.1164</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1112</v>
+        <v>4.1164</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6677</v>
+        <v>6.2845</v>
       </c>
       <c r="I3" t="n">
-        <v>7.2182</v>
+        <v>7.321</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7.2182</v>
+        <v>7.321</v>
       </c>
       <c r="N3" t="n">
         <v>277</v>
@@ -584,78 +584,78 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9417</v>
+        <v>4.0339</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0156</v>
+        <v>1.0393</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1415</v>
+        <v>1.2121</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9417</v>
+        <v>4.0339</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9417</v>
+        <v>4.0339</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2956</v>
+        <v>6.104</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0216</v>
+        <v>7.8724</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7.0216</v>
+        <v>7.8724</v>
       </c>
       <c r="N4" t="n">
-        <v>206</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9069</v>
+        <v>3.9368</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0066</v>
+        <v>1.0143</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1258</v>
+        <v>1.1679</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9069</v>
+        <v>3.9368</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9069</v>
+        <v>3.9368</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.219</v>
+        <v>5.8914</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9202</v>
+        <v>7.0399</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6.9202</v>
+        <v>7.0399</v>
       </c>
       <c r="N5" t="n">
         <v>206</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.882</v>
+        <v>3.9334</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0002</v>
+        <v>1.0135</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1145</v>
+        <v>1.1664</v>
       </c>
       <c r="E6" t="n">
-        <v>3.882</v>
+        <v>3.9334</v>
       </c>
       <c r="F6" t="n">
-        <v>3.882</v>
+        <v>3.9334</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1643</v>
+        <v>5.884</v>
       </c>
       <c r="I6" t="n">
-        <v>7.7276</v>
+        <v>7.031</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.7276</v>
+        <v>7.031</v>
       </c>
       <c r="N6" t="n">
-        <v>249</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6859</v>
+        <v>3.5883</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9497</v>
+        <v>0.9245</v>
       </c>
       <c r="D7" t="n">
-        <v>1.026</v>
+        <v>1.0093</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6859</v>
+        <v>3.5883</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6859</v>
+        <v>3.5883</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7339</v>
+        <v>5.1288</v>
       </c>
       <c r="I7" t="n">
-        <v>6.2769</v>
+        <v>6.1286</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2769</v>
+        <v>6.1286</v>
       </c>
       <c r="N7" t="n">
         <v>206</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5936</v>
+        <v>3.4316</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.8842</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9843</v>
+        <v>0.9379</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5936</v>
+        <v>3.4316</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5936</v>
+        <v>3.4316</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5311</v>
+        <v>4.7858</v>
       </c>
       <c r="I8" t="n">
-        <v>6.008</v>
+        <v>5.7187</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6.008</v>
+        <v>5.7187</v>
       </c>
       <c r="N8" t="n">
         <v>251</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5372</v>
+        <v>3.3747</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9114</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9589</v>
+        <v>0.912</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5372</v>
+        <v>3.3747</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5372</v>
+        <v>3.3747</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4073</v>
+        <v>4.6613</v>
       </c>
       <c r="I9" t="n">
-        <v>5.613</v>
+        <v>5.43</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.613</v>
+        <v>5.43</v>
       </c>
       <c r="N9" t="n">
         <v>277</v>
@@ -860,124 +860,124 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lack1</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2529</v>
+        <v>3.1811</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8381</v>
+        <v>0.8196</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8305</v>
+        <v>0.8239</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2529</v>
+        <v>3.1811</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2529</v>
+        <v>3.1811</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7831</v>
+        <v>4.2375</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2225</v>
+        <v>5.4652</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2225</v>
+        <v>5.4652</v>
       </c>
       <c r="N10" t="n">
-        <v>280</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lollipop21k</t>
+          <t>Lack1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1448</v>
+        <v>3.0648</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8103</v>
+        <v>0.7897</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7817</v>
+        <v>0.771</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1448</v>
+        <v>3.0648</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1448</v>
+        <v>3.0648</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5456</v>
+        <v>3.9829</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1658</v>
+        <v>4.882</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>166</v>
+        <v>280</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1658</v>
+        <v>4.882</v>
       </c>
       <c r="N11" t="n">
-        <v>166</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.1317</v>
+        <v>2.9422</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8069</v>
+        <v>0.7581</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7758</v>
+        <v>0.7151</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1317</v>
+        <v>2.9422</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1317</v>
+        <v>2.9422</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5168</v>
+        <v>3.7145</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2624</v>
+        <v>4.7907</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2624</v>
+        <v>4.7907</v>
       </c>
       <c r="N12" t="n">
         <v>249</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0713</v>
+        <v>2.9187</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7913</v>
+        <v>0.752</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7044</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0713</v>
+        <v>2.9187</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0713</v>
+        <v>2.9187</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3842</v>
+        <v>3.6632</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6718</v>
+        <v>4.4901</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6718</v>
+        <v>4.4901</v>
       </c>
       <c r="N13" t="n">
         <v>280</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X5G7V</t>
+          <t>lollipop21k</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0376</v>
+        <v>2.9019</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7826</v>
+        <v>0.7477</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7333</v>
+        <v>0.6968</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0376</v>
+        <v>2.9019</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0376</v>
+        <v>2.9019</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3103</v>
+        <v>3.6264</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8894</v>
+        <v>4.0149</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8894</v>
+        <v>4.0149</v>
       </c>
       <c r="N14" t="n">
-        <v>216</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>X5G7V</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9795</v>
+        <v>2.7687</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7677</v>
+        <v>0.7134</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7071</v>
+        <v>0.6362</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9795</v>
+        <v>2.7687</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9795</v>
+        <v>2.7687</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1828</v>
+        <v>3.3348</v>
       </c>
       <c r="I15" t="n">
-        <v>4.7625</v>
+        <v>3.6921</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7625</v>
+        <v>3.6921</v>
       </c>
       <c r="N15" t="n">
-        <v>249</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9538</v>
+        <v>2.7422</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7611</v>
+        <v>0.7065</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6955</v>
+        <v>0.6241</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9538</v>
+        <v>2.7422</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9538</v>
+        <v>2.7422</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1262</v>
+        <v>3.2769</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1452</v>
+        <v>3.9157</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1452</v>
+        <v>3.9157</v>
       </c>
       <c r="N16" t="n">
         <v>251</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9062</v>
+        <v>2.6989</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7488</v>
+        <v>0.6954</v>
       </c>
       <c r="D17" t="n">
-        <v>0.674</v>
+        <v>0.6044</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9062</v>
+        <v>2.6989</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9062</v>
+        <v>2.6989</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0217</v>
+        <v>3.1821</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1714</v>
+        <v>3.9004</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1714</v>
+        <v>3.9004</v>
       </c>
       <c r="N17" t="n">
         <v>280</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.8886</v>
+        <v>2.6334</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7443</v>
+        <v>0.6785</v>
       </c>
       <c r="D18" t="n">
-        <v>0.666</v>
+        <v>0.5746</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8886</v>
+        <v>2.6334</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8886</v>
+        <v>2.6334</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9832</v>
+        <v>3.0389</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2336</v>
+        <v>3.1975</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2336</v>
+        <v>3.1975</v>
       </c>
       <c r="N18" t="n">
         <v>151</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.8123</v>
+        <v>2.6263</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7246</v>
+        <v>0.6767</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.5713</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8123</v>
+        <v>2.6263</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8123</v>
+        <v>2.6263</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8156</v>
+        <v>3.0232</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8868</v>
+        <v>3.7057</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8868</v>
+        <v>3.7057</v>
       </c>
       <c r="N19" t="n">
         <v>280</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5425</v>
+        <v>2.5277</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6551</v>
+        <v>0.6513</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5098</v>
+        <v>0.5265</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5425</v>
+        <v>2.5277</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5425</v>
+        <v>2.5277</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5425</v>
+        <v>2.8075</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3712</v>
+        <v>3.6209</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3712</v>
+        <v>3.6209</v>
       </c>
       <c r="N20" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.4511</v>
+        <v>2.4793</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6315</v>
+        <v>0.6388</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4685</v>
+        <v>0.5044</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4511</v>
+        <v>2.4793</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4511</v>
+        <v>2.4793</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4511</v>
+        <v>2.7016</v>
       </c>
       <c r="I21" t="n">
-        <v>3.6677</v>
+        <v>3.2282</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6677</v>
+        <v>3.2282</v>
       </c>
       <c r="N21" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.3711</v>
+        <v>2.326</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6109</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4324</v>
+        <v>0.4346</v>
       </c>
       <c r="E22" t="n">
-        <v>2.3711</v>
+        <v>2.326</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3711</v>
+        <v>2.326</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.3711</v>
+        <v>2.366</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7859</v>
+        <v>2.6195</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7859</v>
+        <v>2.6195</v>
       </c>
       <c r="N22" t="n">
         <v>166</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.968</v>
+        <v>2.1878</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5071</v>
+        <v>0.5637</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2504</v>
+        <v>0.3717</v>
       </c>
       <c r="E23" t="n">
-        <v>1.968</v>
+        <v>2.1878</v>
       </c>
       <c r="F23" t="n">
-        <v>1.968</v>
+        <v>2.1878</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.968</v>
+        <v>2.1878</v>
       </c>
       <c r="I23" t="n">
-        <v>2.6095</v>
+        <v>2.6143</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.6095</v>
+        <v>2.6143</v>
       </c>
       <c r="N23" t="n">
         <v>206</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KENSI</t>
+          <t>dukefissura</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9097</v>
+        <v>1.9041</v>
       </c>
       <c r="C24" t="n">
-        <v>0.492</v>
+        <v>0.4906</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2241</v>
+        <v>0.2426</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9097</v>
+        <v>1.9041</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9097</v>
+        <v>1.9041</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9097</v>
+        <v>1.9041</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9883</v>
+        <v>2.0551</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9883</v>
+        <v>2.0551</v>
       </c>
       <c r="N24" t="n">
-        <v>157</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dukefissura</t>
+          <t>KENSI</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8981</v>
+        <v>1.8908</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4891</v>
+        <v>0.4872</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2189</v>
+        <v>0.2365</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8981</v>
+        <v>1.8908</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8981</v>
+        <v>1.8908</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8981</v>
+        <v>1.8908</v>
       </c>
       <c r="I25" t="n">
-        <v>2.142</v>
+        <v>1.9395</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.142</v>
+        <v>1.9395</v>
       </c>
       <c r="N25" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6945</v>
+        <v>1.561</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4366</v>
+        <v>0.4022</v>
       </c>
       <c r="D26" t="n">
-        <v>0.127</v>
+        <v>0.0864</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6945</v>
+        <v>1.561</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6945</v>
+        <v>1.561</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6945</v>
+        <v>1.561</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8367</v>
+        <v>1.6425</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.8367</v>
+        <v>1.6425</v>
       </c>
       <c r="N26" t="n">
         <v>151</v>
@@ -1642,124 +1642,124 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.33</v>
+        <v>1.3571</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3427</v>
+        <v>0.3497</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0376</v>
+        <v>-0.0064</v>
       </c>
       <c r="E27" t="n">
-        <v>1.33</v>
+        <v>1.3571</v>
       </c>
       <c r="F27" t="n">
-        <v>1.33</v>
+        <v>1.3571</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.33</v>
+        <v>1.3571</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3847</v>
+        <v>1.6217</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3847</v>
+        <v>1.6217</v>
       </c>
       <c r="N27" t="n">
-        <v>157</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.2843</v>
+        <v>1.3151</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3309</v>
+        <v>0.3388</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0582</v>
+        <v>-0.0255</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2843</v>
+        <v>1.3151</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2843</v>
+        <v>1.3151</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2843</v>
+        <v>1.3151</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3921</v>
+        <v>1.349</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3921</v>
+        <v>1.349</v>
       </c>
       <c r="N28" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2132</v>
+        <v>1.3024</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3126</v>
+        <v>0.3356</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0313</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2132</v>
+        <v>1.3024</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2132</v>
+        <v>1.3024</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2132</v>
+        <v>1.3024</v>
       </c>
       <c r="I29" t="n">
-        <v>1.315</v>
+        <v>1.3704</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.315</v>
+        <v>1.3704</v>
       </c>
       <c r="N29" t="n">
         <v>151</v>
@@ -1780,124 +1780,124 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1534</v>
+        <v>1.1909</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2972</v>
+        <v>0.3068</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1173</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1534</v>
+        <v>1.1909</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1534</v>
+        <v>1.1909</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1534</v>
+        <v>1.1909</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5293</v>
+        <v>1.2531</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5293</v>
+        <v>1.2531</v>
       </c>
       <c r="N30" t="n">
-        <v>206</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Porya</t>
+          <t>Jyo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9119</v>
+        <v>0.9296</v>
       </c>
       <c r="C31" t="n">
-        <v>0.235</v>
+        <v>0.2395</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2263</v>
+        <v>-0.201</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9119</v>
+        <v>0.9296</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9119</v>
+        <v>0.9296</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9119</v>
+        <v>0.9296</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9494</v>
+        <v>1.0292</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9494</v>
+        <v>1.0292</v>
       </c>
       <c r="N31" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jyo</t>
+          <t>iDISBALANCE</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9111</v>
+        <v>0.8628</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2347</v>
+        <v>0.2223</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2267</v>
+        <v>-0.2314</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9111</v>
+        <v>0.8628</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9111</v>
+        <v>0.8628</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9111</v>
+        <v>0.8628</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0705</v>
+        <v>0.9552</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.0705</v>
+        <v>0.9552</v>
       </c>
       <c r="N32" t="n">
         <v>166</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>svyat</t>
+          <t>Porya</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7497</v>
+        <v>0.8509</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1932</v>
+        <v>0.2192</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2996</v>
+        <v>-0.2369</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7497</v>
+        <v>0.8509</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7497</v>
+        <v>0.8509</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7497</v>
+        <v>0.8509</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7805</v>
+        <v>0.8728</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7805</v>
+        <v>0.8728</v>
       </c>
       <c r="N33" t="n">
         <v>139</v>
@@ -1964,185 +1964,185 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>svyat</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7353</v>
+        <v>0.7085</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1895</v>
+        <v>0.1825</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3061</v>
+        <v>-0.3017</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7353</v>
+        <v>0.7085</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7353</v>
+        <v>0.7085</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7353</v>
+        <v>0.7085</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7655</v>
+        <v>0.7268</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7655</v>
+        <v>0.7268</v>
       </c>
       <c r="N34" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iDISBALANCE</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7331</v>
+        <v>0.6849</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1889</v>
+        <v>0.1765</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3071</v>
+        <v>-0.3124</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7331</v>
+        <v>0.6849</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7331</v>
+        <v>0.6849</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7331</v>
+        <v>0.6849</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.7025</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.7025</v>
       </c>
       <c r="N35" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SENSEi</t>
+          <t>waterfaLLZ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5535</v>
+        <v>0.5118</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1426</v>
+        <v>0.1319</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3881</v>
+        <v>-0.3912</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5535</v>
+        <v>0.5118</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5535</v>
+        <v>0.5118</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5535</v>
+        <v>0.5118</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5535</v>
+        <v>0.525</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5535</v>
+        <v>0.525</v>
       </c>
       <c r="N36" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>waterfaLLZ</t>
+          <t>SENSEi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.4831</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1417</v>
+        <v>0.1245</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3898</v>
+        <v>-0.4043</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.4831</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.4831</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.4831</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5725</v>
+        <v>0.4831</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5725</v>
+        <v>0.4831</v>
       </c>
       <c r="N37" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4867</v>
+        <v>0.4505</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1254</v>
+        <v>0.1161</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4183</v>
+        <v>-0.4191</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4867</v>
+        <v>0.4505</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4867</v>
+        <v>0.4505</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4867</v>
+        <v>0.4505</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5067</v>
+        <v>0.4621</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5067</v>
+        <v>0.4621</v>
       </c>
       <c r="N38" t="n">
         <v>139</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2851</v>
+        <v>0.2713</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0735</v>
+        <v>0.0699</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5093</v>
+        <v>-0.5007</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2851</v>
+        <v>0.2713</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2851</v>
+        <v>0.2713</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2851</v>
+        <v>0.2713</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3631</v>
+        <v>0.3161</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3631</v>
+        <v>0.3161</v>
       </c>
       <c r="N39" t="n">
         <v>277</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1033</v>
+        <v>0.0101</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0266</v>
+        <v>0.0026</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5914</v>
+        <v>-0.6196</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1033</v>
+        <v>0.0101</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1033</v>
+        <v>0.0101</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1033</v>
+        <v>0.0101</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1075</v>
+        <v>0.0104</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1075</v>
+        <v>0.0104</v>
       </c>
       <c r="N40" t="n">
         <v>139</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1636</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0235</v>
+        <v>-0.0422</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.6792</v>
+        <v>-0.6987</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1636</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1636</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1636</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.103</v>
+        <v>-0.1766</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.103</v>
+        <v>-0.1766</v>
       </c>
       <c r="N41" t="n">
         <v>131</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1407</v>
+        <v>-0.1754</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0363</v>
+        <v>-0.0452</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.7015</v>
+        <v>-0.704</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1407</v>
+        <v>-0.1754</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1407</v>
+        <v>-0.1754</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1407</v>
+        <v>-0.1754</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1865</v>
+        <v>-0.2096</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1865</v>
+        <v>-0.2096</v>
       </c>
       <c r="N42" t="n">
         <v>251</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.2161</v>
+        <v>-0.2921</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0557</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.7356</v>
+        <v>-0.7572</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2161</v>
+        <v>-0.2921</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2161</v>
+        <v>-0.2921</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2161</v>
+        <v>-0.2921</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2539</v>
+        <v>-0.3234</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.2539</v>
+        <v>-0.3234</v>
       </c>
       <c r="N43" t="n">
         <v>216</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.323</v>
+        <v>-0.4244</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0832</v>
+        <v>-0.1093</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.8174</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.323</v>
+        <v>-0.4244</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.323</v>
+        <v>-0.4244</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.323</v>
+        <v>-0.4244</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3795</v>
+        <v>-0.4699</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.3795</v>
+        <v>-0.4699</v>
       </c>
       <c r="N44" t="n">
         <v>216</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4505</v>
+        <v>-0.4514</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.1161</v>
+        <v>-0.1163</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.8414</v>
+        <v>-0.8297</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4505</v>
+        <v>-0.4514</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4505</v>
+        <v>-0.4514</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4505</v>
+        <v>-0.4514</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5738</v>
+        <v>-0.5258</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.5738</v>
+        <v>-0.5258</v>
       </c>
       <c r="N45" t="n">
         <v>277</v>
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.5028</v>
+        <v>-0.5851</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1295</v>
+        <v>-0.1508</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.865</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.5028</v>
+        <v>-0.5851</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.5028</v>
+        <v>-0.5851</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5028</v>
+        <v>-0.5851</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5028</v>
+        <v>-0.5851</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.5028</v>
+        <v>-0.5851</v>
       </c>
       <c r="N46" t="n">
         <v>125</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.5962</v>
+        <v>-0.6649</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1536</v>
+        <v>-0.1713</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.9072</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.5962</v>
+        <v>-0.6649</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.5962</v>
+        <v>-0.6649</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.5962</v>
+        <v>-0.6649</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6207</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6207</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="N47" t="n">
         <v>157</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6151</v>
+        <v>-0.6833</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1585</v>
+        <v>-0.1761</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.9157</v>
+        <v>-0.9353</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6151</v>
+        <v>-0.6833</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6151</v>
+        <v>-0.6833</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.6151</v>
+        <v>-0.6833</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6151</v>
+        <v>-0.6833</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.6151</v>
+        <v>-0.6833</v>
       </c>
       <c r="N48" t="n">
         <v>125</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.7198</v>
+        <v>-0.7698</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1855</v>
+        <v>-0.1983</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.963</v>
+        <v>-0.9746</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.7198</v>
+        <v>-0.7698</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.7198</v>
+        <v>-0.7698</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.7198</v>
+        <v>-0.7698</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.7494</v>
+        <v>-0.7896</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.7494</v>
+        <v>-0.7896</v>
       </c>
       <c r="N49" t="n">
         <v>157</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7503</v>
+        <v>-0.7946</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1933</v>
+        <v>-0.2047</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.9767</v>
+        <v>-0.9859</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.7503</v>
+        <v>-0.7946</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.7503</v>
+        <v>-0.7946</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.7503</v>
+        <v>-0.7946</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8133</v>
+        <v>-0.8361</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.8133</v>
+        <v>-0.8361</v>
       </c>
       <c r="N50" t="n">
         <v>151</v>
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.7901</v>
+        <v>-0.9042</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2036</v>
+        <v>-0.233</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.9947</v>
+        <v>-1.0358</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.7901</v>
+        <v>-0.9042</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.7901</v>
+        <v>-0.9042</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.7901</v>
+        <v>-0.9042</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9283</v>
+        <v>-1.0011</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.9283</v>
+        <v>-1.0011</v>
       </c>
       <c r="N51" t="n">
         <v>216</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.8457</v>
+        <v>-0.9382</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2179</v>
+        <v>-0.2417</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.0198</v>
+        <v>-1.0513</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.8457</v>
+        <v>-0.9382</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.8457</v>
+        <v>-0.9382</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.8457</v>
+        <v>-0.9382</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.077</v>
+        <v>-1.0929</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.077</v>
+        <v>-1.0929</v>
       </c>
       <c r="N52" t="n">
         <v>277</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9963</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2396</v>
+        <v>-0.2567</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.0578</v>
+        <v>-1.0777</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9963</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9963</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9963</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9963</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9963</v>
       </c>
       <c r="N53" t="n">
         <v>125</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.2476</v>
+        <v>-1.361</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.3214</v>
+        <v>-0.3507</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.2012</v>
+        <v>-1.2438</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.2476</v>
+        <v>-1.361</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.2476</v>
+        <v>-1.361</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.2476</v>
+        <v>-1.361</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.4659</v>
+        <v>-1.5068</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.4659</v>
+        <v>-1.5068</v>
       </c>
       <c r="N54" t="n">
         <v>216</v>
@@ -2930,93 +2930,93 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sorrow</t>
+          <t>1eeR</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.2976</v>
+        <v>-1.4105</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.3343</v>
+        <v>-0.3634</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.2238</v>
+        <v>-1.2663</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.2976</v>
+        <v>-1.4105</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.2976</v>
+        <v>-1.4105</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.2976</v>
+        <v>-1.4105</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.4644</v>
+        <v>-1.5616</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.4644</v>
+        <v>-1.5616</v>
       </c>
       <c r="N55" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1eeR</t>
+          <t>sorrow</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.317</v>
+        <v>-1.4216</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3393</v>
+        <v>-0.3663</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.2326</v>
+        <v>-1.2713</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.317</v>
+        <v>-1.4216</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.317</v>
+        <v>-1.4216</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.317</v>
+        <v>-1.4216</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.5474</v>
+        <v>-1.5344</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.5474</v>
+        <v>-1.5344</v>
       </c>
       <c r="N56" t="n">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57">
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.429</v>
+        <v>-1.542</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3682</v>
+        <v>-0.3973</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.2831</v>
+        <v>-1.3262</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.429</v>
+        <v>-1.542</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.429</v>
+        <v>-1.542</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.429</v>
+        <v>-1.542</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.6127</v>
+        <v>-1.6643</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.6127</v>
+        <v>-1.6643</v>
       </c>
       <c r="N57" t="n">
         <v>131</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.5086</v>
+        <v>-1.5686</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3887</v>
+        <v>-0.4042</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.3191</v>
+        <v>-1.3383</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.5086</v>
+        <v>-1.5686</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.5086</v>
+        <v>-1.5686</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.5086</v>
+        <v>-1.5686</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.5086</v>
+        <v>-1.5686</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.5086</v>
+        <v>-1.5686</v>
       </c>
       <c r="N58" t="n">
         <v>125</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.6163</v>
+        <v>-1.6956</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.4164</v>
+        <v>-0.4369</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.3677</v>
+        <v>-1.3961</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.6163</v>
+        <v>-1.6956</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.6163</v>
+        <v>-1.6956</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.6163</v>
+        <v>-1.6956</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.2312</v>
+        <v>-2.0784</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-2.2312</v>
+        <v>-2.0784</v>
       </c>
       <c r="N59" t="n">
         <v>280</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.7195</v>
+        <v>-1.7896</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.443</v>
+        <v>-0.4611</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.4143</v>
+        <v>-1.4389</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.7195</v>
+        <v>-1.7896</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.7195</v>
+        <v>-1.7896</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.7195</v>
+        <v>-1.7896</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.9405</v>
+        <v>-1.9315</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.9405</v>
+        <v>-1.9315</v>
       </c>
       <c r="N60" t="n">
         <v>131</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.8308</v>
+        <v>-1.9201</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4717</v>
+        <v>-0.4947</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.4645</v>
+        <v>-1.4983</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.8308</v>
+        <v>-1.9201</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.8308</v>
+        <v>-1.9201</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.8308</v>
+        <v>-1.9201</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.4276</v>
+        <v>-2.2944</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.4276</v>
+        <v>-2.2944</v>
       </c>
       <c r="N61" t="n">
         <v>251</v>
@@ -3349,10 +3349,10 @@
         <v>1.23</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4568</v>
+        <v>0.4392</v>
       </c>
       <c r="J2" t="n">
-        <v>10.5064</v>
+        <v>10.1016</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.224</v>
+        <v>-0.2429</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.152</v>
+        <v>-5.5867</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3183</v>
+        <v>-0.3354</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.3209</v>
+        <v>-7.7142</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>0.65</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3561</v>
+        <v>-0.3718</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.190300000000001</v>
+        <v>-8.551399999999999</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4216</v>
+        <v>-0.4343</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.6968</v>
+        <v>-9.988899999999999</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8842</v>
       </c>
       <c r="J7" t="n">
-        <v>20.6471</v>
+        <v>20.3366</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.44</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5311</v>
+        <v>0.5433</v>
       </c>
       <c r="J8" t="n">
-        <v>12.2153</v>
+        <v>12.4959</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>1.37</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4584</v>
+        <v>0.4738</v>
       </c>
       <c r="J9" t="n">
-        <v>10.5432</v>
+        <v>10.8974</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>1.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2632</v>
+        <v>0.2853</v>
       </c>
       <c r="J10" t="n">
-        <v>6.0536</v>
+        <v>6.5619</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.145</v>
+        <v>0.1682</v>
       </c>
       <c r="J11" t="n">
-        <v>3.335</v>
+        <v>3.8686</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.95</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5862</v>
+        <v>1.5913</v>
       </c>
       <c r="J12" t="n">
-        <v>26.9654</v>
+        <v>27.0521</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5315</v>
+        <v>1.5338</v>
       </c>
       <c r="J13" t="n">
-        <v>26.0355</v>
+        <v>26.0746</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.61</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2109</v>
+        <v>1.1917</v>
       </c>
       <c r="J14" t="n">
-        <v>20.5853</v>
+        <v>20.2589</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>1.35</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8265</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>14.0505</v>
+        <v>13.5473</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>1.25</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5984</v>
+        <v>0.5957</v>
       </c>
       <c r="J16" t="n">
-        <v>10.1728</v>
+        <v>10.1269</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>0.87</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0546</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9282</v>
+        <v>-1.5691</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>0.58</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3798</v>
+        <v>-0.4019</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.4566</v>
+        <v>-6.8323</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>0.45</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4983</v>
+        <v>-0.5132</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.4711</v>
+        <v>-8.724399999999999</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>0.43</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5174</v>
+        <v>-0.5309</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.7958</v>
+        <v>-9.0253</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.33</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.615</v>
+        <v>-0.6204</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.455</v>
+        <v>-10.5468</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.55</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1947</v>
+        <v>1.1632</v>
       </c>
       <c r="J22" t="n">
-        <v>26.2834</v>
+        <v>25.5904</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.38</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9579</v>
+        <v>0.9022</v>
       </c>
       <c r="J23" t="n">
-        <v>21.0738</v>
+        <v>19.8484</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.19</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5291</v>
+        <v>0.5187</v>
       </c>
       <c r="J24" t="n">
-        <v>11.6402</v>
+        <v>11.4114</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>0.264</v>
+        <v>0.2769</v>
       </c>
       <c r="J25" t="n">
-        <v>5.808</v>
+        <v>6.0918</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.059</v>
+        <v>-0.0408</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.298</v>
+        <v>-0.8976</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>0.97</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0031</v>
+        <v>-0.0217</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0682</v>
+        <v>-0.4774</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1299</v>
+        <v>-0.1517</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.8578</v>
+        <v>-3.3374</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>0.8</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2054</v>
+        <v>-0.2265</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.5188</v>
+        <v>-4.983</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4309</v>
+        <v>-0.4445</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.479799999999999</v>
+        <v>-9.779</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.1418</v>
+        <v>-12.276</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.79</v>
       </c>
       <c r="I32" t="n">
-        <v>1.483</v>
+        <v>1.4696</v>
       </c>
       <c r="J32" t="n">
-        <v>34.109</v>
+        <v>33.8008</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.23</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6212</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>14.2876</v>
+        <v>13.8529</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>1.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5737</v>
+        <v>0.5597</v>
       </c>
       <c r="J34" t="n">
-        <v>13.1951</v>
+        <v>12.8731</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>1.2</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5495</v>
+        <v>0.538</v>
       </c>
       <c r="J35" t="n">
-        <v>12.6385</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4754</v>
+        <v>-0.4428</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.9342</v>
+        <v>-10.1844</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>0.87</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1382</v>
+        <v>-0.1582</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.1786</v>
+        <v>-3.6386</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1812</v>
+        <v>-0.2011</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.1676</v>
+        <v>-4.6253</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2017</v>
+        <v>-0.2214</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.6391</v>
+        <v>-5.0922</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.67</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3337</v>
+        <v>-0.3509</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.6751</v>
+        <v>-8.0707</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.64</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3619</v>
+        <v>-0.378</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.323700000000001</v>
+        <v>-8.694000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.41</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0395</v>
+        <v>0.984</v>
       </c>
       <c r="J42" t="n">
-        <v>28.0665</v>
+        <v>26.568</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.34</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9082</v>
+        <v>0.8495</v>
       </c>
       <c r="J43" t="n">
-        <v>24.5214</v>
+        <v>22.9365</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2896</v>
+        <v>0.2946</v>
       </c>
       <c r="J44" t="n">
-        <v>7.8192</v>
+        <v>7.9542</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2608</v>
+        <v>0.2677</v>
       </c>
       <c r="J45" t="n">
-        <v>7.0416</v>
+        <v>7.2279</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.74</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8104</v>
+        <v>-0.7478</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.8808</v>
+        <v>-20.1906</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9436</v>
       </c>
       <c r="J47" t="n">
-        <v>26.9865</v>
+        <v>25.4772</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1344</v>
+        <v>0.1378</v>
       </c>
       <c r="J48" t="n">
-        <v>3.6288</v>
+        <v>3.7206</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.82</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2098</v>
+        <v>-0.2253</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.6646</v>
+        <v>-6.0831</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2198</v>
+        <v>-0.2353</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.9346</v>
+        <v>-6.3531</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.44</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5658</v>
+        <v>-0.5677</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.2766</v>
+        <v>-15.3279</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.4</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0372</v>
+        <v>0.9785</v>
       </c>
       <c r="J52" t="n">
-        <v>36.302</v>
+        <v>34.2475</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7831</v>
+        <v>0.7372</v>
       </c>
       <c r="J53" t="n">
-        <v>27.4085</v>
+        <v>25.802</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5356</v>
+        <v>0.5177</v>
       </c>
       <c r="J54" t="n">
-        <v>18.746</v>
+        <v>18.1195</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.84</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5415</v>
+        <v>-0.5114</v>
       </c>
       <c r="J55" t="n">
-        <v>-18.9525</v>
+        <v>-17.899</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7746</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-27.111</v>
+        <v>-25.137</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5507</v>
+        <v>0.533</v>
       </c>
       <c r="J57" t="n">
-        <v>19.2745</v>
+        <v>18.655</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.198</v>
+        <v>0.202</v>
       </c>
       <c r="J58" t="n">
-        <v>6.93</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>0.9</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1282</v>
+        <v>-0.1423</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.487</v>
+        <v>-4.9805</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>0.77</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2621</v>
+        <v>-0.2765</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.173500000000001</v>
+        <v>-9.6775</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.301</v>
+        <v>-0.3146</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.535</v>
+        <v>-11.011</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.32</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8893</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>24.9004</v>
+        <v>23.1868</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.21</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6198</v>
+        <v>0.5913</v>
       </c>
       <c r="J63" t="n">
-        <v>17.3544</v>
+        <v>16.5564</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.215</v>
+        <v>-0.2125</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.02</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2471</v>
+        <v>-0.2429</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.9188</v>
+        <v>-6.8012</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3385</v>
+        <v>-0.3282</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.478</v>
+        <v>-9.1896</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.75</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1845</v>
+        <v>1.163</v>
       </c>
       <c r="J67" t="n">
-        <v>33.166</v>
+        <v>32.564</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1299</v>
+        <v>0.1412</v>
       </c>
       <c r="J68" t="n">
-        <v>3.6372</v>
+        <v>3.9536</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0572</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>1.6016</v>
+        <v>1.8788</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.95</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0827</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.3156</v>
+        <v>-2.5564</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4717</v>
+        <v>-0.4768</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.2076</v>
+        <v>-13.3504</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0991</v>
+        <v>1.0535</v>
       </c>
       <c r="J72" t="n">
-        <v>46.1622</v>
+        <v>44.247</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.25</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7018</v>
+        <v>0.6672</v>
       </c>
       <c r="J73" t="n">
-        <v>29.4756</v>
+        <v>28.0224</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.06</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2049</v>
+        <v>0.214</v>
       </c>
       <c r="J74" t="n">
-        <v>8.6058</v>
+        <v>8.988</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>0.93</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2915</v>
+        <v>-0.2814</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.243</v>
+        <v>-11.8188</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.88</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4382</v>
+        <v>-0.4167</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.4044</v>
+        <v>-17.5014</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I77" t="n">
-        <v>0.433</v>
+        <v>0.4259</v>
       </c>
       <c r="J77" t="n">
-        <v>18.186</v>
+        <v>17.8878</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1479</v>
+        <v>0.1541</v>
       </c>
       <c r="J78" t="n">
-        <v>6.2118</v>
+        <v>6.4722</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.549</v>
+        <v>-4.0404</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1301</v>
+        <v>-0.1437</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.4642</v>
+        <v>-6.0354</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3032</v>
+        <v>-0.3163</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.7344</v>
+        <v>-13.2846</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.96</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6174</v>
+        <v>1.6206</v>
       </c>
       <c r="J82" t="n">
-        <v>29.1132</v>
+        <v>29.1708</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.7</v>
       </c>
       <c r="I83" t="n">
-        <v>1.3241</v>
+        <v>1.3108</v>
       </c>
       <c r="J83" t="n">
-        <v>23.8338</v>
+        <v>23.5944</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.54</v>
       </c>
       <c r="I84" t="n">
-        <v>1.1395</v>
+        <v>1.1126</v>
       </c>
       <c r="J84" t="n">
-        <v>20.511</v>
+        <v>20.0268</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.19</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4731</v>
+        <v>0.4799</v>
       </c>
       <c r="J85" t="n">
-        <v>8.5158</v>
+        <v>8.638199999999999</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>1.14</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3444</v>
+        <v>0.3634</v>
       </c>
       <c r="J86" t="n">
-        <v>6.1992</v>
+        <v>6.5412</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>0.64</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.3065</v>
+        <v>-0.3351</v>
       </c>
       <c r="J87" t="n">
-        <v>-5.517</v>
+        <v>-6.0318</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.61</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3385</v>
+        <v>-0.3649</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.093</v>
+        <v>-6.5682</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.45</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4903</v>
+        <v>-0.507</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.8254</v>
+        <v>-9.125999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.41</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5286</v>
+        <v>-0.5423</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.514799999999999</v>
+        <v>-9.7614</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.37</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5677</v>
+        <v>-0.5782</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.2186</v>
+        <v>-10.4076</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>2.29</v>
       </c>
       <c r="I92" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J92" t="n">
-        <v>29.3408</v>
+        <v>30.9952</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.8</v>
       </c>
       <c r="I93" t="n">
-        <v>1.4296</v>
+        <v>1.4244</v>
       </c>
       <c r="J93" t="n">
-        <v>22.8736</v>
+        <v>22.7904</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.33</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7927</v>
+        <v>0.7654</v>
       </c>
       <c r="J94" t="n">
-        <v>12.6832</v>
+        <v>12.2464</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.26</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6241</v>
       </c>
       <c r="J95" t="n">
-        <v>10.1216</v>
+        <v>9.9856</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>1.1</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2251</v>
+        <v>0.2561</v>
       </c>
       <c r="J96" t="n">
-        <v>3.6016</v>
+        <v>4.0976</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.04</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2838</v>
+        <v>0.2481</v>
       </c>
       <c r="J97" t="n">
-        <v>4.5408</v>
+        <v>3.9696</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>0.77</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.218</v>
+        <v>-0.2425</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.488</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.59</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3891</v>
+        <v>-0.4074</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.2256</v>
+        <v>-6.5184</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.42</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5487</v>
+        <v>-0.5568</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.779199999999999</v>
+        <v>-8.908799999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.4</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5676</v>
+        <v>-0.5743</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.0816</v>
+        <v>-9.188800000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.72</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3667</v>
+        <v>1.3525</v>
       </c>
       <c r="J102" t="n">
-        <v>27.334</v>
+        <v>27.05</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.4</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9664</v>
+        <v>0.9167</v>
       </c>
       <c r="J103" t="n">
-        <v>19.328</v>
+        <v>18.334</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.4</v>
       </c>
       <c r="I104" t="n">
-        <v>0.9664</v>
+        <v>0.9167</v>
       </c>
       <c r="J104" t="n">
-        <v>19.328</v>
+        <v>18.334</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9295</v>
+        <v>0.881</v>
       </c>
       <c r="J105" t="n">
-        <v>18.59</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1995</v>
+        <v>0.225</v>
       </c>
       <c r="J106" t="n">
-        <v>3.99</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>0.97</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0011</v>
+        <v>-0.0188</v>
       </c>
       <c r="J107" t="n">
-        <v>0.022</v>
+        <v>-0.376</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>0.78</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2235</v>
+        <v>-0.2448</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.47</v>
+        <v>-4.896</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.77</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2335</v>
+        <v>-0.2546</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.67</v>
+        <v>-5.092</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.61</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3822</v>
+        <v>-0.3987</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.644</v>
+        <v>-7.974</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.44</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5409</v>
+        <v>-0.548</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.818</v>
+        <v>-10.96</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.44</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0604</v>
+        <v>1.0137</v>
       </c>
       <c r="J112" t="n">
-        <v>11.6644</v>
+        <v>11.1507</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.36</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9242</v>
+        <v>0.869</v>
       </c>
       <c r="J113" t="n">
-        <v>10.1662</v>
+        <v>9.558999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.24</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6509</v>
+        <v>0.6274</v>
       </c>
       <c r="J114" t="n">
-        <v>7.1599</v>
+        <v>6.9014</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4846</v>
+        <v>0.4775</v>
       </c>
       <c r="J115" t="n">
-        <v>5.3306</v>
+        <v>5.2525</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4923</v>
+        <v>-0.4605</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.4153</v>
+        <v>-5.0655</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4982</v>
+        <v>0.4877</v>
       </c>
       <c r="J117" t="n">
-        <v>5.4802</v>
+        <v>5.3647</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4433</v>
+        <v>0.4371</v>
       </c>
       <c r="J118" t="n">
-        <v>4.8763</v>
+        <v>4.8081</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.16</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3683</v>
+        <v>0.3672</v>
       </c>
       <c r="J119" t="n">
-        <v>4.0513</v>
+        <v>4.0392</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>1.07</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1868</v>
+        <v>0.1939</v>
       </c>
       <c r="J120" t="n">
-        <v>2.0548</v>
+        <v>2.1329</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.27</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7189</v>
+        <v>-0.7099</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.9079</v>
+        <v>-7.8089</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>2.04</v>
       </c>
       <c r="I122" t="n">
-        <v>1.4591</v>
+        <v>1.4582</v>
       </c>
       <c r="J122" t="n">
-        <v>8.7546</v>
+        <v>8.7492</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.12</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2805</v>
+        <v>0.2865</v>
       </c>
       <c r="J123" t="n">
-        <v>1.683</v>
+        <v>1.719</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>0.77</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2715</v>
+        <v>-0.2839</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.629</v>
+        <v>-1.7034</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.74</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3007</v>
+        <v>-0.3125</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.8042</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.45</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5656</v>
+        <v>-0.5663</v>
       </c>
       <c r="J126" t="n">
-        <v>-3.3936</v>
+        <v>-3.3978</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.56</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2216</v>
+        <v>1.1893</v>
       </c>
       <c r="J127" t="n">
-        <v>7.3296</v>
+        <v>7.1358</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.53</v>
       </c>
       <c r="I128" t="n">
-        <v>1.1834</v>
+        <v>1.1485</v>
       </c>
       <c r="J128" t="n">
-        <v>7.1004</v>
+        <v>6.891</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.96</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2135</v>
+        <v>-0.2029</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.281</v>
+        <v>-1.2174</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2791</v>
+        <v>-0.2653</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.6746</v>
+        <v>-1.5918</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2791</v>
+        <v>-0.2653</v>
       </c>
       <c r="J131" t="n">
-        <v>-1.6746</v>
+        <v>-1.5918</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.88</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6333</v>
+        <v>1.6204</v>
       </c>
       <c r="J132" t="n">
-        <v>9.799799999999999</v>
+        <v>9.7224</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6435</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="J133" t="n">
-        <v>3.861</v>
+        <v>3.7044</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>0.96</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2031</v>
+        <v>-0.1956</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.2186</v>
+        <v>-1.1736</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2365</v>
+        <v>-0.2275</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.419</v>
+        <v>-1.365</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.71</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8878</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-5.3268</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.51</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9681</v>
+        <v>0.9157</v>
       </c>
       <c r="J137" t="n">
-        <v>5.8086</v>
+        <v>5.4942</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4413</v>
+        <v>0.4356</v>
       </c>
       <c r="J138" t="n">
-        <v>2.6478</v>
+        <v>2.6136</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.88</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1552</v>
+        <v>-0.1686</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.9312</v>
+        <v>-1.0116</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.77</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2678</v>
+        <v>-0.281</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.6068</v>
+        <v>-1.686</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.6</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4284</v>
+        <v>-0.4366</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.5704</v>
+        <v>-2.6196</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>2.34</v>
       </c>
       <c r="I142" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J142" t="n">
-        <v>11.0028</v>
+        <v>11.6232</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.39</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9627</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>5.7762</v>
+        <v>5.4588</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1901</v>
+        <v>0.2114</v>
       </c>
       <c r="J144" t="n">
-        <v>1.1406</v>
+        <v>1.2684</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0222</v>
+        <v>0.0501</v>
       </c>
       <c r="J145" t="n">
-        <v>0.1332</v>
+        <v>0.3006</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.9458</v>
+        <v>-0.86</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.6748</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.94</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4674</v>
+        <v>1.4539</v>
       </c>
       <c r="J147" t="n">
-        <v>8.804399999999999</v>
+        <v>8.7234</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>0.74</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2781</v>
+        <v>-0.2949</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.6686</v>
+        <v>-1.7694</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.71</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3069</v>
+        <v>-0.3229</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.8414</v>
+        <v>-1.9374</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.43</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5664</v>
+        <v>-0.5695</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.3984</v>
+        <v>-3.417</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.39</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6025</v>
+        <v>-0.6031</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.615</v>
+        <v>-3.6186</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.52</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2895</v>
+        <v>1.2277</v>
       </c>
       <c r="J152" t="n">
-        <v>5.158</v>
+        <v>4.9108</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1125</v>
+        <v>0.0438</v>
       </c>
       <c r="J153" t="n">
-        <v>0.45</v>
+        <v>0.1752</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.16</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.7864</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.1456</v>
+        <v>-3.1028</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.09</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.8563</v>
+        <v>-0.8387</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.4252</v>
+        <v>-3.3548</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.01</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.9366</v>
+        <v>-0.9107</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.7464</v>
+        <v>-3.6428</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>3.46</v>
       </c>
       <c r="I157" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J157" t="n">
-        <v>7.3352</v>
+        <v>7.7488</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.64</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="J158" t="n">
-        <v>4.9164</v>
+        <v>4.8588</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.49</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0532</v>
+        <v>1.022</v>
       </c>
       <c r="J159" t="n">
-        <v>4.2128</v>
+        <v>4.088</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.23</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5184</v>
+        <v>0.5306</v>
       </c>
       <c r="J160" t="n">
-        <v>2.0736</v>
+        <v>2.1224</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.17</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3706</v>
+        <v>0.3977</v>
       </c>
       <c r="J161" t="n">
-        <v>1.4824</v>
+        <v>1.5908</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>2.39</v>
       </c>
       <c r="I162" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J162" t="n">
-        <v>7.3352</v>
+        <v>7.7488</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.92</v>
       </c>
       <c r="I163" t="n">
-        <v>1.5373</v>
+        <v>1.5427</v>
       </c>
       <c r="J163" t="n">
-        <v>6.1492</v>
+        <v>6.1708</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.86</v>
       </c>
       <c r="I164" t="n">
-        <v>1.473</v>
+        <v>1.4747</v>
       </c>
       <c r="J164" t="n">
-        <v>5.892</v>
+        <v>5.8988</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1.28</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6483</v>
+        <v>0.6437</v>
       </c>
       <c r="J165" t="n">
-        <v>2.5932</v>
+        <v>2.5748</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>1.17</v>
       </c>
       <c r="I166" t="n">
-        <v>0.3825</v>
+        <v>0.4062</v>
       </c>
       <c r="J166" t="n">
-        <v>1.53</v>
+        <v>1.6248</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>0.53</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.4007</v>
+        <v>-0.4259</v>
       </c>
       <c r="J167" t="n">
-        <v>-1.6028</v>
+        <v>-1.7036</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>0.52</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.4112</v>
+        <v>-0.4355</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.6448</v>
+        <v>-1.742</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.5</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4316</v>
+        <v>-0.4544</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.7264</v>
+        <v>-1.8176</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.46</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4706</v>
+        <v>-0.4905</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.8824</v>
+        <v>-1.962</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.19</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7403</v>
+        <v>-0.7358</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.9612</v>
+        <v>-2.9432</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.27</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5676</v>
+        <v>0.5517</v>
       </c>
       <c r="J172" t="n">
-        <v>6.8112</v>
+        <v>6.6204</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.18</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4042</v>
+        <v>0.4011</v>
       </c>
       <c r="J173" t="n">
-        <v>4.8504</v>
+        <v>4.8132</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.09</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2278</v>
+        <v>0.2341</v>
       </c>
       <c r="J174" t="n">
-        <v>2.7336</v>
+        <v>2.8092</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1552</v>
+        <v>-0.1686</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.8624</v>
+        <v>-2.0232</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.54</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4828</v>
+        <v>-0.4884</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.7936</v>
+        <v>-5.8608</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.4</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0243</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="J177" t="n">
-        <v>12.2916</v>
+        <v>11.5944</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.35</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9304</v>
+        <v>0.8697</v>
       </c>
       <c r="J178" t="n">
-        <v>11.1648</v>
+        <v>10.4364</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7439</v>
+        <v>0.7055</v>
       </c>
       <c r="J179" t="n">
-        <v>8.9268</v>
+        <v>8.465999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>1.15</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4484</v>
+        <v>0.4412</v>
       </c>
       <c r="J180" t="n">
-        <v>5.3808</v>
+        <v>5.2944</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.49</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.4003</v>
+        <v>-1.256</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.8036</v>
+        <v>-15.072</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>2.69</v>
       </c>
       <c r="I182" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J182" t="n">
-        <v>9.169</v>
+        <v>9.686</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.76</v>
       </c>
       <c r="I183" t="n">
-        <v>1.3906</v>
+        <v>1.3819</v>
       </c>
       <c r="J183" t="n">
-        <v>6.953</v>
+        <v>6.9095</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.47</v>
       </c>
       <c r="I184" t="n">
-        <v>1.0575</v>
+        <v>1.0201</v>
       </c>
       <c r="J184" t="n">
-        <v>5.2875</v>
+        <v>5.1005</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.91</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4415</v>
+        <v>-0.4006</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.2075</v>
+        <v>-2.003</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.7582</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.186</v>
+        <v>-3.791</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.66</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1622</v>
+        <v>1.129</v>
       </c>
       <c r="J187" t="n">
-        <v>5.811</v>
+        <v>5.645</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0196</v>
+        <v>0.0141</v>
       </c>
       <c r="J188" t="n">
-        <v>0.098</v>
+        <v>0.07049999999999999</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.103</v>
+        <v>-0.117</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.515</v>
+        <v>-0.585</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.48</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5279</v>
+        <v>-0.5324</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.6395</v>
+        <v>-2.662</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.46</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.5493</v>
       </c>
       <c r="J191" t="n">
-        <v>-2.7295</v>
+        <v>-2.7465</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.38</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9712</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J192" t="n">
-        <v>16.5104</v>
+        <v>15.5176</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.27</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7256</v>
+        <v>0.6928</v>
       </c>
       <c r="J193" t="n">
-        <v>12.3352</v>
+        <v>11.7776</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.7023</v>
+        <v>0.6721</v>
       </c>
       <c r="J194" t="n">
-        <v>11.9391</v>
+        <v>11.4257</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2754</v>
+        <v>0.2848</v>
       </c>
       <c r="J195" t="n">
-        <v>4.6818</v>
+        <v>4.8416</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1805</v>
+        <v>-0.1705</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.0685</v>
+        <v>-2.8985</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.03</v>
       </c>
       <c r="I197" t="n">
-        <v>0.128</v>
+        <v>0.1262</v>
       </c>
       <c r="J197" t="n">
-        <v>2.176</v>
+        <v>2.1454</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>0.9</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1212</v>
+        <v>-0.137</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.0604</v>
+        <v>-2.329</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>0.83</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1928</v>
+        <v>-0.2099</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.2776</v>
+        <v>-3.5683</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.79</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2325</v>
+        <v>-0.2495</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.9525</v>
+        <v>-4.2415</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.78</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2423</v>
+        <v>-0.2592</v>
       </c>
       <c r="J201" t="n">
-        <v>-4.1191</v>
+        <v>-4.4064</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.78</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4629</v>
+        <v>1.4498</v>
       </c>
       <c r="J202" t="n">
-        <v>8.7774</v>
+        <v>8.6988</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.48</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0969</v>
+        <v>1.0595</v>
       </c>
       <c r="J203" t="n">
-        <v>6.5814</v>
+        <v>6.357</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.31</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="J204" t="n">
-        <v>4.7754</v>
+        <v>4.554</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.15</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4172</v>
+        <v>0.4199</v>
       </c>
       <c r="J205" t="n">
-        <v>2.5032</v>
+        <v>2.5194</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8704</v>
+        <v>-0.7944</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.2224</v>
+        <v>-4.7664</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4845</v>
       </c>
       <c r="J207" t="n">
-        <v>3.0456</v>
+        <v>2.907</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>1.05</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1892</v>
+        <v>0.1843</v>
       </c>
       <c r="J208" t="n">
-        <v>1.1352</v>
+        <v>1.1058</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0702</v>
+        <v>-0.0853</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.4212</v>
+        <v>-0.5118</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.63</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.382</v>
+        <v>-0.3953</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.292</v>
+        <v>-2.3718</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.37</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.62</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.72</v>
+        <v>-3.717</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.3</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6451</v>
+        <v>0.618</v>
       </c>
       <c r="J212" t="n">
-        <v>19.353</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2654</v>
+        <v>0.2663</v>
       </c>
       <c r="J213" t="n">
-        <v>7.962</v>
+        <v>7.989</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0706</v>
+        <v>-0.082</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.118</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.7</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3285</v>
+        <v>-0.3416</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.855</v>
+        <v>-10.248</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4035</v>
+        <v>-0.4139</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.105</v>
+        <v>-12.417</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8773</v>
+        <v>0.8236</v>
       </c>
       <c r="J217" t="n">
-        <v>26.319</v>
+        <v>24.708</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.29</v>
       </c>
       <c r="I218" t="n">
-        <v>0.784</v>
+        <v>0.7421</v>
       </c>
       <c r="J218" t="n">
-        <v>23.52</v>
+        <v>22.263</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.17</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4946</v>
+        <v>0.4842</v>
       </c>
       <c r="J219" t="n">
-        <v>14.838</v>
+        <v>14.526</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4699</v>
+        <v>0.4617</v>
       </c>
       <c r="J220" t="n">
-        <v>14.097</v>
+        <v>13.851</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6117</v>
+        <v>-0.5709</v>
       </c>
       <c r="J221" t="n">
-        <v>-18.351</v>
+        <v>-17.127</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.88</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6149</v>
+        <v>1.6039</v>
       </c>
       <c r="J222" t="n">
-        <v>9.689399999999999</v>
+        <v>9.6234</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8874</v>
+        <v>0.8348</v>
       </c>
       <c r="J223" t="n">
-        <v>5.3244</v>
+        <v>5.0088</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7262</v>
+        <v>0.6932</v>
       </c>
       <c r="J224" t="n">
-        <v>4.3572</v>
+        <v>4.1592</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5611</v>
+        <v>0.5458</v>
       </c>
       <c r="J225" t="n">
-        <v>3.3666</v>
+        <v>3.2748</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.27</v>
       </c>
       <c r="I226" t="n">
-        <v>-1.8928</v>
+        <v>-1.6696</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.3568</v>
+        <v>-10.0176</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.89</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2962</v>
+        <v>1.2866</v>
       </c>
       <c r="J227" t="n">
-        <v>7.7772</v>
+        <v>7.7196</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.37</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6778</v>
       </c>
       <c r="J228" t="n">
-        <v>4.1946</v>
+        <v>4.0668</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>1.19</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3932</v>
+        <v>0.3969</v>
       </c>
       <c r="J229" t="n">
-        <v>2.3592</v>
+        <v>2.3814</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.63</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4119</v>
+        <v>-0.4189</v>
       </c>
       <c r="J230" t="n">
-        <v>-2.4714</v>
+        <v>-2.5134</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.44</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5803</v>
+        <v>-0.5792</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.4818</v>
+        <v>-3.4752</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6086</v>
+        <v>1.6037</v>
       </c>
       <c r="J232" t="n">
-        <v>33.7806</v>
+        <v>33.6777</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.35</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8784</v>
+        <v>0.8326</v>
       </c>
       <c r="J233" t="n">
-        <v>18.4464</v>
+        <v>17.4846</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>1.2</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5381</v>
+        <v>0.5302</v>
       </c>
       <c r="J234" t="n">
-        <v>11.3001</v>
+        <v>11.1342</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>1.07</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1873</v>
+        <v>0.2094</v>
       </c>
       <c r="J235" t="n">
-        <v>3.9333</v>
+        <v>4.3974</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1246</v>
+        <v>0.1501</v>
       </c>
       <c r="J236" t="n">
-        <v>2.6166</v>
+        <v>3.1521</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>0.93</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.0417</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.8757</v>
+        <v>-1.3881</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>0.76</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2357</v>
+        <v>-0.2583</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.9497</v>
+        <v>-5.4243</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>0.62</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3664</v>
+        <v>-0.3848</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.6944</v>
+        <v>-8.0808</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.53</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4503</v>
+        <v>-0.4642</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.456300000000001</v>
+        <v>-9.748200000000001</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.53</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4503</v>
+        <v>-0.4642</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.456300000000001</v>
+        <v>-9.748200000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.73</v>
       </c>
       <c r="I242" t="n">
-        <v>1.369</v>
+        <v>1.3567</v>
       </c>
       <c r="J242" t="n">
-        <v>27.38</v>
+        <v>27.134</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.63</v>
       </c>
       <c r="I243" t="n">
-        <v>1.2525</v>
+        <v>1.2325</v>
       </c>
       <c r="J243" t="n">
-        <v>25.05</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>1.42</v>
       </c>
       <c r="I244" t="n">
-        <v>0.9953</v>
+        <v>0.9476</v>
       </c>
       <c r="J244" t="n">
-        <v>19.906</v>
+        <v>18.952</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I245" t="n">
-        <v>0.6784</v>
+        <v>0.6605</v>
       </c>
       <c r="J245" t="n">
-        <v>13.568</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>1.17</v>
       </c>
       <c r="I246" t="n">
-        <v>0.4353</v>
+        <v>0.4432</v>
       </c>
       <c r="J246" t="n">
-        <v>8.706</v>
+        <v>8.864000000000001</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.2771</v>
+        <v>-0.3036</v>
       </c>
       <c r="J247" t="n">
-        <v>-5.542</v>
+        <v>-6.072</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>0.66</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.3081</v>
+        <v>-0.333</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.162</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>0.57</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3947</v>
+        <v>-0.415</v>
       </c>
       <c r="J249" t="n">
-        <v>-7.894</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>0.52</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4385</v>
+        <v>-0.4566</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.77</v>
+        <v>-9.132</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.36</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.591</v>
+        <v>-0.5979</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.82</v>
+        <v>-11.958</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.63</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1748</v>
+        <v>1.1363</v>
       </c>
       <c r="J252" t="n">
-        <v>7.0488</v>
+        <v>6.8178</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0669</v>
+        <v>-0.0828</v>
       </c>
       <c r="J253" t="n">
-        <v>-0.4014</v>
+        <v>-0.4968</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.57</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.4355</v>
+        <v>-0.4467</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.613</v>
+        <v>-2.6802</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.49</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5092</v>
+        <v>-0.5162</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.0552</v>
+        <v>-3.0972</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.47</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5275</v>
+        <v>-0.5334</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.165</v>
+        <v>-3.2004</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.79</v>
       </c>
       <c r="I257" t="n">
-        <v>1.4576</v>
+        <v>1.4471</v>
       </c>
       <c r="J257" t="n">
-        <v>8.7456</v>
+        <v>8.682600000000001</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.62</v>
       </c>
       <c r="I258" t="n">
-        <v>1.256</v>
+        <v>1.2333</v>
       </c>
       <c r="J258" t="n">
-        <v>7.536</v>
+        <v>7.3998</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.42</v>
       </c>
       <c r="I259" t="n">
-        <v>1.0052</v>
+        <v>0.9559</v>
       </c>
       <c r="J259" t="n">
-        <v>6.0312</v>
+        <v>5.7354</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>1.41</v>
       </c>
       <c r="I260" t="n">
-        <v>0.9889</v>
+        <v>0.9385</v>
       </c>
       <c r="J260" t="n">
-        <v>5.9334</v>
+        <v>5.631</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.54</v>
       </c>
       <c r="I261" t="n">
-        <v>-1.3246</v>
+        <v>-1.1862</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.9476</v>
+        <v>-7.1172</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.55</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1995</v>
+        <v>1.1674</v>
       </c>
       <c r="J262" t="n">
-        <v>31.187</v>
+        <v>30.3524</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.33</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8558</v>
+        <v>0.8088</v>
       </c>
       <c r="J263" t="n">
-        <v>22.2508</v>
+        <v>21.0288</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.19</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5329</v>
+        <v>0.5214</v>
       </c>
       <c r="J264" t="n">
-        <v>13.8554</v>
+        <v>13.5564</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.07</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2096</v>
+        <v>0.225</v>
       </c>
       <c r="J265" t="n">
-        <v>5.4496</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.97</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1875</v>
+        <v>-0.1754</v>
       </c>
       <c r="J266" t="n">
-        <v>-4.875</v>
+        <v>-4.5604</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.24</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5682</v>
+        <v>0.5426</v>
       </c>
       <c r="J267" t="n">
-        <v>14.7732</v>
+        <v>14.1076</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.03</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1272</v>
+        <v>0.1257</v>
       </c>
       <c r="J268" t="n">
-        <v>3.3072</v>
+        <v>3.2682</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.79</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2328</v>
+        <v>-0.2497</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.0528</v>
+        <v>-6.4922</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.74</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2816</v>
+        <v>-0.2976</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.3216</v>
+        <v>-7.7376</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.54</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4693</v>
+        <v>-0.4777</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.2018</v>
+        <v>-12.4202</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.18</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4704</v>
+        <v>0.4499</v>
       </c>
       <c r="J272" t="n">
-        <v>12.7008</v>
+        <v>12.1473</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.09</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2831</v>
+        <v>0.2746</v>
       </c>
       <c r="J273" t="n">
-        <v>7.6437</v>
+        <v>7.4142</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>0.86</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1601</v>
+        <v>-0.1776</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.3227</v>
+        <v>-4.7952</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.53</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4743</v>
+        <v>-0.4831</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.8061</v>
+        <v>-13.0437</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.51</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4926</v>
+        <v>-0.5004</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.3002</v>
+        <v>-13.5108</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.32</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8365</v>
+        <v>0.7912</v>
       </c>
       <c r="J277" t="n">
-        <v>22.5855</v>
+        <v>21.3624</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.24</v>
       </c>
       <c r="I278" t="n">
-        <v>0.652</v>
+        <v>0.6282</v>
       </c>
       <c r="J278" t="n">
-        <v>17.604</v>
+        <v>16.9614</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.24</v>
       </c>
       <c r="I279" t="n">
-        <v>0.652</v>
+        <v>0.6282</v>
       </c>
       <c r="J279" t="n">
-        <v>17.604</v>
+        <v>16.9614</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1.21</v>
       </c>
       <c r="I280" t="n">
-        <v>0.5823</v>
+        <v>0.5655</v>
       </c>
       <c r="J280" t="n">
-        <v>15.7221</v>
+        <v>15.2685</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>1.04</v>
       </c>
       <c r="I281" t="n">
-        <v>0.1167</v>
+        <v>0.1361</v>
       </c>
       <c r="J281" t="n">
-        <v>3.1509</v>
+        <v>3.6747</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.62</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2757</v>
+        <v>1.2507</v>
       </c>
       <c r="J282" t="n">
-        <v>33.1682</v>
+        <v>32.5182</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.41</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0059</v>
+        <v>0.9529</v>
       </c>
       <c r="J283" t="n">
-        <v>26.1534</v>
+        <v>24.7754</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.35</v>
       </c>
       <c r="I284" t="n">
-        <v>0.889</v>
+        <v>0.84</v>
       </c>
       <c r="J284" t="n">
-        <v>23.114</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>1.22</v>
       </c>
       <c r="I285" t="n">
-        <v>0.5969</v>
+        <v>0.5807</v>
       </c>
       <c r="J285" t="n">
-        <v>15.5194</v>
+        <v>15.0982</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.73</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8656</v>
+        <v>-0.791</v>
       </c>
       <c r="J286" t="n">
-        <v>-22.5056</v>
+        <v>-20.566</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>0.99</v>
       </c>
       <c r="I287" t="n">
-        <v>0.0158</v>
+        <v>-0.0027</v>
       </c>
       <c r="J287" t="n">
-        <v>0.4108</v>
+        <v>-0.0702</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>0.95</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0505</v>
+        <v>-0.0665</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.313</v>
+        <v>-1.729</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>0.78</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2345</v>
+        <v>-0.2531</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.097</v>
+        <v>-6.5806</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.7</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3108</v>
+        <v>-0.3278</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.0808</v>
+        <v>-8.5228</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.59</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4143</v>
+        <v>-0.427</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.7718</v>
+        <v>-11.102</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.16</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3961</v>
+        <v>0.3876</v>
       </c>
       <c r="J292" t="n">
-        <v>13.8635</v>
+        <v>13.566</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.14</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3564</v>
+        <v>0.3505</v>
       </c>
       <c r="J293" t="n">
-        <v>12.474</v>
+        <v>12.2675</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>0.8</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2279</v>
+        <v>-0.2437</v>
       </c>
       <c r="J294" t="n">
-        <v>-7.9765</v>
+        <v>-8.529500000000001</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.78</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2477</v>
+        <v>-0.2633</v>
       </c>
       <c r="J295" t="n">
-        <v>-8.669499999999999</v>
+        <v>-9.2155</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.66</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3631</v>
+        <v>-0.3756</v>
       </c>
       <c r="J296" t="n">
-        <v>-12.7085</v>
+        <v>-13.146</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.58</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2425</v>
+        <v>1.2123</v>
       </c>
       <c r="J297" t="n">
-        <v>43.4875</v>
+        <v>42.4305</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.53</v>
       </c>
       <c r="I298" t="n">
-        <v>1.1792</v>
+        <v>1.1448</v>
       </c>
       <c r="J298" t="n">
-        <v>41.272</v>
+        <v>40.068</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.13</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3843</v>
+        <v>0.3855</v>
       </c>
       <c r="J299" t="n">
-        <v>13.4505</v>
+        <v>13.4925</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.92</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3449</v>
+        <v>-0.3259</v>
       </c>
       <c r="J300" t="n">
-        <v>-12.0715</v>
+        <v>-11.4065</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.85</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5436</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="J301" t="n">
-        <v>-19.026</v>
+        <v>-17.766</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>2.07</v>
       </c>
       <c r="I302" t="n">
-        <v>1.7399</v>
+        <v>1.7486</v>
       </c>
       <c r="J302" t="n">
-        <v>33.0581</v>
+        <v>33.2234</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.9</v>
       </c>
       <c r="I303" t="n">
-        <v>1.5512</v>
+        <v>1.5511</v>
       </c>
       <c r="J303" t="n">
-        <v>29.4728</v>
+        <v>29.4709</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.34</v>
       </c>
       <c r="I304" t="n">
-        <v>0.8254</v>
+        <v>0.7922</v>
       </c>
       <c r="J304" t="n">
-        <v>15.6826</v>
+        <v>15.0518</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>1.22</v>
       </c>
       <c r="I305" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5466</v>
       </c>
       <c r="J305" t="n">
-        <v>10.4101</v>
+        <v>10.3854</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.98</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.211</v>
+        <v>-0.1815</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.009</v>
+        <v>-3.4485</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>0.91</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.011</v>
+        <v>-0.0475</v>
       </c>
       <c r="J307" t="n">
-        <v>-0.209</v>
+        <v>-0.9025</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>0.52</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.4363</v>
+        <v>-0.4549</v>
       </c>
       <c r="J308" t="n">
-        <v>-8.2897</v>
+        <v>-8.6431</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.51</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4454</v>
+        <v>-0.4634</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.4626</v>
+        <v>-8.804600000000001</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.46</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4922</v>
+        <v>-0.5071</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.351800000000001</v>
+        <v>-9.6349</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.34</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6082</v>
+        <v>-0.6139</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.5558</v>
+        <v>-11.6641</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.48</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J312" t="n">
-        <v>27.081</v>
+        <v>25.692</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5341</v>
+        <v>0.524</v>
       </c>
       <c r="J313" t="n">
-        <v>16.023</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.99</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.0238</v>
+        <v>-0.0277</v>
       </c>
       <c r="J314" t="n">
-        <v>-0.714</v>
+        <v>-0.831</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.84</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2027</v>
+        <v>-0.2153</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.081</v>
+        <v>-6.459</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.62</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4148</v>
+        <v>-0.4227</v>
       </c>
       <c r="J316" t="n">
-        <v>-12.444</v>
+        <v>-12.681</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.42</v>
       </c>
       <c r="I317" t="n">
-        <v>1.1022</v>
+        <v>1.0484</v>
       </c>
       <c r="J317" t="n">
-        <v>33.066</v>
+        <v>31.452</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>0.98</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0905</v>
+        <v>-0.0974</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.715</v>
+        <v>-2.922</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>0.98</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0905</v>
+        <v>-0.0974</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.715</v>
+        <v>-2.922</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.85</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4836</v>
+        <v>-0.4655</v>
       </c>
       <c r="J320" t="n">
-        <v>-14.508</v>
+        <v>-13.965</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8937</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="J321" t="n">
-        <v>-26.811</v>
+        <v>-24.813</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.19</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4508</v>
+        <v>0.439</v>
       </c>
       <c r="J322" t="n">
-        <v>12.1716</v>
+        <v>11.853</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.07</v>
       </c>
       <c r="I323" t="n">
-        <v>0.2066</v>
+        <v>0.2083</v>
       </c>
       <c r="J323" t="n">
-        <v>5.5782</v>
+        <v>5.6241</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>0.99</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.0124</v>
+        <v>-0.019</v>
       </c>
       <c r="J324" t="n">
-        <v>-0.3348</v>
+        <v>-0.513</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.77</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2586</v>
+        <v>-0.2738</v>
       </c>
       <c r="J325" t="n">
-        <v>-6.9822</v>
+        <v>-7.3926</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4567</v>
+        <v>-0.4649</v>
       </c>
       <c r="J326" t="n">
-        <v>-12.3309</v>
+        <v>-12.5523</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.47</v>
       </c>
       <c r="I327" t="n">
-        <v>1.1011</v>
+        <v>1.0606</v>
       </c>
       <c r="J327" t="n">
-        <v>29.7297</v>
+        <v>28.6362</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.4</v>
       </c>
       <c r="I328" t="n">
-        <v>1.0031</v>
+        <v>0.947</v>
       </c>
       <c r="J328" t="n">
-        <v>27.0837</v>
+        <v>25.569</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>1.26</v>
       </c>
       <c r="I329" t="n">
-        <v>0.699</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J329" t="n">
-        <v>18.873</v>
+        <v>18.0873</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>1.13</v>
       </c>
       <c r="I330" t="n">
-        <v>0.3829</v>
+        <v>0.3846</v>
       </c>
       <c r="J330" t="n">
-        <v>10.3383</v>
+        <v>10.3842</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.78</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7282</v>
+        <v>-0.6721</v>
       </c>
       <c r="J331" t="n">
-        <v>-19.6614</v>
+        <v>-18.1467</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.23</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6838</v>
+        <v>0.6455</v>
       </c>
       <c r="J332" t="n">
-        <v>24.6168</v>
+        <v>23.238</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.14</v>
       </c>
       <c r="I333" t="n">
-        <v>0.4493</v>
+        <v>0.436</v>
       </c>
       <c r="J333" t="n">
-        <v>16.1748</v>
+        <v>15.696</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>1.1</v>
       </c>
       <c r="I334" t="n">
-        <v>0.3384</v>
+        <v>0.3348</v>
       </c>
       <c r="J334" t="n">
-        <v>12.1824</v>
+        <v>12.0528</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>1.02</v>
       </c>
       <c r="I335" t="n">
-        <v>0.0882</v>
+        <v>0.0959</v>
       </c>
       <c r="J335" t="n">
-        <v>3.1752</v>
+        <v>3.4524</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.67</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.9562</v>
+        <v>-0.879</v>
       </c>
       <c r="J336" t="n">
-        <v>-34.4232</v>
+        <v>-31.644</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.5</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9106</v>
+        <v>0.8672</v>
       </c>
       <c r="J337" t="n">
-        <v>32.7816</v>
+        <v>31.2192</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.1</v>
       </c>
       <c r="I338" t="n">
-        <v>0.2285</v>
+        <v>0.2396</v>
       </c>
       <c r="J338" t="n">
-        <v>8.226000000000001</v>
+        <v>8.6256</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.01</v>
       </c>
       <c r="I339" t="n">
-        <v>0.0232</v>
+        <v>0.033</v>
       </c>
       <c r="J339" t="n">
-        <v>0.8352000000000001</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.01</v>
       </c>
       <c r="I340" t="n">
-        <v>0.0232</v>
+        <v>0.033</v>
       </c>
       <c r="J340" t="n">
-        <v>0.8352000000000001</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.86</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.1881</v>
+        <v>-0.1992</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.7716</v>
+        <v>-7.1712</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.65</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3193</v>
+        <v>1.2958</v>
       </c>
       <c r="J342" t="n">
-        <v>31.6632</v>
+        <v>31.0992</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.23</v>
       </c>
       <c r="I343" t="n">
-        <v>0.6248</v>
+        <v>0.6047</v>
       </c>
       <c r="J343" t="n">
-        <v>14.9952</v>
+        <v>14.5128</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.23</v>
       </c>
       <c r="I344" t="n">
-        <v>0.6248</v>
+        <v>0.6047</v>
       </c>
       <c r="J344" t="n">
-        <v>14.9952</v>
+        <v>14.5128</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>1.22</v>
       </c>
       <c r="I345" t="n">
-        <v>0.6015</v>
+        <v>0.5838</v>
       </c>
       <c r="J345" t="n">
-        <v>14.436</v>
+        <v>14.0112</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.87</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4981</v>
+        <v>-0.4645</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.9544</v>
+        <v>-11.148</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.21</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5229</v>
       </c>
       <c r="J347" t="n">
-        <v>13.3176</v>
+        <v>12.5496</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>0.86</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1542</v>
+        <v>-0.1731</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.7008</v>
+        <v>-4.1544</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2054</v>
+        <v>-0.2243</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.9296</v>
+        <v>-5.3832</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.64</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3661</v>
+        <v>-0.3812</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.7864</v>
+        <v>-9.1488</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.44</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5515</v>
+        <v>-0.5563</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.236</v>
+        <v>-13.3512</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.02</v>
       </c>
       <c r="I352" t="n">
-        <v>0.0737</v>
+        <v>0.0789</v>
       </c>
       <c r="J352" t="n">
-        <v>3.0954</v>
+        <v>3.3138</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>0.98</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.0332</v>
+        <v>-0.0406</v>
       </c>
       <c r="J353" t="n">
-        <v>-1.3944</v>
+        <v>-1.7052</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>0.96</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.0601</v>
+        <v>-0.0701</v>
       </c>
       <c r="J354" t="n">
-        <v>-2.5242</v>
+        <v>-2.9442</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>0.93</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.096</v>
+        <v>-0.1084</v>
       </c>
       <c r="J355" t="n">
-        <v>-4.032</v>
+        <v>-4.5528</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.91</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.1188</v>
+        <v>-0.1321</v>
       </c>
       <c r="J356" t="n">
-        <v>-4.9896</v>
+        <v>-5.5482</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.22</v>
       </c>
       <c r="I357" t="n">
-        <v>0.6434</v>
+        <v>0.6126</v>
       </c>
       <c r="J357" t="n">
-        <v>27.0228</v>
+        <v>25.7292</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.17</v>
       </c>
       <c r="I358" t="n">
-        <v>0.5161</v>
+        <v>0.4989</v>
       </c>
       <c r="J358" t="n">
-        <v>21.6762</v>
+        <v>20.9538</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.11</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3561</v>
+        <v>0.3534</v>
       </c>
       <c r="J359" t="n">
-        <v>14.9562</v>
+        <v>14.8428</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.96</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1828</v>
+        <v>-0.1815</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.6776</v>
+        <v>-7.623</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.89</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3976</v>
+        <v>-0.3823</v>
       </c>
       <c r="J361" t="n">
-        <v>-16.6992</v>
+        <v>-16.0566</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.28</v>
       </c>
       <c r="I362" t="n">
-        <v>0.7511</v>
+        <v>0.7149</v>
       </c>
       <c r="J362" t="n">
-        <v>22.533</v>
+        <v>21.447</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.28</v>
       </c>
       <c r="I363" t="n">
-        <v>0.7511</v>
+        <v>0.7149</v>
       </c>
       <c r="J363" t="n">
-        <v>22.533</v>
+        <v>21.447</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>1.21</v>
       </c>
       <c r="I364" t="n">
-        <v>0.5859</v>
+        <v>0.5679</v>
       </c>
       <c r="J364" t="n">
-        <v>17.577</v>
+        <v>17.037</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>1.17</v>
       </c>
       <c r="I365" t="n">
-        <v>0.4902</v>
+        <v>0.4813</v>
       </c>
       <c r="J365" t="n">
-        <v>14.706</v>
+        <v>14.439</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.99</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.1</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J366" t="n">
-        <v>-3</v>
+        <v>-2.727</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.12</v>
       </c>
       <c r="I367" t="n">
-        <v>0.327</v>
+        <v>0.3205</v>
       </c>
       <c r="J367" t="n">
-        <v>9.81</v>
+        <v>9.615</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1</v>
       </c>
       <c r="I368" t="n">
-        <v>0.0268</v>
+        <v>0.0193</v>
       </c>
       <c r="J368" t="n">
-        <v>0.804</v>
+        <v>0.579</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>0.98</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.023</v>
+        <v>-0.0328</v>
       </c>
       <c r="J369" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.984</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.75</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2735</v>
+        <v>-0.2893</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.205</v>
+        <v>-8.679</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.55</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4616</v>
+        <v>-0.4702</v>
       </c>
       <c r="J371" t="n">
-        <v>-13.848</v>
+        <v>-14.106</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.65</v>
       </c>
       <c r="I372" t="n">
-        <v>1.3361</v>
+        <v>1.3107</v>
       </c>
       <c r="J372" t="n">
-        <v>38.7469</v>
+        <v>38.0103</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.17</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4909</v>
+        <v>0.4817</v>
       </c>
       <c r="J373" t="n">
-        <v>14.2361</v>
+        <v>13.9693</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.13</v>
       </c>
       <c r="I374" t="n">
-        <v>0.3886</v>
+        <v>0.3885</v>
       </c>
       <c r="J374" t="n">
-        <v>11.2694</v>
+        <v>11.2665</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>1.02</v>
       </c>
       <c r="I375" t="n">
-        <v>0.0519</v>
+        <v>0.0708</v>
       </c>
       <c r="J375" t="n">
-        <v>1.5051</v>
+        <v>2.0532</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.2781</v>
+        <v>-0.2646</v>
       </c>
       <c r="J376" t="n">
-        <v>-8.0649</v>
+        <v>-7.6734</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.15</v>
       </c>
       <c r="I377" t="n">
-        <v>0.3748</v>
+        <v>0.368</v>
       </c>
       <c r="J377" t="n">
-        <v>10.8692</v>
+        <v>10.672</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>0.96</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.0556</v>
+        <v>-0.0667</v>
       </c>
       <c r="J378" t="n">
-        <v>-1.6124</v>
+        <v>-1.9343</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>0.95</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.0684</v>
+        <v>-0.0803</v>
       </c>
       <c r="J379" t="n">
-        <v>-1.9836</v>
+        <v>-2.3287</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.83</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.1982</v>
+        <v>-0.2141</v>
       </c>
       <c r="J380" t="n">
-        <v>-5.7478</v>
+        <v>-6.2089</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.67</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3541</v>
+        <v>-0.3669</v>
       </c>
       <c r="J381" t="n">
-        <v>-10.2689</v>
+        <v>-10.6401</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.56</v>
       </c>
       <c r="I382" t="n">
-        <v>1.2284</v>
+        <v>1.1953</v>
       </c>
       <c r="J382" t="n">
-        <v>36.852</v>
+        <v>35.859</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.25</v>
       </c>
       <c r="I383" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="J383" t="n">
-        <v>20.61</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.21</v>
       </c>
       <c r="I384" t="n">
-        <v>0.5909</v>
+        <v>0.5714</v>
       </c>
       <c r="J384" t="n">
-        <v>17.727</v>
+        <v>17.142</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.0389</v>
+        <v>-0.0268</v>
       </c>
       <c r="J385" t="n">
-        <v>-1.167</v>
+        <v>-0.804</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.79</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.6916</v>
+        <v>-0.6417</v>
       </c>
       <c r="J386" t="n">
-        <v>-20.748</v>
+        <v>-19.251</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.18</v>
       </c>
       <c r="I387" t="n">
-        <v>0.4419</v>
+        <v>0.4288</v>
       </c>
       <c r="J387" t="n">
-        <v>13.257</v>
+        <v>12.864</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1.09</v>
       </c>
       <c r="I388" t="n">
-        <v>0.2589</v>
+        <v>0.2568</v>
       </c>
       <c r="J388" t="n">
-        <v>7.767</v>
+        <v>7.704</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.85</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.1754</v>
+        <v>-0.1918</v>
       </c>
       <c r="J389" t="n">
-        <v>-5.262</v>
+        <v>-5.754</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3327</v>
+        <v>-0.3466</v>
       </c>
       <c r="J390" t="n">
-        <v>-9.981</v>
+        <v>-10.398</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.65</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.3704</v>
+        <v>-0.383</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.112</v>
+        <v>-11.49</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>2.04</v>
       </c>
       <c r="I392" t="n">
-        <v>1.7196</v>
+        <v>1.7253</v>
       </c>
       <c r="J392" t="n">
-        <v>32.6724</v>
+        <v>32.7807</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.91</v>
       </c>
       <c r="I393" t="n">
-        <v>1.5736</v>
+        <v>1.5727</v>
       </c>
       <c r="J393" t="n">
-        <v>29.8984</v>
+        <v>29.8813</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.21</v>
       </c>
       <c r="I394" t="n">
-        <v>0.5341</v>
+        <v>0.5323</v>
       </c>
       <c r="J394" t="n">
-        <v>10.1479</v>
+        <v>10.1137</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>1.07</v>
       </c>
       <c r="I395" t="n">
-        <v>0.1581</v>
+        <v>0.189</v>
       </c>
       <c r="J395" t="n">
-        <v>3.0039</v>
+        <v>3.591</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>1.02</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.0094</v>
+        <v>0.0279</v>
       </c>
       <c r="J396" t="n">
-        <v>-0.1786</v>
+        <v>0.5301</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>0.95</v>
       </c>
       <c r="I397" t="n">
-        <v>-0.0315</v>
+        <v>-0.0516</v>
       </c>
       <c r="J397" t="n">
-        <v>-0.5985</v>
+        <v>-0.9804</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>0.86</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.1412</v>
+        <v>-0.1629</v>
       </c>
       <c r="J398" t="n">
-        <v>-2.6828</v>
+        <v>-3.0951</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>0.8</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.2054</v>
+        <v>-0.2265</v>
       </c>
       <c r="J399" t="n">
-        <v>-3.9026</v>
+        <v>-4.3035</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.57</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.4215</v>
+        <v>-0.4357</v>
       </c>
       <c r="J400" t="n">
-        <v>-8.0085</v>
+        <v>-8.2783</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.45</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.5334</v>
+        <v>-0.5407</v>
       </c>
       <c r="J401" t="n">
-        <v>-10.1346</v>
+        <v>-10.2733</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.45</v>
       </c>
       <c r="I402" t="n">
-        <v>1.0622</v>
+        <v>1.0184</v>
       </c>
       <c r="J402" t="n">
-        <v>26.555</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.34</v>
       </c>
       <c r="I403" t="n">
-        <v>0.8656</v>
+        <v>0.8196</v>
       </c>
       <c r="J403" t="n">
-        <v>21.64</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.25</v>
       </c>
       <c r="I404" t="n">
-        <v>0.6659</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="J404" t="n">
-        <v>16.6475</v>
+        <v>16.065</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>1.2</v>
       </c>
       <c r="I405" t="n">
-        <v>0.5475</v>
+        <v>0.5366</v>
       </c>
       <c r="J405" t="n">
-        <v>13.6875</v>
+        <v>13.415</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>1.12</v>
       </c>
       <c r="I406" t="n">
-        <v>0.3412</v>
+        <v>0.3497</v>
       </c>
       <c r="J406" t="n">
-        <v>8.529999999999999</v>
+        <v>8.7425</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>0.97</v>
       </c>
       <c r="I407" t="n">
-        <v>-0.0264</v>
+        <v>-0.04</v>
       </c>
       <c r="J407" t="n">
-        <v>-0.66</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>0.86</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.1581</v>
+        <v>-0.176</v>
       </c>
       <c r="J408" t="n">
-        <v>-3.9525</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>0.79</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.2267</v>
+        <v>-0.245</v>
       </c>
       <c r="J409" t="n">
-        <v>-5.6675</v>
+        <v>-6.125</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.77</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.246</v>
+        <v>-0.2641</v>
       </c>
       <c r="J410" t="n">
-        <v>-6.15</v>
+        <v>-6.6025</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.7</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3131</v>
+        <v>-0.3295</v>
       </c>
       <c r="J411" t="n">
-        <v>-7.8275</v>
+        <v>-8.237500000000001</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.4</v>
       </c>
       <c r="I412" t="n">
-        <v>1.0379</v>
+        <v>0.9791</v>
       </c>
       <c r="J412" t="n">
-        <v>30.0991</v>
+        <v>28.3939</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.16</v>
       </c>
       <c r="I413" t="n">
-        <v>0.4847</v>
+        <v>0.4718</v>
       </c>
       <c r="J413" t="n">
-        <v>14.0563</v>
+        <v>13.6822</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.98</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.1156</v>
+        <v>-0.1146</v>
       </c>
       <c r="J414" t="n">
-        <v>-3.3524</v>
+        <v>-3.3234</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.95</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.221</v>
+        <v>-0.2167</v>
       </c>
       <c r="J415" t="n">
-        <v>-6.409</v>
+        <v>-6.2843</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.95</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.221</v>
+        <v>-0.2167</v>
       </c>
       <c r="J416" t="n">
-        <v>-6.409</v>
+        <v>-6.2843</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.35</v>
       </c>
       <c r="I417" t="n">
-        <v>0.7016</v>
+        <v>0.6741</v>
       </c>
       <c r="J417" t="n">
-        <v>20.3464</v>
+        <v>19.5489</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.14</v>
       </c>
       <c r="I418" t="n">
-        <v>0.3246</v>
+        <v>0.3272</v>
       </c>
       <c r="J418" t="n">
-        <v>9.413399999999999</v>
+        <v>9.488799999999999</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>1.1</v>
       </c>
       <c r="I419" t="n">
-        <v>0.2454</v>
+        <v>0.2518</v>
       </c>
       <c r="J419" t="n">
-        <v>7.1166</v>
+        <v>7.3022</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.89</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.1457</v>
+        <v>-0.1586</v>
       </c>
       <c r="J420" t="n">
-        <v>-4.2253</v>
+        <v>-4.5994</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.54</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.484</v>
+        <v>-0.4893</v>
       </c>
       <c r="J421" t="n">
-        <v>-14.036</v>
+        <v>-14.1897</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.22</v>
       </c>
       <c r="I422" t="n">
-        <v>0.4651</v>
+        <v>0.4601</v>
       </c>
       <c r="J422" t="n">
-        <v>12.5577</v>
+        <v>12.4227</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.21</v>
       </c>
       <c r="I423" t="n">
-        <v>0.4471</v>
+        <v>0.4434</v>
       </c>
       <c r="J423" t="n">
-        <v>12.0717</v>
+        <v>11.9718</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.07</v>
       </c>
       <c r="I424" t="n">
-        <v>0.1772</v>
+        <v>0.187</v>
       </c>
       <c r="J424" t="n">
-        <v>4.7844</v>
+        <v>5.049</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>0.95</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0886</v>
       </c>
       <c r="J425" t="n">
-        <v>-2.1384</v>
+        <v>-2.3922</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.71</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.3303</v>
+        <v>-0.3412</v>
       </c>
       <c r="J426" t="n">
-        <v>-8.918100000000001</v>
+        <v>-9.212400000000001</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.26</v>
       </c>
       <c r="I427" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.6915</v>
       </c>
       <c r="J427" t="n">
-        <v>19.7181</v>
+        <v>18.6705</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.24</v>
       </c>
       <c r="I428" t="n">
-        <v>0.6815</v>
+        <v>0.6485</v>
       </c>
       <c r="J428" t="n">
-        <v>18.4005</v>
+        <v>17.5095</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>1.19</v>
       </c>
       <c r="I429" t="n">
-        <v>0.5573</v>
+        <v>0.538</v>
       </c>
       <c r="J429" t="n">
-        <v>15.0471</v>
+        <v>14.526</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>1.1</v>
       </c>
       <c r="I430" t="n">
-        <v>0.3229</v>
+        <v>0.3242</v>
       </c>
       <c r="J430" t="n">
-        <v>8.718299999999999</v>
+        <v>8.753399999999999</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.72</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.8524</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="J431" t="n">
-        <v>-23.0148</v>
+        <v>-21.2166</v>
       </c>
     </row>
     <row r="432">
@@ -20549,10 +20549,10 @@
         <v>1.81</v>
       </c>
       <c r="I432" t="n">
-        <v>1.4887</v>
+        <v>1.4785</v>
       </c>
       <c r="J432" t="n">
-        <v>32.7514</v>
+        <v>32.527</v>
       </c>
     </row>
     <row r="433">
@@ -20589,10 +20589,10 @@
         <v>1.42</v>
       </c>
       <c r="I433" t="n">
-        <v>1.0101</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="J433" t="n">
-        <v>22.2222</v>
+        <v>21.1244</v>
       </c>
     </row>
     <row r="434">
@@ -20629,10 +20629,10 @@
         <v>1.25</v>
       </c>
       <c r="I434" t="n">
-        <v>0.6559</v>
+        <v>0.6357</v>
       </c>
       <c r="J434" t="n">
-        <v>14.4298</v>
+        <v>13.9854</v>
       </c>
     </row>
     <row r="435">
@@ -20669,10 +20669,10 @@
         <v>1.11</v>
       </c>
       <c r="I435" t="n">
-        <v>0.3012</v>
+        <v>0.3157</v>
       </c>
       <c r="J435" t="n">
-        <v>6.6264</v>
+        <v>6.9454</v>
       </c>
     </row>
     <row r="436">
@@ -20709,10 +20709,10 @@
         <v>1.04</v>
       </c>
       <c r="I436" t="n">
-        <v>0.0891</v>
+        <v>0.1168</v>
       </c>
       <c r="J436" t="n">
-        <v>1.9602</v>
+        <v>2.5696</v>
       </c>
     </row>
     <row r="437">
@@ -20749,10 +20749,10 @@
         <v>0.87</v>
       </c>
       <c r="I437" t="n">
-        <v>-0.1211</v>
+        <v>-0.1448</v>
       </c>
       <c r="J437" t="n">
-        <v>-2.6642</v>
+        <v>-3.1856</v>
       </c>
     </row>
     <row r="438">
@@ -20789,10 +20789,10 @@
         <v>0.77</v>
       </c>
       <c r="I438" t="n">
-        <v>-0.2294</v>
+        <v>-0.2513</v>
       </c>
       <c r="J438" t="n">
-        <v>-5.0468</v>
+        <v>-5.5286</v>
       </c>
     </row>
     <row r="439">
@@ -20829,10 +20829,10 @@
         <v>0.72</v>
       </c>
       <c r="I439" t="n">
-        <v>-0.2784</v>
+        <v>-0.2991</v>
       </c>
       <c r="J439" t="n">
-        <v>-6.1248</v>
+        <v>-6.5802</v>
       </c>
     </row>
     <row r="440">
@@ -20869,10 +20869,10 @@
         <v>0.64</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.3507</v>
+        <v>-0.3693</v>
       </c>
       <c r="J440" t="n">
-        <v>-7.7154</v>
+        <v>-8.124599999999999</v>
       </c>
     </row>
     <row r="441">
@@ -20909,10 +20909,10 @@
         <v>0.46</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.5189</v>
+        <v>-0.528</v>
       </c>
       <c r="J441" t="n">
-        <v>-11.4158</v>
+        <v>-11.616</v>
       </c>
     </row>
     <row r="442">
@@ -20949,10 +20949,10 @@
         <v>1.3</v>
       </c>
       <c r="I442" t="n">
-        <v>0.6218</v>
+        <v>0.6008</v>
       </c>
       <c r="J442" t="n">
-        <v>18.0322</v>
+        <v>17.4232</v>
       </c>
     </row>
     <row r="443">
@@ -20989,10 +20989,10 @@
         <v>1.08</v>
       </c>
       <c r="I443" t="n">
-        <v>0.2078</v>
+        <v>0.2145</v>
       </c>
       <c r="J443" t="n">
-        <v>6.0262</v>
+        <v>6.2205</v>
       </c>
     </row>
     <row r="444">
@@ -21029,10 +21029,10 @@
         <v>0.98</v>
       </c>
       <c r="I444" t="n">
-        <v>-0.0351</v>
+        <v>-0.042</v>
       </c>
       <c r="J444" t="n">
-        <v>-1.0179</v>
+        <v>-1.218</v>
       </c>
     </row>
     <row r="445">
@@ -21069,10 +21069,10 @@
         <v>0.93</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.0988</v>
+        <v>-0.1105</v>
       </c>
       <c r="J445" t="n">
-        <v>-2.8652</v>
+        <v>-3.2045</v>
       </c>
     </row>
     <row r="446">
@@ -21109,10 +21109,10 @@
         <v>0.65</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.3818</v>
+        <v>-0.392</v>
       </c>
       <c r="J446" t="n">
-        <v>-11.0722</v>
+        <v>-11.368</v>
       </c>
     </row>
     <row r="447">
@@ -21149,10 +21149,10 @@
         <v>1.5</v>
       </c>
       <c r="I447" t="n">
-        <v>1.1657</v>
+        <v>1.1257</v>
       </c>
       <c r="J447" t="n">
-        <v>33.8053</v>
+        <v>32.6453</v>
       </c>
     </row>
     <row r="448">
@@ -21189,10 +21189,10 @@
         <v>1.14</v>
       </c>
       <c r="I448" t="n">
-        <v>0.4267</v>
+        <v>0.4204</v>
       </c>
       <c r="J448" t="n">
-        <v>12.3743</v>
+        <v>12.1916</v>
       </c>
     </row>
     <row r="449">
@@ -21229,10 +21229,10 @@
         <v>1.08</v>
       </c>
       <c r="I449" t="n">
-        <v>0.2651</v>
+        <v>0.2706</v>
       </c>
       <c r="J449" t="n">
-        <v>7.6879</v>
+        <v>7.8474</v>
       </c>
     </row>
     <row r="450">
@@ -21269,10 +21269,10 @@
         <v>0.96</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.1941</v>
+        <v>-0.1893</v>
       </c>
       <c r="J450" t="n">
-        <v>-5.6289</v>
+        <v>-5.4897</v>
       </c>
     </row>
     <row r="451">
@@ -21309,10 +21309,10 @@
         <v>0.88</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.4376</v>
+        <v>-0.4163</v>
       </c>
       <c r="J451" t="n">
-        <v>-12.6904</v>
+        <v>-12.0727</v>
       </c>
     </row>
     <row r="452">
@@ -21349,10 +21349,10 @@
         <v>1.34</v>
       </c>
       <c r="I452" t="n">
-        <v>0.6972</v>
+        <v>0.668</v>
       </c>
       <c r="J452" t="n">
-        <v>20.916</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="453">
@@ -21389,10 +21389,10 @@
         <v>1.08</v>
       </c>
       <c r="I453" t="n">
-        <v>0.2114</v>
+        <v>0.2171</v>
       </c>
       <c r="J453" t="n">
-        <v>6.342</v>
+        <v>6.513</v>
       </c>
     </row>
     <row r="454">
@@ -21429,10 +21429,10 @@
         <v>1.04</v>
       </c>
       <c r="I454" t="n">
-        <v>0.1215</v>
+        <v>0.1285</v>
       </c>
       <c r="J454" t="n">
-        <v>3.645</v>
+        <v>3.855</v>
       </c>
     </row>
     <row r="455">
@@ -21469,10 +21469,10 @@
         <v>0.72</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.3142</v>
+        <v>-0.3268</v>
       </c>
       <c r="J455" t="n">
-        <v>-9.426</v>
+        <v>-9.804</v>
       </c>
     </row>
     <row r="456">
@@ -21509,10 +21509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.3427</v>
+        <v>-0.3545</v>
       </c>
       <c r="J456" t="n">
-        <v>-10.281</v>
+        <v>-10.635</v>
       </c>
     </row>
     <row r="457">
@@ -21549,10 +21549,10 @@
         <v>1.34</v>
       </c>
       <c r="I457" t="n">
-        <v>0.9301</v>
+        <v>0.8655</v>
       </c>
       <c r="J457" t="n">
-        <v>27.903</v>
+        <v>25.965</v>
       </c>
     </row>
     <row r="458">
@@ -21589,10 +21589,10 @@
         <v>1.19</v>
       </c>
       <c r="I458" t="n">
-        <v>0.5649</v>
+        <v>0.5432</v>
       </c>
       <c r="J458" t="n">
-        <v>16.947</v>
+        <v>16.296</v>
       </c>
     </row>
     <row r="459">
@@ -21629,10 +21629,10 @@
         <v>0.98</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.1129</v>
+        <v>-0.1127</v>
       </c>
       <c r="J459" t="n">
-        <v>-3.387</v>
+        <v>-3.381</v>
       </c>
     </row>
     <row r="460">
@@ -21669,10 +21669,10 @@
         <v>0.96</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.1849</v>
+        <v>-0.183</v>
       </c>
       <c r="J460" t="n">
-        <v>-5.547</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="461">
@@ -21709,10 +21709,10 @@
         <v>0.92</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.3121</v>
+        <v>-0.3029</v>
       </c>
       <c r="J461" t="n">
-        <v>-9.363</v>
+        <v>-9.087</v>
       </c>
     </row>
     <row r="462">
@@ -21749,10 +21749,10 @@
         <v>1.67</v>
       </c>
       <c r="I462" t="n">
-        <v>1.3163</v>
+        <v>1.2974</v>
       </c>
       <c r="J462" t="n">
-        <v>26.326</v>
+        <v>25.948</v>
       </c>
     </row>
     <row r="463">
@@ -21789,10 +21789,10 @@
         <v>1.42</v>
       </c>
       <c r="I463" t="n">
-        <v>1.0055</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="J463" t="n">
-        <v>20.11</v>
+        <v>19.122</v>
       </c>
     </row>
     <row r="464">
@@ -21829,10 +21829,10 @@
         <v>1.31</v>
       </c>
       <c r="I464" t="n">
-        <v>0.787</v>
+        <v>0.753</v>
       </c>
       <c r="J464" t="n">
-        <v>15.74</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="465">
@@ -21869,10 +21869,10 @@
         <v>1.25</v>
       </c>
       <c r="I465" t="n">
-        <v>0.6502</v>
+        <v>0.6318</v>
       </c>
       <c r="J465" t="n">
-        <v>13.004</v>
+        <v>12.636</v>
       </c>
     </row>
     <row r="466">
@@ -21909,10 +21909,10 @@
         <v>1.12</v>
       </c>
       <c r="I466" t="n">
-        <v>0.3225</v>
+        <v>0.3367</v>
       </c>
       <c r="J466" t="n">
-        <v>6.45</v>
+        <v>6.734</v>
       </c>
     </row>
     <row r="467">
@@ -21949,10 +21949,10 @@
         <v>1.16</v>
       </c>
       <c r="I467" t="n">
-        <v>0.48</v>
+        <v>0.4496</v>
       </c>
       <c r="J467" t="n">
-        <v>9.6</v>
+        <v>8.992000000000001</v>
       </c>
     </row>
     <row r="468">
@@ -21989,10 +21989,10 @@
         <v>0.97</v>
       </c>
       <c r="I468" t="n">
-        <v>-0.0106</v>
+        <v>-0.0276</v>
       </c>
       <c r="J468" t="n">
-        <v>-0.212</v>
+        <v>-0.552</v>
       </c>
     </row>
     <row r="469">
@@ -22029,10 +22029,10 @@
         <v>0.72</v>
       </c>
       <c r="I469" t="n">
-        <v>-0.285</v>
+        <v>-0.3041</v>
       </c>
       <c r="J469" t="n">
-        <v>-5.7</v>
+        <v>-6.082</v>
       </c>
     </row>
     <row r="470">
@@ -22069,10 +22069,10 @@
         <v>0.58</v>
       </c>
       <c r="I470" t="n">
-        <v>-0.4162</v>
+        <v>-0.4301</v>
       </c>
       <c r="J470" t="n">
-        <v>-8.324</v>
+        <v>-8.602</v>
       </c>
     </row>
     <row r="471">
@@ -22109,10 +22109,10 @@
         <v>0.33</v>
       </c>
       <c r="I471" t="n">
-        <v>-0.6474</v>
+        <v>-0.6461</v>
       </c>
       <c r="J471" t="n">
-        <v>-12.948</v>
+        <v>-12.922</v>
       </c>
     </row>
     <row r="472">
@@ -22149,10 +22149,10 @@
         <v>1.39</v>
       </c>
       <c r="I472" t="n">
-        <v>1.0144</v>
+        <v>0.9536</v>
       </c>
       <c r="J472" t="n">
-        <v>29.4176</v>
+        <v>27.6544</v>
       </c>
     </row>
     <row r="473">
@@ -22189,10 +22189,10 @@
         <v>1.36</v>
       </c>
       <c r="I473" t="n">
-        <v>0.959</v>
+        <v>0.8955</v>
       </c>
       <c r="J473" t="n">
-        <v>27.811</v>
+        <v>25.9695</v>
       </c>
     </row>
     <row r="474">
@@ -22229,10 +22229,10 @@
         <v>1.16</v>
       </c>
       <c r="I474" t="n">
-        <v>0.4783</v>
+        <v>0.4674</v>
       </c>
       <c r="J474" t="n">
-        <v>13.8707</v>
+        <v>13.5546</v>
       </c>
     </row>
     <row r="475">
@@ -22269,10 +22269,10 @@
         <v>0.91</v>
       </c>
       <c r="I475" t="n">
-        <v>-0.3512</v>
+        <v>-0.3371</v>
       </c>
       <c r="J475" t="n">
-        <v>-10.1848</v>
+        <v>-9.7759</v>
       </c>
     </row>
     <row r="476">
@@ -22309,10 +22309,10 @@
         <v>0.74</v>
       </c>
       <c r="I476" t="n">
-        <v>-0.8054</v>
+        <v>-0.7442</v>
       </c>
       <c r="J476" t="n">
-        <v>-23.3566</v>
+        <v>-21.5818</v>
       </c>
     </row>
     <row r="477">
@@ -22349,10 +22349,10 @@
         <v>1.2</v>
       </c>
       <c r="I477" t="n">
-        <v>0.4406</v>
+        <v>0.4351</v>
       </c>
       <c r="J477" t="n">
-        <v>12.7774</v>
+        <v>12.6179</v>
       </c>
     </row>
     <row r="478">
@@ -22389,10 +22389,10 @@
         <v>1.12</v>
       </c>
       <c r="I478" t="n">
-        <v>0.2882</v>
+        <v>0.2921</v>
       </c>
       <c r="J478" t="n">
-        <v>8.357799999999999</v>
+        <v>8.4709</v>
       </c>
     </row>
     <row r="479">
@@ -22429,10 +22429,10 @@
         <v>0.99</v>
       </c>
       <c r="I479" t="n">
-        <v>-0.0202</v>
+        <v>-0.0249</v>
       </c>
       <c r="J479" t="n">
-        <v>-0.5858</v>
+        <v>-0.7221</v>
       </c>
     </row>
     <row r="480">
@@ -22469,10 +22469,10 @@
         <v>0.91</v>
       </c>
       <c r="I480" t="n">
-        <v>-0.1224</v>
+        <v>-0.1349</v>
       </c>
       <c r="J480" t="n">
-        <v>-3.5496</v>
+        <v>-3.9121</v>
       </c>
     </row>
     <row r="481">
@@ -22509,10 +22509,10 @@
         <v>0.75</v>
       </c>
       <c r="I481" t="n">
-        <v>-0.2876</v>
+        <v>-0.3004</v>
       </c>
       <c r="J481" t="n">
-        <v>-8.340400000000001</v>
+        <v>-8.711600000000001</v>
       </c>
     </row>
     <row r="482">
@@ -22549,10 +22549,10 @@
         <v>1.29</v>
       </c>
       <c r="I482" t="n">
-        <v>0.6028</v>
+        <v>0.5838</v>
       </c>
       <c r="J482" t="n">
-        <v>16.8784</v>
+        <v>16.3464</v>
       </c>
     </row>
     <row r="483">
@@ -22589,10 +22589,10 @@
         <v>1.14</v>
       </c>
       <c r="I483" t="n">
-        <v>0.328</v>
+        <v>0.3297</v>
       </c>
       <c r="J483" t="n">
-        <v>9.183999999999999</v>
+        <v>9.2316</v>
       </c>
     </row>
     <row r="484">
@@ -22629,10 +22629,10 @@
         <v>0.91</v>
       </c>
       <c r="I484" t="n">
-        <v>-0.1222</v>
+        <v>-0.1347</v>
       </c>
       <c r="J484" t="n">
-        <v>-3.4216</v>
+        <v>-3.7716</v>
       </c>
     </row>
     <row r="485">
@@ -22669,10 +22669,10 @@
         <v>0.83</v>
       </c>
       <c r="I485" t="n">
-        <v>-0.2077</v>
+        <v>-0.2215</v>
       </c>
       <c r="J485" t="n">
-        <v>-5.8156</v>
+        <v>-6.202</v>
       </c>
     </row>
     <row r="486">
@@ -22709,10 +22709,10 @@
         <v>0.79</v>
       </c>
       <c r="I486" t="n">
-        <v>-0.2481</v>
+        <v>-0.2616</v>
       </c>
       <c r="J486" t="n">
-        <v>-6.9468</v>
+        <v>-7.3248</v>
       </c>
     </row>
     <row r="487">
@@ -22749,10 +22749,10 @@
         <v>1.52</v>
       </c>
       <c r="I487" t="n">
-        <v>1.2096</v>
+        <v>1.1694</v>
       </c>
       <c r="J487" t="n">
-        <v>33.8688</v>
+        <v>32.7432</v>
       </c>
     </row>
     <row r="488">
@@ -22789,10 +22789,10 @@
         <v>1.14</v>
       </c>
       <c r="I488" t="n">
-        <v>0.4402</v>
+        <v>0.4297</v>
       </c>
       <c r="J488" t="n">
-        <v>12.3256</v>
+        <v>12.0316</v>
       </c>
     </row>
     <row r="489">
@@ -22829,10 +22829,10 @@
         <v>0.9</v>
       </c>
       <c r="I489" t="n">
-        <v>-0.3661</v>
+        <v>-0.3539</v>
       </c>
       <c r="J489" t="n">
-        <v>-10.2508</v>
+        <v>-9.9092</v>
       </c>
     </row>
     <row r="490">
@@ -22869,10 +22869,10 @@
         <v>0.87</v>
       </c>
       <c r="I490" t="n">
-        <v>-0.4511</v>
+        <v>-0.4315</v>
       </c>
       <c r="J490" t="n">
-        <v>-12.6308</v>
+        <v>-12.082</v>
       </c>
     </row>
     <row r="491">
@@ -22909,10 +22909,10 @@
         <v>0.87</v>
       </c>
       <c r="I491" t="n">
-        <v>-0.4511</v>
+        <v>-0.4315</v>
       </c>
       <c r="J491" t="n">
-        <v>-12.6308</v>
+        <v>-12.082</v>
       </c>
     </row>
     <row r="492">
@@ -22949,10 +22949,10 @@
         <v>1.53</v>
       </c>
       <c r="I492" t="n">
-        <v>1.1738</v>
+        <v>1.14</v>
       </c>
       <c r="J492" t="n">
-        <v>31.6926</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="493">
@@ -22989,10 +22989,10 @@
         <v>1.53</v>
       </c>
       <c r="I493" t="n">
-        <v>1.1738</v>
+        <v>1.14</v>
       </c>
       <c r="J493" t="n">
-        <v>31.6926</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="494">
@@ -23029,10 +23029,10 @@
         <v>1.18</v>
       </c>
       <c r="I494" t="n">
-        <v>0.508</v>
+        <v>0.4989</v>
       </c>
       <c r="J494" t="n">
-        <v>13.716</v>
+        <v>13.4703</v>
       </c>
     </row>
     <row r="495">
@@ -23069,10 +23069,10 @@
         <v>1.09</v>
       </c>
       <c r="I495" t="n">
-        <v>0.2683</v>
+        <v>0.2799</v>
       </c>
       <c r="J495" t="n">
-        <v>7.2441</v>
+        <v>7.5573</v>
       </c>
     </row>
     <row r="496">
@@ -23109,10 +23109,10 @@
         <v>0.79</v>
       </c>
       <c r="I496" t="n">
-        <v>-0.7064</v>
+        <v>-0.6521</v>
       </c>
       <c r="J496" t="n">
-        <v>-19.0728</v>
+        <v>-17.6067</v>
       </c>
     </row>
     <row r="497">
@@ -23149,10 +23149,10 @@
         <v>0.95</v>
       </c>
       <c r="I497" t="n">
-        <v>-0.0509</v>
+        <v>-0.0668</v>
       </c>
       <c r="J497" t="n">
-        <v>-1.3743</v>
+        <v>-1.8036</v>
       </c>
     </row>
     <row r="498">
@@ -23189,10 +23189,10 @@
         <v>0.9</v>
       </c>
       <c r="I498" t="n">
-        <v>-0.112</v>
+        <v>-0.1299</v>
       </c>
       <c r="J498" t="n">
-        <v>-3.024</v>
+        <v>-3.5073</v>
       </c>
     </row>
     <row r="499">
@@ -23229,10 +23229,10 @@
         <v>0.79</v>
       </c>
       <c r="I499" t="n">
-        <v>-0.2252</v>
+        <v>-0.2439</v>
       </c>
       <c r="J499" t="n">
-        <v>-6.0804</v>
+        <v>-6.5853</v>
       </c>
     </row>
     <row r="500">
@@ -23269,10 +23269,10 @@
         <v>0.75</v>
       </c>
       <c r="I500" t="n">
-        <v>-0.2634</v>
+        <v>-0.2816</v>
       </c>
       <c r="J500" t="n">
-        <v>-7.1118</v>
+        <v>-7.6032</v>
       </c>
     </row>
     <row r="501">
@@ -23309,10 +23309,10 @@
         <v>0.63</v>
       </c>
       <c r="I501" t="n">
-        <v>-0.3772</v>
+        <v>-0.3916</v>
       </c>
       <c r="J501" t="n">
-        <v>-10.1844</v>
+        <v>-10.5732</v>
       </c>
     </row>
     <row r="502">
@@ -23349,10 +23349,10 @@
         <v>1.39</v>
       </c>
       <c r="I502" t="n">
-        <v>1.0298</v>
+        <v>0.968</v>
       </c>
       <c r="J502" t="n">
-        <v>29.8642</v>
+        <v>28.072</v>
       </c>
     </row>
     <row r="503">
@@ -23389,10 +23389,10 @@
         <v>1.05</v>
       </c>
       <c r="I503" t="n">
-        <v>0.1839</v>
+        <v>0.1912</v>
       </c>
       <c r="J503" t="n">
-        <v>5.3331</v>
+        <v>5.5448</v>
       </c>
     </row>
     <row r="504">
@@ -23429,10 +23429,10 @@
         <v>1.02</v>
       </c>
       <c r="I504" t="n">
-        <v>0.0809</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J504" t="n">
-        <v>2.3461</v>
+        <v>2.6361</v>
       </c>
     </row>
     <row r="505">
@@ -23469,10 +23469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I505" t="n">
-        <v>-0.2471</v>
+        <v>-0.2429</v>
       </c>
       <c r="J505" t="n">
-        <v>-7.1659</v>
+        <v>-7.0441</v>
       </c>
     </row>
     <row r="506">
@@ -23509,10 +23509,10 @@
         <v>0.93</v>
       </c>
       <c r="I506" t="n">
-        <v>-0.2783</v>
+        <v>-0.2722</v>
       </c>
       <c r="J506" t="n">
-        <v>-8.0707</v>
+        <v>-7.8938</v>
       </c>
     </row>
     <row r="507">
@@ -23549,10 +23549,10 @@
         <v>1.07</v>
       </c>
       <c r="I507" t="n">
-        <v>0.1935</v>
+        <v>0.1987</v>
       </c>
       <c r="J507" t="n">
-        <v>5.6115</v>
+        <v>5.7623</v>
       </c>
     </row>
     <row r="508">
@@ -23589,10 +23589,10 @@
         <v>1.06</v>
       </c>
       <c r="I508" t="n">
-        <v>0.1713</v>
+        <v>0.177</v>
       </c>
       <c r="J508" t="n">
-        <v>4.9677</v>
+        <v>5.133</v>
       </c>
     </row>
     <row r="509">
@@ -23629,10 +23629,10 @@
         <v>0.89</v>
       </c>
       <c r="I509" t="n">
-        <v>-0.1408</v>
+        <v>-0.1548</v>
       </c>
       <c r="J509" t="n">
-        <v>-4.0832</v>
+        <v>-4.4892</v>
       </c>
     </row>
     <row r="510">
@@ -23669,10 +23669,10 @@
         <v>0.89</v>
       </c>
       <c r="I510" t="n">
-        <v>-0.1408</v>
+        <v>-0.1548</v>
       </c>
       <c r="J510" t="n">
-        <v>-4.0832</v>
+        <v>-4.4892</v>
       </c>
     </row>
     <row r="511">
@@ -23709,10 +23709,10 @@
         <v>0.89</v>
       </c>
       <c r="I511" t="n">
-        <v>-0.1408</v>
+        <v>-0.1548</v>
       </c>
       <c r="J511" t="n">
-        <v>-4.0832</v>
+        <v>-4.4892</v>
       </c>
     </row>
     <row r="512">
@@ -23749,10 +23749,10 @@
         <v>1.42</v>
       </c>
       <c r="I512" t="n">
-        <v>1.0474</v>
+        <v>0.9948</v>
       </c>
       <c r="J512" t="n">
-        <v>29.3272</v>
+        <v>27.8544</v>
       </c>
     </row>
     <row r="513">
@@ -23789,10 +23789,10 @@
         <v>1.19</v>
       </c>
       <c r="I513" t="n">
-        <v>0.5435</v>
+        <v>0.5285</v>
       </c>
       <c r="J513" t="n">
-        <v>15.218</v>
+        <v>14.798</v>
       </c>
     </row>
     <row r="514">
@@ -23829,10 +23829,10 @@
         <v>1.16</v>
       </c>
       <c r="I514" t="n">
-        <v>0.4696</v>
+        <v>0.4615</v>
       </c>
       <c r="J514" t="n">
-        <v>13.1488</v>
+        <v>12.922</v>
       </c>
     </row>
     <row r="515">
@@ -23869,10 +23869,10 @@
         <v>1.13</v>
       </c>
       <c r="I515" t="n">
-        <v>0.3939</v>
+        <v>0.3921</v>
       </c>
       <c r="J515" t="n">
-        <v>11.0292</v>
+        <v>10.9788</v>
       </c>
     </row>
     <row r="516">
@@ -23909,10 +23909,10 @@
         <v>0.88</v>
       </c>
       <c r="I516" t="n">
-        <v>-0.4493</v>
+        <v>-0.4245</v>
       </c>
       <c r="J516" t="n">
-        <v>-12.5804</v>
+        <v>-11.886</v>
       </c>
     </row>
     <row r="517">
@@ -23949,10 +23949,10 @@
         <v>1.32</v>
       </c>
       <c r="I517" t="n">
-        <v>0.6875</v>
+        <v>0.6552</v>
       </c>
       <c r="J517" t="n">
-        <v>19.25</v>
+        <v>18.3456</v>
       </c>
     </row>
     <row r="518">
@@ -23989,10 +23989,10 @@
         <v>1.14</v>
       </c>
       <c r="I518" t="n">
-        <v>0.3518</v>
+        <v>0.3471</v>
       </c>
       <c r="J518" t="n">
-        <v>9.8504</v>
+        <v>9.7188</v>
       </c>
     </row>
     <row r="519">
@@ -24029,10 +24029,10 @@
         <v>0.78</v>
       </c>
       <c r="I519" t="n">
-        <v>-0.2492</v>
+        <v>-0.2645</v>
       </c>
       <c r="J519" t="n">
-        <v>-6.9776</v>
+        <v>-7.406</v>
       </c>
     </row>
     <row r="520">
@@ -24069,10 +24069,10 @@
         <v>0.7</v>
       </c>
       <c r="I520" t="n">
-        <v>-0.3267</v>
+        <v>-0.3402</v>
       </c>
       <c r="J520" t="n">
-        <v>-9.147600000000001</v>
+        <v>-9.525600000000001</v>
       </c>
     </row>
     <row r="521">
@@ -24109,10 +24109,10 @@
         <v>0.66</v>
       </c>
       <c r="I521" t="n">
-        <v>-0.3646</v>
+        <v>-0.3767</v>
       </c>
       <c r="J521" t="n">
-        <v>-10.2088</v>
+        <v>-10.5476</v>
       </c>
     </row>
     <row r="522">
@@ -24149,10 +24149,10 @@
         <v>0.85</v>
       </c>
       <c r="I522" t="n">
-        <v>-0.1172</v>
+        <v>-0.1464</v>
       </c>
       <c r="J522" t="n">
-        <v>-2.344</v>
+        <v>-2.928</v>
       </c>
     </row>
     <row r="523">
@@ -24189,10 +24189,10 @@
         <v>0.8</v>
       </c>
       <c r="I523" t="n">
-        <v>-0.1749</v>
+        <v>-0.2027</v>
       </c>
       <c r="J523" t="n">
-        <v>-3.498</v>
+        <v>-4.054</v>
       </c>
     </row>
     <row r="524">
@@ -24229,10 +24229,10 @@
         <v>0.76</v>
       </c>
       <c r="I524" t="n">
-        <v>-0.2188</v>
+        <v>-0.2451</v>
       </c>
       <c r="J524" t="n">
-        <v>-4.376</v>
+        <v>-4.902</v>
       </c>
     </row>
     <row r="525">
@@ -24269,10 +24269,10 @@
         <v>0.51</v>
       </c>
       <c r="I525" t="n">
-        <v>-0.4575</v>
+        <v>-0.4728</v>
       </c>
       <c r="J525" t="n">
-        <v>-9.15</v>
+        <v>-9.456</v>
       </c>
     </row>
     <row r="526">
@@ -24309,10 +24309,10 @@
         <v>0.13</v>
       </c>
       <c r="I526" t="n">
-        <v>-0.8212</v>
+        <v>-0.8065</v>
       </c>
       <c r="J526" t="n">
-        <v>-16.424</v>
+        <v>-16.13</v>
       </c>
     </row>
     <row r="527">
@@ -24349,10 +24349,10 @@
         <v>1.91</v>
       </c>
       <c r="I527" t="n">
-        <v>1.5796</v>
+        <v>1.5781</v>
       </c>
       <c r="J527" t="n">
-        <v>31.592</v>
+        <v>31.562</v>
       </c>
     </row>
     <row r="528">
@@ -24389,10 +24389,10 @@
         <v>1.58</v>
       </c>
       <c r="I528" t="n">
-        <v>1.1965</v>
+        <v>1.1719</v>
       </c>
       <c r="J528" t="n">
-        <v>23.93</v>
+        <v>23.438</v>
       </c>
     </row>
     <row r="529">
@@ -24429,10 +24429,10 @@
         <v>1.42</v>
       </c>
       <c r="I529" t="n">
-        <v>0.9972</v>
+        <v>0.9492</v>
       </c>
       <c r="J529" t="n">
-        <v>19.944</v>
+        <v>18.984</v>
       </c>
     </row>
     <row r="530">
@@ -24469,10 +24469,10 @@
         <v>1.11</v>
       </c>
       <c r="I530" t="n">
-        <v>0.2797</v>
+        <v>0.3006</v>
       </c>
       <c r="J530" t="n">
-        <v>5.594</v>
+        <v>6.012</v>
       </c>
     </row>
     <row r="531">
@@ -24509,10 +24509,10 @@
         <v>1.1</v>
       </c>
       <c r="I531" t="n">
-        <v>0.2515</v>
+        <v>0.2747</v>
       </c>
       <c r="J531" t="n">
-        <v>5.03</v>
+        <v>5.494</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6070/event_6070_evp_summary.xlsx
+++ b/database/event/6070/event_6070_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.2999</v>
+        <v>5.1391</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3655</v>
+        <v>1.3241</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7884</v>
+        <v>1.7353</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2999</v>
+        <v>5.1391</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2999</v>
+        <v>5.1391</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8.8748</v>
+        <v>8.827199999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>11.446</v>
+        <v>11.4908</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>11.446</v>
+        <v>11.4908</v>
       </c>
       <c r="N2" t="n">
         <v>249</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.1164</v>
+        <v>4.0109</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0606</v>
+        <v>1.0334</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2497</v>
+        <v>1.2214</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1164</v>
+        <v>4.0109</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1164</v>
+        <v>4.0109</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2845</v>
+        <v>6.2416</v>
       </c>
       <c r="I3" t="n">
-        <v>7.321</v>
+        <v>7.3116</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7.321</v>
+        <v>7.3116</v>
       </c>
       <c r="N3" t="n">
         <v>277</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0339</v>
+        <v>3.9669</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0393</v>
+        <v>1.0221</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2121</v>
+        <v>1.2013</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0339</v>
+        <v>3.9669</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0339</v>
+        <v>3.9669</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.104</v>
+        <v>6.1408</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8724</v>
+        <v>7.9938</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7.8724</v>
+        <v>7.9938</v>
       </c>
       <c r="N4" t="n">
         <v>249</v>
@@ -630,32 +630,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9368</v>
+        <v>3.8674</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0143</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1679</v>
+        <v>1.156</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9368</v>
+        <v>3.8674</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9368</v>
+        <v>3.8674</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.8914</v>
+        <v>5.9129</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0399</v>
+        <v>7.1117</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>7.0399</v>
+        <v>7.1117</v>
       </c>
       <c r="N5" t="n">
         <v>206</v>
@@ -676,32 +676,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9334</v>
+        <v>3.8436</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0135</v>
+        <v>0.9903</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1664</v>
+        <v>1.1452</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9334</v>
+        <v>3.8436</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9334</v>
+        <v>3.8436</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.884</v>
+        <v>5.8583</v>
       </c>
       <c r="I6" t="n">
-        <v>7.031</v>
+        <v>7.046</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.031</v>
+        <v>7.046</v>
       </c>
       <c r="N6" t="n">
         <v>206</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5883</v>
+        <v>3.501</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9245</v>
+        <v>0.902</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0093</v>
+        <v>0.9891</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5883</v>
+        <v>3.501</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5883</v>
+        <v>3.501</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1288</v>
+        <v>5.0731</v>
       </c>
       <c r="I7" t="n">
-        <v>6.1286</v>
+        <v>6.1017</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6.1286</v>
+        <v>6.1017</v>
       </c>
       <c r="N7" t="n">
         <v>206</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4316</v>
+        <v>3.2917</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8842</v>
+        <v>0.8481</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9379</v>
+        <v>0.8937</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4316</v>
+        <v>3.2917</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4316</v>
+        <v>3.2917</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7858</v>
+        <v>4.5935</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7187</v>
+        <v>5.5247</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.7187</v>
+        <v>5.5247</v>
       </c>
       <c r="N8" t="n">
         <v>251</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3747</v>
+        <v>3.2666</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8417</v>
       </c>
       <c r="D9" t="n">
-        <v>0.912</v>
+        <v>0.8823</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3747</v>
+        <v>3.2666</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3747</v>
+        <v>3.2666</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6613</v>
+        <v>4.5361</v>
       </c>
       <c r="I9" t="n">
-        <v>5.43</v>
+        <v>5.3137</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.43</v>
+        <v>5.3137</v>
       </c>
       <c r="N9" t="n">
         <v>277</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1811</v>
+        <v>3.1137</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8196</v>
+        <v>0.8023</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8239</v>
+        <v>0.8127</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1811</v>
+        <v>3.1137</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1811</v>
+        <v>3.1137</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2375</v>
+        <v>4.1856</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4652</v>
+        <v>5.4486</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.4652</v>
+        <v>5.4486</v>
       </c>
       <c r="N10" t="n">
         <v>249</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0648</v>
+        <v>2.9624</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7897</v>
+        <v>0.7633</v>
       </c>
       <c r="D11" t="n">
-        <v>0.771</v>
+        <v>0.7437</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0648</v>
+        <v>2.9624</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0648</v>
+        <v>2.9624</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9829</v>
+        <v>3.8387</v>
       </c>
       <c r="I11" t="n">
-        <v>4.882</v>
+        <v>4.7403</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.882</v>
+        <v>4.7403</v>
       </c>
       <c r="N11" t="n">
         <v>280</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>El1an</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9422</v>
+        <v>2.9026</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7581</v>
+        <v>0.7479</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7151</v>
+        <v>0.7165</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9422</v>
+        <v>2.9026</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9422</v>
+        <v>2.9026</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7145</v>
+        <v>3.7018</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7907</v>
+        <v>4.5713</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.7907</v>
+        <v>4.5713</v>
       </c>
       <c r="N12" t="n">
-        <v>249</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>El1an</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9187</v>
+        <v>2.8762</v>
       </c>
       <c r="C13" t="n">
-        <v>0.752</v>
+        <v>0.7411</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7044</v>
+        <v>0.7045</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9187</v>
+        <v>2.8762</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9187</v>
+        <v>2.8762</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6632</v>
+        <v>3.6413</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4901</v>
+        <v>4.7401</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4901</v>
+        <v>4.7401</v>
       </c>
       <c r="N13" t="n">
-        <v>280</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9019</v>
+        <v>2.8371</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7477</v>
+        <v>0.731</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6968</v>
+        <v>0.6866</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9019</v>
+        <v>2.8371</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9019</v>
+        <v>2.8371</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6264</v>
+        <v>3.5517</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0149</v>
+        <v>3.9469</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.0149</v>
+        <v>3.9469</v>
       </c>
       <c r="N14" t="n">
         <v>166</v>
@@ -1090,139 +1090,139 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X5G7V</t>
+          <t>Forester</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7687</v>
+        <v>2.7056</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7134</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6362</v>
+        <v>0.6267</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7687</v>
+        <v>2.7056</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7687</v>
+        <v>2.7056</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3348</v>
+        <v>3.2504</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6921</v>
+        <v>4.0138</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6921</v>
+        <v>4.0138</v>
       </c>
       <c r="N15" t="n">
-        <v>216</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>X5G7V</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7422</v>
+        <v>2.6949</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7065</v>
+        <v>0.6944</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6241</v>
+        <v>0.6219</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7422</v>
+        <v>2.6949</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7422</v>
+        <v>2.6949</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2769</v>
+        <v>3.2259</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9157</v>
+        <v>3.5847</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9157</v>
+        <v>3.5847</v>
       </c>
       <c r="N16" t="n">
-        <v>251</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Forester</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6989</v>
+        <v>2.688</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6954</v>
+        <v>0.6926</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6044</v>
+        <v>0.6187</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6989</v>
+        <v>2.688</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6989</v>
+        <v>2.688</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1821</v>
+        <v>3.2099</v>
       </c>
       <c r="I17" t="n">
-        <v>3.9004</v>
+        <v>3.8607</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9004</v>
+        <v>3.8607</v>
       </c>
       <c r="N17" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6334</v>
+        <v>2.6046</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6785</v>
+        <v>0.6711</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5746</v>
+        <v>0.5807</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6334</v>
+        <v>2.6046</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6334</v>
+        <v>2.6046</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0389</v>
+        <v>3.0188</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1975</v>
+        <v>3.1823</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1975</v>
+        <v>3.1823</v>
       </c>
       <c r="N18" t="n">
         <v>151</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6263</v>
+        <v>2.5325</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6767</v>
+        <v>0.6525</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5713</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6263</v>
+        <v>2.5325</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6263</v>
+        <v>2.5325</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0232</v>
+        <v>2.8536</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7057</v>
+        <v>3.5239</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7057</v>
+        <v>3.5239</v>
       </c>
       <c r="N19" t="n">
         <v>280</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5277</v>
+        <v>2.505</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6513</v>
+        <v>0.6454</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5265</v>
+        <v>0.5354</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5277</v>
+        <v>2.505</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5277</v>
+        <v>2.505</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8075</v>
+        <v>2.7905</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6209</v>
+        <v>3.6325</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6209</v>
+        <v>3.6325</v>
       </c>
       <c r="N20" t="n">
         <v>249</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.4793</v>
+        <v>2.4742</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6388</v>
+        <v>0.6375</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5044</v>
+        <v>0.5213</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4793</v>
+        <v>2.4742</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4793</v>
+        <v>2.4742</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7016</v>
+        <v>2.7199</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2282</v>
+        <v>3.2713</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2282</v>
+        <v>3.2713</v>
       </c>
       <c r="N21" t="n">
         <v>251</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.326</v>
+        <v>2.145</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5527</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4346</v>
+        <v>0.3714</v>
       </c>
       <c r="E22" t="n">
-        <v>2.326</v>
+        <v>2.145</v>
       </c>
       <c r="F22" t="n">
-        <v>2.326</v>
+        <v>2.145</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.366</v>
+        <v>2.145</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6195</v>
+        <v>2.3836</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.6195</v>
+        <v>2.3836</v>
       </c>
       <c r="N22" t="n">
         <v>166</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1878</v>
+        <v>2.1046</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5637</v>
+        <v>0.5423</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3717</v>
+        <v>0.353</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1878</v>
+        <v>2.1046</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1878</v>
+        <v>2.1046</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1878</v>
+        <v>2.1046</v>
       </c>
       <c r="I23" t="n">
-        <v>2.6143</v>
+        <v>2.5312</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.6143</v>
+        <v>2.5312</v>
       </c>
       <c r="N23" t="n">
         <v>206</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9041</v>
+        <v>1.9368</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4906</v>
+        <v>0.499</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2426</v>
+        <v>0.2765</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9041</v>
+        <v>1.9368</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9041</v>
+        <v>1.9368</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9041</v>
+        <v>1.9368</v>
       </c>
       <c r="I24" t="n">
-        <v>2.0551</v>
+        <v>2.0963</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.0551</v>
+        <v>2.0963</v>
       </c>
       <c r="N24" t="n">
         <v>131</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8908</v>
+        <v>1.8167</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4872</v>
+        <v>0.4681</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2365</v>
+        <v>0.2218</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8908</v>
+        <v>1.8167</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8908</v>
+        <v>1.8167</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8908</v>
+        <v>1.8167</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9395</v>
+        <v>1.8653</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9395</v>
+        <v>1.8653</v>
       </c>
       <c r="N25" t="n">
         <v>157</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.561</v>
+        <v>1.5402</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4022</v>
+        <v>0.3968</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0864</v>
+        <v>0.0958</v>
       </c>
       <c r="E26" t="n">
-        <v>1.561</v>
+        <v>1.5402</v>
       </c>
       <c r="F26" t="n">
-        <v>1.561</v>
+        <v>1.5402</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.561</v>
+        <v>1.5402</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6425</v>
+        <v>1.6236</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6425</v>
+        <v>1.6236</v>
       </c>
       <c r="N26" t="n">
         <v>151</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3571</v>
+        <v>1.3576</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3497</v>
+        <v>0.3498</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0064</v>
+        <v>0.0127</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3571</v>
+        <v>1.3576</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3571</v>
+        <v>1.3576</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3571</v>
+        <v>1.3576</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6217</v>
+        <v>1.6328</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6217</v>
+        <v>1.6328</v>
       </c>
       <c r="N27" t="n">
         <v>206</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3151</v>
+        <v>1.3101</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3388</v>
+        <v>0.3376</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0255</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3151</v>
+        <v>1.3101</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3151</v>
+        <v>1.3101</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3151</v>
+        <v>1.3101</v>
       </c>
       <c r="I28" t="n">
-        <v>1.349</v>
+        <v>1.381</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.349</v>
+        <v>1.381</v>
       </c>
       <c r="N28" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3024</v>
+        <v>1.1063</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3356</v>
+        <v>0.285</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0313</v>
+        <v>-0.1018</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3024</v>
+        <v>1.1063</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3024</v>
+        <v>1.1063</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3024</v>
+        <v>1.1063</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3704</v>
+        <v>1.1359</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3704</v>
+        <v>1.1359</v>
       </c>
       <c r="N29" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1909</v>
+        <v>1.0516</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3068</v>
+        <v>0.2709</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.1267</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1909</v>
+        <v>1.0516</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1909</v>
+        <v>1.0516</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1909</v>
+        <v>1.0516</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2531</v>
+        <v>1.1086</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2531</v>
+        <v>1.1086</v>
       </c>
       <c r="N30" t="n">
         <v>151</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9296</v>
+        <v>0.8234</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2395</v>
+        <v>0.2122</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.201</v>
+        <v>-0.2307</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9296</v>
+        <v>0.8234</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9296</v>
+        <v>0.8234</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9296</v>
+        <v>0.8234</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0292</v>
+        <v>0.915</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0292</v>
+        <v>0.915</v>
       </c>
       <c r="N31" t="n">
         <v>166</v>
@@ -1872,78 +1872,78 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iDISBALANCE</t>
+          <t>Porya</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8628</v>
+        <v>0.7765</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2223</v>
+        <v>0.2001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2314</v>
+        <v>-0.2521</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8628</v>
+        <v>0.7765</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8628</v>
+        <v>0.7765</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8628</v>
+        <v>0.7765</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9552</v>
+        <v>0.7973</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9552</v>
+        <v>0.7973</v>
       </c>
       <c r="N32" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porya</t>
+          <t>svyat</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8509</v>
+        <v>0.6204</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2192</v>
+        <v>0.1598</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2369</v>
+        <v>-0.3232</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8509</v>
+        <v>0.6204</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8509</v>
+        <v>0.6204</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8509</v>
+        <v>0.6204</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8728</v>
+        <v>0.637</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8728</v>
+        <v>0.637</v>
       </c>
       <c r="N33" t="n">
         <v>139</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>svyat</t>
+          <t>iDISBALANCE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7085</v>
+        <v>0.5729</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1825</v>
+        <v>0.1476</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3017</v>
+        <v>-0.3448</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7085</v>
+        <v>0.5729</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7085</v>
+        <v>0.5729</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7085</v>
+        <v>0.5729</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7268</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7268</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6849</v>
+        <v>0.5184</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1765</v>
+        <v>0.1336</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3124</v>
+        <v>-0.3696</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6849</v>
+        <v>0.5184</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6849</v>
+        <v>0.5184</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6849</v>
+        <v>0.5184</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7025</v>
+        <v>0.5323</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7025</v>
+        <v>0.5323</v>
       </c>
       <c r="N35" t="n">
         <v>157</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5118</v>
+        <v>0.3873</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1319</v>
+        <v>0.0998</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3912</v>
+        <v>-0.4294</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5118</v>
+        <v>0.3873</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5118</v>
+        <v>0.3873</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5118</v>
+        <v>0.3873</v>
       </c>
       <c r="I36" t="n">
-        <v>0.525</v>
+        <v>0.3977</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.525</v>
+        <v>0.3977</v>
       </c>
       <c r="N36" t="n">
         <v>139</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4831</v>
+        <v>0.3857</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1245</v>
+        <v>0.0994</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4043</v>
+        <v>-0.4301</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4831</v>
+        <v>0.3857</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4831</v>
+        <v>0.3857</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4831</v>
+        <v>0.3857</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4831</v>
+        <v>0.3857</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4831</v>
+        <v>0.3857</v>
       </c>
       <c r="N37" t="n">
         <v>125</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4505</v>
+        <v>0.3807</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1161</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4191</v>
+        <v>-0.4324</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4505</v>
+        <v>0.3807</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4505</v>
+        <v>0.3807</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4505</v>
+        <v>0.3807</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4621</v>
+        <v>0.3909</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4621</v>
+        <v>0.3909</v>
       </c>
       <c r="N38" t="n">
         <v>139</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2713</v>
+        <v>0.0646</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0699</v>
+        <v>0.0166</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5007</v>
+        <v>-0.5764</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2713</v>
+        <v>0.0646</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2713</v>
+        <v>0.0646</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2713</v>
+        <v>0.0646</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3161</v>
+        <v>0.0757</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3161</v>
+        <v>0.0757</v>
       </c>
       <c r="N39" t="n">
         <v>277</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0101</v>
+        <v>0.0437</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0026</v>
+        <v>0.0113</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.6196</v>
+        <v>-0.5859</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0101</v>
+        <v>0.0437</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0101</v>
+        <v>0.0437</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0101</v>
+        <v>0.0437</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0104</v>
+        <v>0.0449</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0104</v>
+        <v>0.0449</v>
       </c>
       <c r="N40" t="n">
         <v>139</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ice</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.1636</v>
+        <v>-0.1019</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0422</v>
+        <v>-0.0263</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.6987</v>
+        <v>-0.6522</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.1636</v>
+        <v>-0.1019</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.1636</v>
+        <v>-0.1019</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.1636</v>
+        <v>-0.1019</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1766</v>
+        <v>-0.1226</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.1766</v>
+        <v>-0.1226</v>
       </c>
       <c r="N41" t="n">
-        <v>131</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>ice</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1754</v>
+        <v>-0.1176</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0452</v>
+        <v>-0.0303</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.704</v>
+        <v>-0.6594</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1754</v>
+        <v>-0.1176</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1754</v>
+        <v>-0.1176</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1754</v>
+        <v>-0.1176</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.2096</v>
+        <v>-0.1273</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.2096</v>
+        <v>-0.1273</v>
       </c>
       <c r="N42" t="n">
-        <v>251</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.2921</v>
+        <v>-0.3822</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0985</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.7572</v>
+        <v>-0.7799</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2921</v>
+        <v>-0.3822</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2921</v>
+        <v>-0.3822</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2921</v>
+        <v>-0.3822</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3234</v>
+        <v>-0.4247</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.3234</v>
+        <v>-0.4247</v>
       </c>
       <c r="N43" t="n">
         <v>216</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.4244</v>
+        <v>-0.4508</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1093</v>
+        <v>-0.1162</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.8174</v>
+        <v>-0.8111</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.4244</v>
+        <v>-0.4508</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.4244</v>
+        <v>-0.4508</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.4244</v>
+        <v>-0.4508</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4699</v>
+        <v>-0.501</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.4699</v>
+        <v>-0.501</v>
       </c>
       <c r="N44" t="n">
         <v>216</v>
@@ -2470,185 +2470,185 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>Sergiz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4514</v>
+        <v>-0.5944</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.1163</v>
+        <v>-0.1531</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.8297</v>
+        <v>-0.8766</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4514</v>
+        <v>-0.5944</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4514</v>
+        <v>-0.5944</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4514</v>
+        <v>-0.5944</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5258</v>
+        <v>-0.5944</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>277</v>
+        <v>125</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.5258</v>
+        <v>-0.5944</v>
       </c>
       <c r="N45" t="n">
-        <v>277</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sergiz</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.5851</v>
+        <v>-0.6381</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1508</v>
+        <v>-0.1644</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.8965</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.5851</v>
+        <v>-0.6381</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.5851</v>
+        <v>-0.6381</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5851</v>
+        <v>-0.6381</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5851</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>125</v>
+        <v>277</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.5851</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>125</v>
+        <v>277</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>j3kie</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.6649</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1713</v>
+        <v>-0.1697</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.9059</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.6649</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6649</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6649</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>j3kie</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6833</v>
+        <v>-0.7063</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1761</v>
+        <v>-0.182</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.9353</v>
+        <v>-0.9275</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6833</v>
+        <v>-0.7063</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6833</v>
+        <v>-0.7063</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.6833</v>
+        <v>-0.7063</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6833</v>
+        <v>-0.7252</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.6833</v>
+        <v>-0.7252</v>
       </c>
       <c r="N48" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.7698</v>
+        <v>-0.7711</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1983</v>
+        <v>-0.1987</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9746</v>
+        <v>-0.9571</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.7698</v>
+        <v>-0.7711</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.7698</v>
+        <v>-0.7711</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.7698</v>
+        <v>-0.7711</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.7896</v>
+        <v>-0.7917</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.7896</v>
+        <v>-0.7917</v>
       </c>
       <c r="N49" t="n">
         <v>157</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7946</v>
+        <v>-0.7996</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.2047</v>
+        <v>-0.206</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.9859</v>
+        <v>-0.97</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.7946</v>
+        <v>-0.7996</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.7946</v>
+        <v>-0.7996</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.7946</v>
+        <v>-0.7996</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8361</v>
+        <v>-0.8429</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.8361</v>
+        <v>-0.8429</v>
       </c>
       <c r="N50" t="n">
         <v>151</v>
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.9042</v>
+        <v>-0.9425</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.233</v>
+        <v>-0.2428</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.0358</v>
+        <v>-1.0351</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.9042</v>
+        <v>-0.9425</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.9042</v>
+        <v>-0.9425</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.9042</v>
+        <v>-0.9425</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0011</v>
+        <v>-1.0474</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-1.0011</v>
+        <v>-1.0474</v>
       </c>
       <c r="N51" t="n">
         <v>216</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9382</v>
+        <v>-0.9478</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2417</v>
+        <v>-0.2442</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.0513</v>
+        <v>-1.0376</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.9382</v>
+        <v>-0.9478</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.9382</v>
+        <v>-0.9478</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.9382</v>
+        <v>-0.9478</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0929</v>
+        <v>-1.1103</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.0929</v>
+        <v>-1.1103</v>
       </c>
       <c r="N52" t="n">
         <v>277</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9963</v>
+        <v>-1.022</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2567</v>
+        <v>-0.2633</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.0777</v>
+        <v>-1.0714</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.9963</v>
+        <v>-1.022</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.9963</v>
+        <v>-1.022</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.9963</v>
+        <v>-1.022</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9963</v>
+        <v>-1.022</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.9963</v>
+        <v>-1.022</v>
       </c>
       <c r="N53" t="n">
         <v>125</v>
@@ -2884,124 +2884,124 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>floweaN</t>
+          <t>sorrow</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.361</v>
+        <v>-1.3354</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.3507</v>
+        <v>-0.3441</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.2438</v>
+        <v>-1.2141</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.361</v>
+        <v>-1.3354</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.361</v>
+        <v>-1.3354</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.361</v>
+        <v>-1.3354</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.5068</v>
+        <v>-1.4453</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>216</v>
+        <v>131</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.5068</v>
+        <v>-1.4453</v>
       </c>
       <c r="N54" t="n">
-        <v>216</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1eeR</t>
+          <t>floweaN</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.4105</v>
+        <v>-1.3677</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.3634</v>
+        <v>-0.3524</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.2663</v>
+        <v>-1.2288</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.4105</v>
+        <v>-1.3677</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.4105</v>
+        <v>-1.3677</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.4105</v>
+        <v>-1.3677</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.5616</v>
+        <v>-1.5199</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.5616</v>
+        <v>-1.5199</v>
       </c>
       <c r="N55" t="n">
-        <v>166</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sorrow</t>
+          <t>smiley</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.4216</v>
+        <v>-1.3888</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3663</v>
+        <v>-0.3578</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.2713</v>
+        <v>-1.2385</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.4216</v>
+        <v>-1.3888</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.4216</v>
+        <v>-1.3888</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.4216</v>
+        <v>-1.3888</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.5344</v>
+        <v>-1.5031</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.5344</v>
+        <v>-1.5031</v>
       </c>
       <c r="N56" t="n">
         <v>131</v>
@@ -3022,47 +3022,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>smiley</t>
+          <t>1eeR</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.542</v>
+        <v>-1.4461</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3973</v>
+        <v>-0.3726</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.3262</v>
+        <v>-1.2646</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.542</v>
+        <v>-1.4461</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.542</v>
+        <v>-1.4461</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.542</v>
+        <v>-1.4461</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.6643</v>
+        <v>-1.607</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.6643</v>
+        <v>-1.607</v>
       </c>
       <c r="N57" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58">
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.5686</v>
+        <v>-1.5291</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.4042</v>
+        <v>-0.394</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.3383</v>
+        <v>-1.3024</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.5686</v>
+        <v>-1.5291</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.5686</v>
+        <v>-1.5291</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.5686</v>
+        <v>-1.5291</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.5686</v>
+        <v>-1.5291</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.5686</v>
+        <v>-1.5291</v>
       </c>
       <c r="N58" t="n">
         <v>125</v>
@@ -3114,93 +3114,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NickelBack</t>
+          <t>w1nt3r</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.6956</v>
+        <v>-1.7054</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.4369</v>
+        <v>-0.4394</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.3961</v>
+        <v>-1.3827</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.6956</v>
+        <v>-1.7054</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.6956</v>
+        <v>-1.7054</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.6956</v>
+        <v>-1.7054</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.0784</v>
+        <v>-1.8458</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>280</v>
+        <v>131</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-2.0784</v>
+        <v>-1.8458</v>
       </c>
       <c r="N59" t="n">
-        <v>280</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>w1nt3r</t>
+          <t>NickelBack</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.7896</v>
+        <v>-1.7285</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.4611</v>
+        <v>-0.4454</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.4389</v>
+        <v>-1.3932</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.7896</v>
+        <v>-1.7285</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.7896</v>
+        <v>-1.7285</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.7896</v>
+        <v>-1.7285</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.9315</v>
+        <v>-2.1345</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>131</v>
+        <v>280</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.9315</v>
+        <v>-2.1345</v>
       </c>
       <c r="N60" t="n">
-        <v>131</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61">
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.9201</v>
+        <v>-1.8246</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4947</v>
+        <v>-0.4701</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.4983</v>
+        <v>-1.437</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.9201</v>
+        <v>-1.8246</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.9201</v>
+        <v>-1.8246</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.9201</v>
+        <v>-1.8246</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.2944</v>
+        <v>-2.1945</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.2944</v>
+        <v>-2.1945</v>
       </c>
       <c r="N61" t="n">
         <v>251</v>
@@ -3349,10 +3349,10 @@
         <v>1.23</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4392</v>
+        <v>0.4536</v>
       </c>
       <c r="J2" t="n">
-        <v>10.1016</v>
+        <v>10.4328</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2429</v>
+        <v>-0.2258</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.5867</v>
+        <v>-5.1934</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3354</v>
+        <v>-0.3198</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.7142</v>
+        <v>-7.3554</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>0.65</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3718</v>
+        <v>-0.3582</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.551399999999999</v>
+        <v>-8.2386</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4343</v>
+        <v>-0.4258</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.988899999999999</v>
+        <v>-9.7934</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8842</v>
+        <v>0.8143</v>
       </c>
       <c r="J7" t="n">
-        <v>20.3366</v>
+        <v>18.7289</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.44</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5433</v>
+        <v>0.4767</v>
       </c>
       <c r="J8" t="n">
-        <v>12.4959</v>
+        <v>10.9641</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>1.37</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4738</v>
+        <v>0.4112</v>
       </c>
       <c r="J9" t="n">
-        <v>10.8974</v>
+        <v>9.457599999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>1.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2853</v>
+        <v>0.2371</v>
       </c>
       <c r="J10" t="n">
-        <v>6.5619</v>
+        <v>5.4533</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1682</v>
+        <v>0.1325</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8686</v>
+        <v>3.0475</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.95</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5913</v>
+        <v>1.6304</v>
       </c>
       <c r="J12" t="n">
-        <v>27.0521</v>
+        <v>27.7168</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5338</v>
+        <v>1.569</v>
       </c>
       <c r="J13" t="n">
-        <v>26.0746</v>
+        <v>26.673</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.61</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1917</v>
+        <v>1.2141</v>
       </c>
       <c r="J14" t="n">
-        <v>20.2589</v>
+        <v>20.6397</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>1.35</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.787</v>
       </c>
       <c r="J15" t="n">
-        <v>13.5473</v>
+        <v>13.379</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>1.25</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5957</v>
+        <v>0.5712</v>
       </c>
       <c r="J16" t="n">
-        <v>10.1269</v>
+        <v>9.7104</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>0.87</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0605</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5691</v>
+        <v>-1.0285</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>0.58</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4019</v>
+        <v>-0.3972</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.8323</v>
+        <v>-6.7524</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>0.45</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5132</v>
+        <v>-0.5135</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.724399999999999</v>
+        <v>-8.7295</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>0.43</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5309</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.0253</v>
+        <v>-9.057600000000001</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.33</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6204</v>
+        <v>-0.6342</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.5468</v>
+        <v>-10.7814</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.55</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1632</v>
+        <v>1.1767</v>
       </c>
       <c r="J22" t="n">
-        <v>25.5904</v>
+        <v>25.8874</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.38</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9022</v>
+        <v>0.8867</v>
       </c>
       <c r="J23" t="n">
-        <v>19.8484</v>
+        <v>19.5074</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.19</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5187</v>
+        <v>0.4864</v>
       </c>
       <c r="J24" t="n">
-        <v>11.4114</v>
+        <v>10.7008</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2769</v>
+        <v>0.2456</v>
       </c>
       <c r="J25" t="n">
-        <v>6.0918</v>
+        <v>5.4032</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0408</v>
+        <v>-0.0355</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8976</v>
+        <v>-0.781</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>0.97</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0217</v>
+        <v>-0.0102</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4774</v>
+        <v>-0.2244</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1517</v>
+        <v>-0.1361</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.3374</v>
+        <v>-2.9942</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>0.8</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2265</v>
+        <v>-0.2112</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.983</v>
+        <v>-4.6464</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4445</v>
+        <v>-0.437</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.779</v>
+        <v>-9.614000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5645</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.276</v>
+        <v>-12.419</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.79</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4696</v>
+        <v>1.5008</v>
       </c>
       <c r="J32" t="n">
-        <v>33.8008</v>
+        <v>34.5184</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.23</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.5725</v>
       </c>
       <c r="J33" t="n">
-        <v>13.8529</v>
+        <v>13.1675</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>1.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5597</v>
+        <v>0.5289</v>
       </c>
       <c r="J34" t="n">
-        <v>12.8731</v>
+        <v>12.1647</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>1.2</v>
       </c>
       <c r="I35" t="n">
-        <v>0.538</v>
+        <v>0.5068</v>
       </c>
       <c r="J35" t="n">
-        <v>12.374</v>
+        <v>11.6564</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4428</v>
+        <v>-0.4037</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.1844</v>
+        <v>-9.2851</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>0.87</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1582</v>
+        <v>-0.1426</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.6386</v>
+        <v>-3.2798</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2011</v>
+        <v>-0.1851</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.6253</v>
+        <v>-4.2573</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2214</v>
+        <v>-0.2053</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.0922</v>
+        <v>-4.7219</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.67</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3509</v>
+        <v>-0.3364</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.0707</v>
+        <v>-7.7372</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.64</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.378</v>
+        <v>-0.365</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.694000000000001</v>
+        <v>-8.395</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.41</v>
       </c>
       <c r="I42" t="n">
-        <v>0.984</v>
+        <v>0.9778</v>
       </c>
       <c r="J42" t="n">
-        <v>26.568</v>
+        <v>26.4006</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.34</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8495</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>22.9365</v>
+        <v>22.3317</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2946</v>
+        <v>0.2603</v>
       </c>
       <c r="J44" t="n">
-        <v>7.9542</v>
+        <v>7.0281</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2677</v>
+        <v>0.2346</v>
       </c>
       <c r="J45" t="n">
-        <v>7.2279</v>
+        <v>6.3342</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.74</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7478</v>
+        <v>-0.7209</v>
       </c>
       <c r="J46" t="n">
-        <v>-20.1906</v>
+        <v>-19.4643</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9436</v>
+        <v>0.911</v>
       </c>
       <c r="J47" t="n">
-        <v>25.4772</v>
+        <v>24.597</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1378</v>
+        <v>0.1045</v>
       </c>
       <c r="J48" t="n">
-        <v>3.7206</v>
+        <v>2.8215</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.82</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2253</v>
+        <v>-0.2052</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.0831</v>
+        <v>-5.5404</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2353</v>
+        <v>-0.2153</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.3531</v>
+        <v>-5.8131</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.44</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5677</v>
+        <v>-0.5784</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.3279</v>
+        <v>-15.6168</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.4</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9785</v>
+        <v>0.9719</v>
       </c>
       <c r="J52" t="n">
-        <v>34.2475</v>
+        <v>34.0165</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7372</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>25.802</v>
+        <v>24.7135</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5177</v>
+        <v>0.4778</v>
       </c>
       <c r="J54" t="n">
-        <v>18.1195</v>
+        <v>16.723</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.84</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5114</v>
+        <v>-0.4701</v>
       </c>
       <c r="J55" t="n">
-        <v>-17.899</v>
+        <v>-16.4535</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-25.137</v>
+        <v>-24.08</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0.533</v>
+        <v>0.4752</v>
       </c>
       <c r="J57" t="n">
-        <v>18.655</v>
+        <v>16.632</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.202</v>
+        <v>0.1602</v>
       </c>
       <c r="J58" t="n">
-        <v>7.07</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>0.9</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1423</v>
+        <v>-0.1236</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.9805</v>
+        <v>-4.326</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>0.77</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2765</v>
+        <v>-0.2574</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.6775</v>
+        <v>-9.009</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3146</v>
+        <v>-0.2973</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.011</v>
+        <v>-10.4055</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.32</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8038</v>
       </c>
       <c r="J62" t="n">
-        <v>23.1868</v>
+        <v>22.5064</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.21</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5913</v>
+        <v>0.5526</v>
       </c>
       <c r="J63" t="n">
-        <v>16.5564</v>
+        <v>15.4728</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2125</v>
+        <v>-0.176</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.95</v>
+        <v>-4.928</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2429</v>
+        <v>-0.2044</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.8012</v>
+        <v>-5.7232</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3282</v>
+        <v>-0.2861</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.1896</v>
+        <v>-8.0108</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.75</v>
       </c>
       <c r="I67" t="n">
-        <v>1.163</v>
+        <v>1.1536</v>
       </c>
       <c r="J67" t="n">
-        <v>32.564</v>
+        <v>32.3008</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1412</v>
+        <v>0.1103</v>
       </c>
       <c r="J68" t="n">
-        <v>3.9536</v>
+        <v>3.0884</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0492</v>
       </c>
       <c r="J69" t="n">
-        <v>1.8788</v>
+        <v>1.3776</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.95</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0747</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.5564</v>
+        <v>-2.0916</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4768</v>
+        <v>-0.4762</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.3504</v>
+        <v>-13.3336</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0535</v>
+        <v>1.06</v>
       </c>
       <c r="J72" t="n">
-        <v>44.247</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.25</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6672</v>
+        <v>0.6327</v>
       </c>
       <c r="J73" t="n">
-        <v>28.0224</v>
+        <v>26.5734</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.06</v>
       </c>
       <c r="I74" t="n">
-        <v>0.214</v>
+        <v>0.1835</v>
       </c>
       <c r="J74" t="n">
-        <v>8.988</v>
+        <v>7.707</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>0.93</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2814</v>
+        <v>-0.2411</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.8188</v>
+        <v>-10.1262</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.88</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4167</v>
+        <v>-0.374</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.5014</v>
+        <v>-15.708</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4259</v>
+        <v>0.369</v>
       </c>
       <c r="J77" t="n">
-        <v>17.8878</v>
+        <v>15.498</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1541</v>
+        <v>0.1185</v>
       </c>
       <c r="J78" t="n">
-        <v>6.4722</v>
+        <v>4.977</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.0803</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.0404</v>
+        <v>-3.3726</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1437</v>
+        <v>-0.1247</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.0354</v>
+        <v>-5.2374</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3163</v>
+        <v>-0.2992</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.2846</v>
+        <v>-12.5664</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.96</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6206</v>
+        <v>1.6613</v>
       </c>
       <c r="J82" t="n">
-        <v>29.1708</v>
+        <v>29.9034</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.7</v>
       </c>
       <c r="I83" t="n">
-        <v>1.3108</v>
+        <v>1.3329</v>
       </c>
       <c r="J83" t="n">
-        <v>23.5944</v>
+        <v>23.9922</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.54</v>
       </c>
       <c r="I84" t="n">
-        <v>1.1126</v>
+        <v>1.1307</v>
       </c>
       <c r="J84" t="n">
-        <v>20.0268</v>
+        <v>20.3526</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.19</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4799</v>
+        <v>0.45</v>
       </c>
       <c r="J85" t="n">
-        <v>8.638199999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>1.14</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3634</v>
+        <v>0.3302</v>
       </c>
       <c r="J86" t="n">
-        <v>6.5412</v>
+        <v>5.9436</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>0.64</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.3351</v>
+        <v>-0.3259</v>
       </c>
       <c r="J87" t="n">
-        <v>-6.0318</v>
+        <v>-5.8662</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.61</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3649</v>
+        <v>-0.3585</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.5682</v>
+        <v>-6.453</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.45</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.507</v>
+        <v>-0.5078</v>
       </c>
       <c r="J89" t="n">
-        <v>-9.125999999999999</v>
+        <v>-9.1404</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.41</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5423</v>
+        <v>-0.5458</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.7614</v>
+        <v>-9.824400000000001</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.37</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5782</v>
+        <v>-0.5856</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.4076</v>
+        <v>-10.5408</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>2.29</v>
       </c>
       <c r="I92" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J92" t="n">
-        <v>30.9952</v>
+        <v>31.7088</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.8</v>
       </c>
       <c r="I93" t="n">
-        <v>1.4244</v>
+        <v>1.4525</v>
       </c>
       <c r="J93" t="n">
-        <v>22.7904</v>
+        <v>23.24</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.33</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7654</v>
+        <v>0.7524</v>
       </c>
       <c r="J94" t="n">
-        <v>12.2464</v>
+        <v>12.0384</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.26</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6241</v>
+        <v>0.6015</v>
       </c>
       <c r="J95" t="n">
-        <v>9.9856</v>
+        <v>9.624000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>1.1</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2561</v>
+        <v>0.2211</v>
       </c>
       <c r="J96" t="n">
-        <v>4.0976</v>
+        <v>3.5376</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.04</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2481</v>
+        <v>0.2322</v>
       </c>
       <c r="J97" t="n">
-        <v>3.9696</v>
+        <v>3.7152</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>0.77</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2425</v>
+        <v>-0.2284</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.88</v>
+        <v>-3.6544</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.59</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4074</v>
+        <v>-0.3981</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.5184</v>
+        <v>-6.3696</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.42</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5568</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.908799999999999</v>
+        <v>-8.992000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.4</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5743</v>
+        <v>-0.5821</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.188800000000001</v>
+        <v>-9.313599999999999</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.72</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3525</v>
+        <v>1.3747</v>
       </c>
       <c r="J102" t="n">
-        <v>27.05</v>
+        <v>27.494</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.4</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9167</v>
+        <v>0.9096</v>
       </c>
       <c r="J103" t="n">
-        <v>18.334</v>
+        <v>18.192</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.4</v>
       </c>
       <c r="I104" t="n">
-        <v>0.9167</v>
+        <v>0.9096</v>
       </c>
       <c r="J104" t="n">
-        <v>18.334</v>
+        <v>18.192</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I105" t="n">
-        <v>0.881</v>
+        <v>0.8711</v>
       </c>
       <c r="J105" t="n">
-        <v>17.62</v>
+        <v>17.422</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I106" t="n">
-        <v>0.225</v>
+        <v>0.194</v>
       </c>
       <c r="J106" t="n">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>0.97</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0188</v>
+        <v>-0.0066</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.376</v>
+        <v>-0.132</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>0.78</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2448</v>
+        <v>-0.2299</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.896</v>
+        <v>-4.598</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.77</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2546</v>
+        <v>-0.2398</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.092</v>
+        <v>-4.796</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.61</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3987</v>
+        <v>-0.3876</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.974</v>
+        <v>-7.752</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.44</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.548</v>
+        <v>-0.5528</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.96</v>
+        <v>-11.056</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.44</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0137</v>
+        <v>1.0133</v>
       </c>
       <c r="J112" t="n">
-        <v>11.1507</v>
+        <v>11.1463</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.36</v>
       </c>
       <c r="I113" t="n">
-        <v>0.869</v>
+        <v>0.8499</v>
       </c>
       <c r="J113" t="n">
-        <v>9.558999999999999</v>
+        <v>9.3489</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.24</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6274</v>
+        <v>0.5959</v>
       </c>
       <c r="J114" t="n">
-        <v>6.9014</v>
+        <v>6.5549</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4775</v>
+        <v>0.4436</v>
       </c>
       <c r="J115" t="n">
-        <v>5.2525</v>
+        <v>4.8796</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4605</v>
+        <v>-0.4204</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.0655</v>
+        <v>-4.6244</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4877</v>
+        <v>0.4291</v>
       </c>
       <c r="J117" t="n">
-        <v>5.3647</v>
+        <v>4.7201</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4371</v>
+        <v>0.3795</v>
       </c>
       <c r="J118" t="n">
-        <v>4.8081</v>
+        <v>4.1745</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.16</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3672</v>
+        <v>0.3124</v>
       </c>
       <c r="J119" t="n">
-        <v>4.0392</v>
+        <v>3.4364</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>1.07</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1939</v>
+        <v>0.1535</v>
       </c>
       <c r="J120" t="n">
-        <v>2.1329</v>
+        <v>1.6885</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.27</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7099</v>
+        <v>-0.7481</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.8089</v>
+        <v>-8.229100000000001</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>2.04</v>
       </c>
       <c r="I122" t="n">
-        <v>1.4582</v>
+        <v>1.4716</v>
       </c>
       <c r="J122" t="n">
-        <v>8.7492</v>
+        <v>8.829599999999999</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.12</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2865</v>
+        <v>0.2374</v>
       </c>
       <c r="J123" t="n">
-        <v>1.719</v>
+        <v>1.4244</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>0.77</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2839</v>
+        <v>-0.2653</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.7034</v>
+        <v>-1.5918</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.74</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3125</v>
+        <v>-0.2955</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.875</v>
+        <v>-1.773</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.45</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5663</v>
+        <v>-0.5782</v>
       </c>
       <c r="J126" t="n">
-        <v>-3.3978</v>
+        <v>-3.4692</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.56</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1893</v>
+        <v>1.2041</v>
       </c>
       <c r="J127" t="n">
-        <v>7.1358</v>
+        <v>7.2246</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.53</v>
       </c>
       <c r="I128" t="n">
-        <v>1.1485</v>
+        <v>1.1617</v>
       </c>
       <c r="J128" t="n">
-        <v>6.891</v>
+        <v>6.9702</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.96</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2029</v>
+        <v>-0.1684</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.2174</v>
+        <v>-1.0104</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2653</v>
+        <v>-0.2269</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.5918</v>
+        <v>-1.3614</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2653</v>
+        <v>-0.2269</v>
       </c>
       <c r="J131" t="n">
-        <v>-1.5918</v>
+        <v>-1.3614</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.88</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6204</v>
+        <v>1.6727</v>
       </c>
       <c r="J132" t="n">
-        <v>9.7224</v>
+        <v>10.0362</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.5821</v>
       </c>
       <c r="J133" t="n">
-        <v>3.7044</v>
+        <v>3.4926</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>0.96</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1956</v>
+        <v>-0.1609</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.1736</v>
+        <v>-0.9654</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2275</v>
+        <v>-0.1905</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.365</v>
+        <v>-1.143</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.71</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.7945</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.89</v>
+        <v>-4.767</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.51</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9157</v>
+        <v>0.8734</v>
       </c>
       <c r="J137" t="n">
-        <v>5.4942</v>
+        <v>5.2404</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4356</v>
+        <v>0.3781</v>
       </c>
       <c r="J138" t="n">
-        <v>2.6136</v>
+        <v>2.2686</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.88</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1686</v>
+        <v>-0.1484</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.0116</v>
+        <v>-0.8904</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.77</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.281</v>
+        <v>-0.2622</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.686</v>
+        <v>-1.5732</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.6</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4366</v>
+        <v>-0.4301</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.6196</v>
+        <v>-2.5806</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>2.34</v>
       </c>
       <c r="I142" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J142" t="n">
-        <v>11.6232</v>
+        <v>11.8908</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.39</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8974</v>
       </c>
       <c r="J143" t="n">
-        <v>5.4588</v>
+        <v>5.3844</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2114</v>
+        <v>0.1822</v>
       </c>
       <c r="J144" t="n">
-        <v>1.2684</v>
+        <v>1.0932</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0501</v>
+        <v>0.0333</v>
       </c>
       <c r="J145" t="n">
-        <v>0.3006</v>
+        <v>0.1998</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.86</v>
+        <v>-0.8488</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.16</v>
+        <v>-5.0928</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.94</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4539</v>
+        <v>1.4977</v>
       </c>
       <c r="J147" t="n">
-        <v>8.7234</v>
+        <v>8.9862</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>0.74</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2949</v>
+        <v>-0.277</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.7694</v>
+        <v>-1.662</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.71</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3229</v>
+        <v>-0.3062</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.9374</v>
+        <v>-1.8372</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.43</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5695</v>
+        <v>-0.5793</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.417</v>
+        <v>-3.4758</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.39</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6031</v>
+        <v>-0.6186</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.6186</v>
+        <v>-3.7116</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.52</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2277</v>
+        <v>1.3415</v>
       </c>
       <c r="J152" t="n">
-        <v>4.9108</v>
+        <v>5.366</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0438</v>
+        <v>0.0984</v>
       </c>
       <c r="J153" t="n">
-        <v>0.1752</v>
+        <v>0.3936</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.16</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.8227</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.1028</v>
+        <v>-3.2908</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.09</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.8387</v>
+        <v>-0.9028</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.3548</v>
+        <v>-3.6112</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.01</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.9107</v>
+        <v>-0.9967</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.6428</v>
+        <v>-3.9868</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>3.46</v>
       </c>
       <c r="I157" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J157" t="n">
-        <v>7.7488</v>
+        <v>7.9272</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.64</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2147</v>
+        <v>1.2426</v>
       </c>
       <c r="J158" t="n">
-        <v>4.8588</v>
+        <v>4.9704</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.49</v>
       </c>
       <c r="I159" t="n">
-        <v>1.022</v>
+        <v>1.0397</v>
       </c>
       <c r="J159" t="n">
-        <v>4.088</v>
+        <v>4.1588</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.23</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5306</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
-        <v>2.1224</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.17</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3977</v>
+        <v>0.3602</v>
       </c>
       <c r="J161" t="n">
-        <v>1.5908</v>
+        <v>1.4408</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>2.39</v>
       </c>
       <c r="I162" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J162" t="n">
-        <v>7.7488</v>
+        <v>7.9272</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.92</v>
       </c>
       <c r="I163" t="n">
-        <v>1.5427</v>
+        <v>1.5809</v>
       </c>
       <c r="J163" t="n">
-        <v>6.1708</v>
+        <v>6.3236</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.86</v>
       </c>
       <c r="I164" t="n">
-        <v>1.4747</v>
+        <v>1.5092</v>
       </c>
       <c r="J164" t="n">
-        <v>5.8988</v>
+        <v>6.0368</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1.28</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6437</v>
+        <v>0.6218</v>
       </c>
       <c r="J165" t="n">
-        <v>2.5748</v>
+        <v>2.4872</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>1.17</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4062</v>
+        <v>0.3704</v>
       </c>
       <c r="J166" t="n">
-        <v>1.6248</v>
+        <v>1.4816</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>0.53</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.4259</v>
+        <v>-0.4251</v>
       </c>
       <c r="J167" t="n">
-        <v>-1.7036</v>
+        <v>-1.7004</v>
       </c>
     </row>
     <row r="168">
@@ -10029,10 +10029,10 @@
         <v>0.5</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4544</v>
+        <v>-0.4559</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.8176</v>
+        <v>-1.8236</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.46</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4905</v>
+        <v>-0.4937</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.962</v>
+        <v>-1.9748</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.19</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7358</v>
+        <v>-0.7708</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.9432</v>
+        <v>-3.0832</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.27</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5517</v>
+        <v>0.4926</v>
       </c>
       <c r="J172" t="n">
-        <v>6.6204</v>
+        <v>5.9112</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.18</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4011</v>
+        <v>0.3447</v>
       </c>
       <c r="J173" t="n">
-        <v>4.8132</v>
+        <v>4.1364</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.09</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2341</v>
+        <v>0.1893</v>
       </c>
       <c r="J174" t="n">
-        <v>2.8092</v>
+        <v>2.2716</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1686</v>
+        <v>-0.1484</v>
       </c>
       <c r="J175" t="n">
-        <v>-2.0232</v>
+        <v>-1.7808</v>
       </c>
     </row>
     <row r="176">
@@ -10349,10 +10349,10 @@
         <v>1.4</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="J177" t="n">
-        <v>11.5944</v>
+        <v>11.484</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.35</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8697</v>
+        <v>0.8489</v>
       </c>
       <c r="J178" t="n">
-        <v>10.4364</v>
+        <v>10.1868</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7055</v>
+        <v>0.6734</v>
       </c>
       <c r="J179" t="n">
-        <v>8.465999999999999</v>
+        <v>8.0808</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>1.15</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4412</v>
+        <v>0.4032</v>
       </c>
       <c r="J180" t="n">
-        <v>5.2944</v>
+        <v>4.8384</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.49</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.256</v>
+        <v>-1.2938</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.072</v>
+        <v>-15.5256</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>2.69</v>
       </c>
       <c r="I182" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J182" t="n">
-        <v>9.686</v>
+        <v>9.909000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.76</v>
       </c>
       <c r="I183" t="n">
-        <v>1.3819</v>
+        <v>1.4072</v>
       </c>
       <c r="J183" t="n">
-        <v>6.9095</v>
+        <v>7.036</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.47</v>
       </c>
       <c r="I184" t="n">
-        <v>1.0201</v>
+        <v>1.0314</v>
       </c>
       <c r="J184" t="n">
-        <v>5.1005</v>
+        <v>5.157</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.91</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4006</v>
+        <v>-0.3695</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.003</v>
+        <v>-1.8475</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7582</v>
+        <v>-0.7436</v>
       </c>
       <c r="J186" t="n">
-        <v>-3.791</v>
+        <v>-3.718</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.66</v>
       </c>
       <c r="I187" t="n">
-        <v>1.129</v>
+        <v>1.132</v>
       </c>
       <c r="J187" t="n">
-        <v>5.645</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0141</v>
+        <v>0.0097</v>
       </c>
       <c r="J188" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0485</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.117</v>
+        <v>-0.1008</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.585</v>
+        <v>-0.504</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.48</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5324</v>
+        <v>-0.5374</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.662</v>
+        <v>-2.687</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.46</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5493</v>
+        <v>-0.5569</v>
       </c>
       <c r="J191" t="n">
-        <v>-2.7465</v>
+        <v>-2.7845</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.38</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8968</v>
       </c>
       <c r="J192" t="n">
-        <v>15.5176</v>
+        <v>15.2456</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.27</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6928</v>
+        <v>0.6625</v>
       </c>
       <c r="J193" t="n">
-        <v>11.7776</v>
+        <v>11.2625</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6721</v>
+        <v>0.6409</v>
       </c>
       <c r="J194" t="n">
-        <v>11.4257</v>
+        <v>10.8953</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2848</v>
+        <v>0.2527</v>
       </c>
       <c r="J195" t="n">
-        <v>4.8416</v>
+        <v>4.2959</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1705</v>
+        <v>-0.1391</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.8985</v>
+        <v>-2.3647</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.03</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1262</v>
+        <v>0.0958</v>
       </c>
       <c r="J197" t="n">
-        <v>2.1454</v>
+        <v>1.6286</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>0.9</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.137</v>
+        <v>-0.1205</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.329</v>
+        <v>-2.0485</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>0.83</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2099</v>
+        <v>-0.1909</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.5683</v>
+        <v>-3.2453</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.79</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2495</v>
+        <v>-0.2303</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.2415</v>
+        <v>-3.9151</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.78</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2592</v>
+        <v>-0.2401</v>
       </c>
       <c r="J201" t="n">
-        <v>-4.4064</v>
+        <v>-4.0817</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.78</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4498</v>
+        <v>1.4788</v>
       </c>
       <c r="J202" t="n">
-        <v>8.6988</v>
+        <v>8.8728</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.48</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0595</v>
+        <v>1.0675</v>
       </c>
       <c r="J203" t="n">
-        <v>6.357</v>
+        <v>6.405</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.31</v>
       </c>
       <c r="I204" t="n">
-        <v>0.759</v>
+        <v>0.7366</v>
       </c>
       <c r="J204" t="n">
-        <v>4.554</v>
+        <v>4.4196</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.15</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4199</v>
+        <v>0.3878</v>
       </c>
       <c r="J205" t="n">
-        <v>2.5194</v>
+        <v>2.3268</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7944</v>
+        <v>-0.7762</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.7664</v>
+        <v>-4.6572</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4845</v>
+        <v>0.4327</v>
       </c>
       <c r="J207" t="n">
-        <v>2.907</v>
+        <v>2.5962</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>1.05</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1843</v>
+        <v>0.147</v>
       </c>
       <c r="J208" t="n">
-        <v>1.1058</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0853</v>
+        <v>-0.0723</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.5118</v>
+        <v>-0.4338</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.63</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3953</v>
+        <v>-0.3835</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.3718</v>
+        <v>-2.301</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.37</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.6379</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.717</v>
+        <v>-3.8274</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.3</v>
       </c>
       <c r="I212" t="n">
-        <v>0.618</v>
+        <v>0.5621</v>
       </c>
       <c r="J212" t="n">
-        <v>18.54</v>
+        <v>16.863</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2663</v>
+        <v>0.2183</v>
       </c>
       <c r="J213" t="n">
-        <v>7.989</v>
+        <v>6.549</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.082</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.46</v>
+        <v>-2.043</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.7</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3416</v>
+        <v>-0.3259</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.248</v>
+        <v>-9.776999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4139</v>
+        <v>-0.4044</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.417</v>
+        <v>-12.132</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8236</v>
+        <v>0.7996</v>
       </c>
       <c r="J217" t="n">
-        <v>24.708</v>
+        <v>23.988</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.29</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7421</v>
+        <v>0.7127</v>
       </c>
       <c r="J218" t="n">
-        <v>22.263</v>
+        <v>21.381</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.17</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4842</v>
+        <v>0.4471</v>
       </c>
       <c r="J219" t="n">
-        <v>14.526</v>
+        <v>13.413</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4617</v>
+        <v>0.4247</v>
       </c>
       <c r="J220" t="n">
-        <v>13.851</v>
+        <v>12.741</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5709</v>
+        <v>-0.5331</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.127</v>
+        <v>-15.993</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.88</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6039</v>
+        <v>1.6512</v>
       </c>
       <c r="J222" t="n">
-        <v>9.6234</v>
+        <v>9.9072</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8348</v>
+        <v>0.8125</v>
       </c>
       <c r="J223" t="n">
-        <v>5.0088</v>
+        <v>4.875</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6932</v>
+        <v>0.6627</v>
       </c>
       <c r="J224" t="n">
-        <v>4.1592</v>
+        <v>3.9762</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5458</v>
+        <v>0.5113</v>
       </c>
       <c r="J225" t="n">
-        <v>3.2748</v>
+        <v>3.0678</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.27</v>
       </c>
       <c r="I226" t="n">
-        <v>-1.6696</v>
+        <v>-1.7897</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.0176</v>
+        <v>-10.7382</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.89</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2866</v>
+        <v>1.28</v>
       </c>
       <c r="J227" t="n">
-        <v>7.7196</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.37</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6778</v>
+        <v>0.6188</v>
       </c>
       <c r="J228" t="n">
-        <v>4.0668</v>
+        <v>3.7128</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>1.19</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3969</v>
+        <v>0.3422</v>
       </c>
       <c r="J229" t="n">
-        <v>2.3814</v>
+        <v>2.0532</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.63</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4189</v>
+        <v>-0.4119</v>
       </c>
       <c r="J230" t="n">
-        <v>-2.5134</v>
+        <v>-2.4714</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.44</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5792</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.4752</v>
+        <v>-3.5658</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6037</v>
+        <v>1.6455</v>
       </c>
       <c r="J232" t="n">
-        <v>33.6777</v>
+        <v>34.5555</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.35</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8326</v>
+        <v>0.8156</v>
       </c>
       <c r="J233" t="n">
-        <v>17.4846</v>
+        <v>17.1276</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>1.2</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5302</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="J234" t="n">
-        <v>11.1342</v>
+        <v>10.5105</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>1.07</v>
       </c>
       <c r="I235" t="n">
-        <v>0.2094</v>
+        <v>0.1802</v>
       </c>
       <c r="J235" t="n">
-        <v>4.3974</v>
+        <v>3.7842</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>1.05</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1501</v>
+        <v>0.1238</v>
       </c>
       <c r="J236" t="n">
-        <v>3.1521</v>
+        <v>2.5998</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>0.93</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.049</v>
       </c>
       <c r="J237" t="n">
-        <v>-1.3881</v>
+        <v>-1.029</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>0.76</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2583</v>
+        <v>-0.2445</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.4243</v>
+        <v>-5.1345</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>0.62</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3848</v>
+        <v>-0.3737</v>
       </c>
       <c r="J239" t="n">
-        <v>-8.0808</v>
+        <v>-7.8477</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.53</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4642</v>
+        <v>-0.4586</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.748200000000001</v>
+        <v>-9.630599999999999</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.53</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4642</v>
+        <v>-0.4586</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.748200000000001</v>
+        <v>-9.630599999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.73</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3567</v>
+        <v>1.3796</v>
       </c>
       <c r="J242" t="n">
-        <v>27.134</v>
+        <v>27.592</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.63</v>
       </c>
       <c r="I243" t="n">
-        <v>1.2325</v>
+        <v>1.2507</v>
       </c>
       <c r="J243" t="n">
-        <v>24.65</v>
+        <v>25.014</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>1.42</v>
       </c>
       <c r="I244" t="n">
-        <v>0.9476</v>
+        <v>0.9462</v>
       </c>
       <c r="J244" t="n">
-        <v>18.952</v>
+        <v>18.924</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I245" t="n">
-        <v>0.6605</v>
+        <v>0.6389</v>
       </c>
       <c r="J245" t="n">
-        <v>13.21</v>
+        <v>12.778</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>1.17</v>
       </c>
       <c r="I246" t="n">
-        <v>0.4432</v>
+        <v>0.4124</v>
       </c>
       <c r="J246" t="n">
-        <v>8.864000000000001</v>
+        <v>8.247999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.3036</v>
+        <v>-0.2925</v>
       </c>
       <c r="J247" t="n">
-        <v>-6.072</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>0.66</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.333</v>
+        <v>-0.3239</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.66</v>
+        <v>-6.478</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>0.57</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.415</v>
+        <v>-0.4094</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.188000000000001</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>0.52</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4566</v>
+        <v>-0.4524</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.132</v>
+        <v>-9.048</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.36</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5979</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.958</v>
+        <v>-12.168</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.63</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1363</v>
+        <v>1.1515</v>
       </c>
       <c r="J252" t="n">
-        <v>6.8178</v>
+        <v>6.909</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0828</v>
+        <v>-0.0699</v>
       </c>
       <c r="J253" t="n">
-        <v>-0.4968</v>
+        <v>-0.4194</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.57</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.4467</v>
+        <v>-0.4396</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.6802</v>
+        <v>-2.6376</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.49</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5162</v>
+        <v>-0.5178</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.0972</v>
+        <v>-3.1068</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.47</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5334</v>
+        <v>-0.5374</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.2004</v>
+        <v>-3.2244</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.79</v>
       </c>
       <c r="I257" t="n">
-        <v>1.4471</v>
+        <v>1.475</v>
       </c>
       <c r="J257" t="n">
-        <v>8.682600000000001</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.62</v>
       </c>
       <c r="I258" t="n">
-        <v>1.2333</v>
+        <v>1.25</v>
       </c>
       <c r="J258" t="n">
-        <v>7.3998</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.42</v>
       </c>
       <c r="I259" t="n">
-        <v>0.9559</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="J259" t="n">
-        <v>5.7354</v>
+        <v>5.7066</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>1.41</v>
       </c>
       <c r="I260" t="n">
-        <v>0.9385</v>
+        <v>0.9316</v>
       </c>
       <c r="J260" t="n">
-        <v>5.631</v>
+        <v>5.5896</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.54</v>
       </c>
       <c r="I261" t="n">
-        <v>-1.1862</v>
+        <v>-1.2194</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.1172</v>
+        <v>-7.3164</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.55</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1674</v>
+        <v>1.1811</v>
       </c>
       <c r="J262" t="n">
-        <v>30.3524</v>
+        <v>30.7086</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.33</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8088</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="J263" t="n">
-        <v>21.0288</v>
+        <v>20.4308</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.19</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5214</v>
+        <v>0.4881</v>
       </c>
       <c r="J264" t="n">
-        <v>13.5564</v>
+        <v>12.6906</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.07</v>
       </c>
       <c r="I265" t="n">
-        <v>0.225</v>
+        <v>0.1956</v>
       </c>
       <c r="J265" t="n">
-        <v>5.85</v>
+        <v>5.0856</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.97</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1754</v>
+        <v>-0.1442</v>
       </c>
       <c r="J266" t="n">
-        <v>-4.5604</v>
+        <v>-3.7492</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.24</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5426</v>
+        <v>0.4892</v>
       </c>
       <c r="J267" t="n">
-        <v>14.1076</v>
+        <v>12.7192</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.03</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1257</v>
+        <v>0.0953</v>
       </c>
       <c r="J268" t="n">
-        <v>3.2682</v>
+        <v>2.4778</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.79</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2497</v>
+        <v>-0.2305</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.4922</v>
+        <v>-5.993</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.74</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2976</v>
+        <v>-0.2796</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.7376</v>
+        <v>-7.2696</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.54</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4777</v>
+        <v>-0.4748</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.4202</v>
+        <v>-12.3448</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.18</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4499</v>
+        <v>0.3984</v>
       </c>
       <c r="J272" t="n">
-        <v>12.1473</v>
+        <v>10.7568</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.09</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2746</v>
+        <v>0.2293</v>
       </c>
       <c r="J273" t="n">
-        <v>7.4142</v>
+        <v>6.1911</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>0.86</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1776</v>
+        <v>-0.1603</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.7952</v>
+        <v>-4.3281</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.53</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4831</v>
+        <v>-0.4804</v>
       </c>
       <c r="J275" t="n">
-        <v>-13.0437</v>
+        <v>-12.9708</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.51</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5004</v>
+        <v>-0.4999</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.5108</v>
+        <v>-13.4973</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.32</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7912</v>
+        <v>0.7667</v>
       </c>
       <c r="J277" t="n">
-        <v>21.3624</v>
+        <v>20.7009</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.24</v>
       </c>
       <c r="I278" t="n">
-        <v>0.6282</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J278" t="n">
-        <v>16.9614</v>
+        <v>16.1001</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.24</v>
       </c>
       <c r="I279" t="n">
-        <v>0.6282</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J279" t="n">
-        <v>16.9614</v>
+        <v>16.1001</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1.21</v>
       </c>
       <c r="I280" t="n">
-        <v>0.5655</v>
+        <v>0.5323</v>
       </c>
       <c r="J280" t="n">
-        <v>15.2685</v>
+        <v>14.3721</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>1.04</v>
       </c>
       <c r="I281" t="n">
-        <v>0.1361</v>
+        <v>0.1125</v>
       </c>
       <c r="J281" t="n">
-        <v>3.6747</v>
+        <v>3.0375</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.62</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2507</v>
+        <v>1.2677</v>
       </c>
       <c r="J282" t="n">
-        <v>32.5182</v>
+        <v>32.9602</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.41</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9529</v>
+        <v>0.944</v>
       </c>
       <c r="J283" t="n">
-        <v>24.7754</v>
+        <v>24.544</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.35</v>
       </c>
       <c r="I284" t="n">
-        <v>0.84</v>
+        <v>0.8209</v>
       </c>
       <c r="J284" t="n">
-        <v>21.84</v>
+        <v>21.3434</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>1.22</v>
       </c>
       <c r="I285" t="n">
-        <v>0.5807</v>
+        <v>0.5505</v>
       </c>
       <c r="J285" t="n">
-        <v>15.0982</v>
+        <v>14.313</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.73</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.791</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="J286" t="n">
-        <v>-20.566</v>
+        <v>-20.0642</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>0.99</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.0027</v>
+        <v>0.0032</v>
       </c>
       <c r="J287" t="n">
-        <v>-0.0702</v>
+        <v>0.0832</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>0.95</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0665</v>
+        <v>-0.0546</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.729</v>
+        <v>-1.4196</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>0.78</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2531</v>
+        <v>-0.2355</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.5806</v>
+        <v>-6.123</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.7</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3278</v>
+        <v>-0.3117</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.5228</v>
+        <v>-8.104200000000001</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.59</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.427</v>
+        <v>-0.4179</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.102</v>
+        <v>-10.8654</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.16</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3876</v>
+        <v>0.3332</v>
       </c>
       <c r="J292" t="n">
-        <v>13.566</v>
+        <v>11.662</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.14</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3505</v>
+        <v>0.2976</v>
       </c>
       <c r="J293" t="n">
-        <v>12.2675</v>
+        <v>10.416</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>0.8</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2437</v>
+        <v>-0.224</v>
       </c>
       <c r="J294" t="n">
-        <v>-8.529500000000001</v>
+        <v>-7.84</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.78</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2633</v>
+        <v>-0.2439</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.2155</v>
+        <v>-8.5365</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.66</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3756</v>
+        <v>-0.3623</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.146</v>
+        <v>-12.6805</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.58</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2123</v>
+        <v>1.228</v>
       </c>
       <c r="J297" t="n">
-        <v>42.4305</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.53</v>
       </c>
       <c r="I298" t="n">
-        <v>1.1448</v>
+        <v>1.1578</v>
       </c>
       <c r="J298" t="n">
-        <v>40.068</v>
+        <v>40.523</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.13</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3855</v>
+        <v>0.3513</v>
       </c>
       <c r="J299" t="n">
-        <v>13.4925</v>
+        <v>12.2955</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.92</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3259</v>
+        <v>-0.2857</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.4065</v>
+        <v>-9.999499999999999</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.85</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.4684</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.766</v>
+        <v>-16.394</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>2.07</v>
       </c>
       <c r="I302" t="n">
-        <v>1.7486</v>
+        <v>1.8009</v>
       </c>
       <c r="J302" t="n">
-        <v>33.2234</v>
+        <v>34.2171</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.9</v>
       </c>
       <c r="I303" t="n">
-        <v>1.5511</v>
+        <v>1.5864</v>
       </c>
       <c r="J303" t="n">
-        <v>29.4709</v>
+        <v>30.1416</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.34</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7922</v>
+        <v>0.7802</v>
       </c>
       <c r="J304" t="n">
-        <v>15.0518</v>
+        <v>14.8238</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>1.22</v>
       </c>
       <c r="I305" t="n">
-        <v>0.5466</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="J305" t="n">
-        <v>10.3854</v>
+        <v>9.8743</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.98</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1815</v>
+        <v>-0.161</v>
       </c>
       <c r="J306" t="n">
-        <v>-3.4485</v>
+        <v>-3.059</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>0.91</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0475</v>
+        <v>-0.015</v>
       </c>
       <c r="J307" t="n">
-        <v>-0.9025</v>
+        <v>-0.285</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>0.52</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.4549</v>
+        <v>-0.4511</v>
       </c>
       <c r="J308" t="n">
-        <v>-8.6431</v>
+        <v>-8.5709</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.51</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4634</v>
+        <v>-0.46</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.804600000000001</v>
+        <v>-8.74</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.46</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5071</v>
+        <v>-0.5065</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.6349</v>
+        <v>-9.6235</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.34</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6139</v>
+        <v>-0.6268</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.6641</v>
+        <v>-11.9092</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.48</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.8066</v>
       </c>
       <c r="J312" t="n">
-        <v>25.692</v>
+        <v>24.198</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.524</v>
+        <v>0.4644</v>
       </c>
       <c r="J313" t="n">
-        <v>15.72</v>
+        <v>13.932</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.99</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.0277</v>
+        <v>-0.0196</v>
       </c>
       <c r="J314" t="n">
-        <v>-0.831</v>
+        <v>-0.588</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.84</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2153</v>
+        <v>-0.1947</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.459</v>
+        <v>-5.841</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.62</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4227</v>
+        <v>-0.4153</v>
       </c>
       <c r="J316" t="n">
-        <v>-12.681</v>
+        <v>-12.459</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.42</v>
       </c>
       <c r="I317" t="n">
-        <v>1.0484</v>
+        <v>1.0592</v>
       </c>
       <c r="J317" t="n">
-        <v>31.452</v>
+        <v>31.776</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>0.98</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0974</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.922</v>
+        <v>-2.262</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>0.98</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0974</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.922</v>
+        <v>-2.262</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.85</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4655</v>
+        <v>-0.4229</v>
       </c>
       <c r="J320" t="n">
-        <v>-13.965</v>
+        <v>-12.687</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="J321" t="n">
-        <v>-24.813</v>
+        <v>-24.117</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.19</v>
       </c>
       <c r="I322" t="n">
-        <v>0.439</v>
+        <v>0.383</v>
       </c>
       <c r="J322" t="n">
-        <v>11.853</v>
+        <v>10.341</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.07</v>
       </c>
       <c r="I323" t="n">
-        <v>0.2083</v>
+        <v>0.166</v>
       </c>
       <c r="J323" t="n">
-        <v>5.6241</v>
+        <v>4.482</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>0.99</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.019</v>
+        <v>-0.014</v>
       </c>
       <c r="J324" t="n">
-        <v>-0.513</v>
+        <v>-0.378</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.77</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2738</v>
+        <v>-0.2547</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.3926</v>
+        <v>-6.8769</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4649</v>
+        <v>-0.4609</v>
       </c>
       <c r="J326" t="n">
-        <v>-12.5523</v>
+        <v>-12.4443</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.47</v>
       </c>
       <c r="I327" t="n">
-        <v>1.0606</v>
+        <v>1.0677</v>
       </c>
       <c r="J327" t="n">
-        <v>28.6362</v>
+        <v>28.8279</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.4</v>
       </c>
       <c r="I328" t="n">
-        <v>0.947</v>
+        <v>0.9356</v>
       </c>
       <c r="J328" t="n">
-        <v>25.569</v>
+        <v>25.2612</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>1.26</v>
       </c>
       <c r="I329" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6393</v>
       </c>
       <c r="J329" t="n">
-        <v>18.0873</v>
+        <v>17.2611</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>1.13</v>
       </c>
       <c r="I330" t="n">
-        <v>0.3846</v>
+        <v>0.3506</v>
       </c>
       <c r="J330" t="n">
-        <v>10.3842</v>
+        <v>9.466200000000001</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.78</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6721</v>
+        <v>-0.6415</v>
       </c>
       <c r="J331" t="n">
-        <v>-18.1467</v>
+        <v>-17.3205</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.23</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6455</v>
+        <v>0.6088</v>
       </c>
       <c r="J332" t="n">
-        <v>23.238</v>
+        <v>21.9168</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.14</v>
       </c>
       <c r="I333" t="n">
-        <v>0.436</v>
+        <v>0.3937</v>
       </c>
       <c r="J333" t="n">
-        <v>15.696</v>
+        <v>14.1732</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>1.1</v>
       </c>
       <c r="I334" t="n">
-        <v>0.3348</v>
+        <v>0.294</v>
       </c>
       <c r="J334" t="n">
-        <v>12.0528</v>
+        <v>10.584</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>1.02</v>
       </c>
       <c r="I335" t="n">
-        <v>0.0959</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J335" t="n">
-        <v>3.4524</v>
+        <v>2.6928</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.67</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.879</v>
+        <v>-0.862</v>
       </c>
       <c r="J336" t="n">
-        <v>-31.644</v>
+        <v>-31.032</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.5</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8672</v>
+        <v>0.8159</v>
       </c>
       <c r="J337" t="n">
-        <v>31.2192</v>
+        <v>29.3724</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.1</v>
       </c>
       <c r="I338" t="n">
-        <v>0.2396</v>
+        <v>0.1972</v>
       </c>
       <c r="J338" t="n">
-        <v>8.6256</v>
+        <v>7.0992</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.01</v>
       </c>
       <c r="I339" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
       <c r="J339" t="n">
-        <v>1.188</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.01</v>
       </c>
       <c r="I340" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
       <c r="J340" t="n">
-        <v>1.188</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.86</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.1992</v>
+        <v>-0.1787</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.1712</v>
+        <v>-6.4332</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.65</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2958</v>
+        <v>1.3153</v>
       </c>
       <c r="J342" t="n">
-        <v>31.0992</v>
+        <v>31.5672</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.23</v>
       </c>
       <c r="I343" t="n">
-        <v>0.6047</v>
+        <v>0.5738</v>
       </c>
       <c r="J343" t="n">
-        <v>14.5128</v>
+        <v>13.7712</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.23</v>
       </c>
       <c r="I344" t="n">
-        <v>0.6047</v>
+        <v>0.5738</v>
       </c>
       <c r="J344" t="n">
-        <v>14.5128</v>
+        <v>13.7712</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>1.22</v>
       </c>
       <c r="I345" t="n">
-        <v>0.5838</v>
+        <v>0.5525</v>
       </c>
       <c r="J345" t="n">
-        <v>14.0112</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.87</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4645</v>
+        <v>-0.4252</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.148</v>
+        <v>-10.2048</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.21</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5229</v>
+        <v>0.4765</v>
       </c>
       <c r="J347" t="n">
-        <v>12.5496</v>
+        <v>11.436</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>0.86</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1731</v>
+        <v>-0.1569</v>
       </c>
       <c r="J348" t="n">
-        <v>-4.1544</v>
+        <v>-3.7656</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2243</v>
+        <v>-0.2072</v>
       </c>
       <c r="J349" t="n">
-        <v>-5.3832</v>
+        <v>-4.9728</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.64</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3812</v>
+        <v>-0.3683</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.1488</v>
+        <v>-8.8392</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.44</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5563</v>
+        <v>-0.5634</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.3512</v>
+        <v>-13.5216</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.02</v>
       </c>
       <c r="I352" t="n">
-        <v>0.0789</v>
+        <v>0.056</v>
       </c>
       <c r="J352" t="n">
-        <v>3.3138</v>
+        <v>2.352</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>0.98</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.0406</v>
+        <v>-0.0315</v>
       </c>
       <c r="J353" t="n">
-        <v>-1.7052</v>
+        <v>-1.323</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>0.96</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.0701</v>
+        <v>-0.0569</v>
       </c>
       <c r="J354" t="n">
-        <v>-2.9442</v>
+        <v>-2.3898</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>0.93</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.1084</v>
+        <v>-0.0915</v>
       </c>
       <c r="J355" t="n">
-        <v>-4.5528</v>
+        <v>-3.843</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.91</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.1321</v>
+        <v>-0.1137</v>
       </c>
       <c r="J356" t="n">
-        <v>-5.5482</v>
+        <v>-4.7754</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.22</v>
       </c>
       <c r="I357" t="n">
-        <v>0.6126</v>
+        <v>0.5748</v>
       </c>
       <c r="J357" t="n">
-        <v>25.7292</v>
+        <v>24.1416</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.17</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4989</v>
+        <v>0.4581</v>
       </c>
       <c r="J358" t="n">
-        <v>20.9538</v>
+        <v>19.2402</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.11</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3534</v>
+        <v>0.3138</v>
       </c>
       <c r="J359" t="n">
-        <v>14.8428</v>
+        <v>13.1796</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.96</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1815</v>
+        <v>-0.1475</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.623</v>
+        <v>-6.195</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.89</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3823</v>
+        <v>-0.3393</v>
       </c>
       <c r="J361" t="n">
-        <v>-16.0566</v>
+        <v>-14.2506</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.28</v>
       </c>
       <c r="I362" t="n">
-        <v>0.7149</v>
+        <v>0.6852</v>
       </c>
       <c r="J362" t="n">
-        <v>21.447</v>
+        <v>20.556</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.28</v>
       </c>
       <c r="I363" t="n">
-        <v>0.7149</v>
+        <v>0.6852</v>
       </c>
       <c r="J363" t="n">
-        <v>21.447</v>
+        <v>20.556</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>1.21</v>
       </c>
       <c r="I364" t="n">
-        <v>0.5679</v>
+        <v>0.5334</v>
       </c>
       <c r="J364" t="n">
-        <v>17.037</v>
+        <v>16.002</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>1.17</v>
       </c>
       <c r="I365" t="n">
-        <v>0.4813</v>
+        <v>0.4459</v>
       </c>
       <c r="J365" t="n">
-        <v>14.439</v>
+        <v>13.377</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.99</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J366" t="n">
-        <v>-2.727</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.12</v>
       </c>
       <c r="I367" t="n">
-        <v>0.3205</v>
+        <v>0.2701</v>
       </c>
       <c r="J367" t="n">
-        <v>9.615</v>
+        <v>8.103</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1</v>
       </c>
       <c r="I368" t="n">
-        <v>0.0193</v>
+        <v>0.0142</v>
       </c>
       <c r="J368" t="n">
-        <v>0.579</v>
+        <v>0.426</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>0.98</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.0328</v>
+        <v>-0.0253</v>
       </c>
       <c r="J369" t="n">
-        <v>-0.984</v>
+        <v>-0.759</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.75</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2893</v>
+        <v>-0.271</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.679</v>
+        <v>-8.130000000000001</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.55</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4702</v>
+        <v>-0.4665</v>
       </c>
       <c r="J371" t="n">
-        <v>-14.106</v>
+        <v>-13.995</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.65</v>
       </c>
       <c r="I372" t="n">
-        <v>1.3107</v>
+        <v>1.3323</v>
       </c>
       <c r="J372" t="n">
-        <v>38.0103</v>
+        <v>38.6367</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.17</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4817</v>
+        <v>0.4461</v>
       </c>
       <c r="J373" t="n">
-        <v>13.9693</v>
+        <v>12.9369</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.13</v>
       </c>
       <c r="I374" t="n">
-        <v>0.3885</v>
+        <v>0.3535</v>
       </c>
       <c r="J374" t="n">
-        <v>11.2665</v>
+        <v>10.2515</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>1.02</v>
       </c>
       <c r="I375" t="n">
-        <v>0.0708</v>
+        <v>0.0545</v>
       </c>
       <c r="J375" t="n">
-        <v>2.0532</v>
+        <v>1.5805</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.2646</v>
+        <v>-0.2261</v>
       </c>
       <c r="J376" t="n">
-        <v>-7.6734</v>
+        <v>-6.5569</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.15</v>
       </c>
       <c r="I377" t="n">
-        <v>0.368</v>
+        <v>0.3142</v>
       </c>
       <c r="J377" t="n">
-        <v>10.672</v>
+        <v>9.111800000000001</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>0.96</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.0667</v>
+        <v>-0.0548</v>
       </c>
       <c r="J378" t="n">
-        <v>-1.9343</v>
+        <v>-1.5892</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>0.95</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.0803</v>
+        <v>-0.067</v>
       </c>
       <c r="J379" t="n">
-        <v>-2.3287</v>
+        <v>-1.943</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.83</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2141</v>
+        <v>-0.1941</v>
       </c>
       <c r="J380" t="n">
-        <v>-6.2089</v>
+        <v>-5.6289</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.67</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3669</v>
+        <v>-0.353</v>
       </c>
       <c r="J381" t="n">
-        <v>-10.6401</v>
+        <v>-10.237</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.56</v>
       </c>
       <c r="I382" t="n">
-        <v>1.1953</v>
+        <v>1.2108</v>
       </c>
       <c r="J382" t="n">
-        <v>35.859</v>
+        <v>36.324</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.25</v>
       </c>
       <c r="I383" t="n">
-        <v>0.657</v>
+        <v>0.6237</v>
       </c>
       <c r="J383" t="n">
-        <v>19.71</v>
+        <v>18.711</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.21</v>
       </c>
       <c r="I384" t="n">
-        <v>0.5714</v>
+        <v>0.5356</v>
       </c>
       <c r="J384" t="n">
-        <v>17.142</v>
+        <v>16.068</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.0268</v>
+        <v>-0.0213</v>
       </c>
       <c r="J385" t="n">
-        <v>-0.804</v>
+        <v>-0.639</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.79</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.6417</v>
+        <v>-0.6079</v>
       </c>
       <c r="J386" t="n">
-        <v>-19.251</v>
+        <v>-18.237</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.18</v>
       </c>
       <c r="I387" t="n">
-        <v>0.4288</v>
+        <v>0.374</v>
       </c>
       <c r="J387" t="n">
-        <v>12.864</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1.09</v>
       </c>
       <c r="I388" t="n">
-        <v>0.2568</v>
+        <v>0.2103</v>
       </c>
       <c r="J388" t="n">
-        <v>7.704</v>
+        <v>6.309</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.85</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.1918</v>
+        <v>-0.1725</v>
       </c>
       <c r="J389" t="n">
-        <v>-5.754</v>
+        <v>-5.175</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3466</v>
+        <v>-0.3312</v>
       </c>
       <c r="J390" t="n">
-        <v>-10.398</v>
+        <v>-9.936</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.65</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.383</v>
+        <v>-0.3703</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.49</v>
+        <v>-11.109</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>2.04</v>
       </c>
       <c r="I392" t="n">
-        <v>1.7253</v>
+        <v>1.7761</v>
       </c>
       <c r="J392" t="n">
-        <v>32.7807</v>
+        <v>33.7459</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.91</v>
       </c>
       <c r="I393" t="n">
-        <v>1.5727</v>
+        <v>1.6096</v>
       </c>
       <c r="J393" t="n">
-        <v>29.8813</v>
+        <v>30.5824</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.21</v>
       </c>
       <c r="I394" t="n">
-        <v>0.5323</v>
+        <v>0.5046</v>
       </c>
       <c r="J394" t="n">
-        <v>10.1137</v>
+        <v>9.587400000000001</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>1.07</v>
       </c>
       <c r="I395" t="n">
-        <v>0.189</v>
+        <v>0.1577</v>
       </c>
       <c r="J395" t="n">
-        <v>3.591</v>
+        <v>2.9963</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>1.02</v>
       </c>
       <c r="I396" t="n">
-        <v>0.0279</v>
+        <v>0.008</v>
       </c>
       <c r="J396" t="n">
-        <v>0.5301</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>0.95</v>
       </c>
       <c r="I397" t="n">
-        <v>-0.0516</v>
+        <v>-0.0381</v>
       </c>
       <c r="J397" t="n">
-        <v>-0.9804</v>
+        <v>-0.7239</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>0.86</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.1629</v>
+        <v>-0.1473</v>
       </c>
       <c r="J398" t="n">
-        <v>-3.0951</v>
+        <v>-2.7987</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>0.8</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.2265</v>
+        <v>-0.2112</v>
       </c>
       <c r="J399" t="n">
-        <v>-4.3035</v>
+        <v>-4.0128</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.57</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.4357</v>
+        <v>-0.4273</v>
       </c>
       <c r="J400" t="n">
-        <v>-8.2783</v>
+        <v>-8.1187</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.45</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.5407</v>
+        <v>-0.5446</v>
       </c>
       <c r="J401" t="n">
-        <v>-10.2733</v>
+        <v>-10.3474</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.45</v>
       </c>
       <c r="I402" t="n">
-        <v>1.0184</v>
+        <v>1.0199</v>
       </c>
       <c r="J402" t="n">
-        <v>25.46</v>
+        <v>25.4975</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.34</v>
       </c>
       <c r="I403" t="n">
-        <v>0.8196</v>
+        <v>0.7996</v>
       </c>
       <c r="J403" t="n">
-        <v>20.49</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.25</v>
       </c>
       <c r="I404" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="J404" t="n">
-        <v>16.065</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>1.2</v>
       </c>
       <c r="I405" t="n">
-        <v>0.5366</v>
+        <v>0.5057</v>
       </c>
       <c r="J405" t="n">
-        <v>13.415</v>
+        <v>12.6425</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>1.12</v>
       </c>
       <c r="I406" t="n">
-        <v>0.3497</v>
+        <v>0.3174</v>
       </c>
       <c r="J406" t="n">
-        <v>8.7425</v>
+        <v>7.935</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>0.97</v>
       </c>
       <c r="I407" t="n">
-        <v>-0.04</v>
+        <v>-0.0308</v>
       </c>
       <c r="J407" t="n">
-        <v>-1</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>0.86</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.176</v>
+        <v>-0.1592</v>
       </c>
       <c r="J408" t="n">
-        <v>-4.4</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>0.79</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.245</v>
+        <v>-0.2269</v>
       </c>
       <c r="J409" t="n">
-        <v>-6.125</v>
+        <v>-5.6725</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.77</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2641</v>
+        <v>-0.246</v>
       </c>
       <c r="J410" t="n">
-        <v>-6.6025</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.7</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3295</v>
+        <v>-0.3133</v>
       </c>
       <c r="J411" t="n">
-        <v>-8.237500000000001</v>
+        <v>-7.8325</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.4</v>
       </c>
       <c r="I412" t="n">
-        <v>0.9791</v>
+        <v>0.9727</v>
       </c>
       <c r="J412" t="n">
-        <v>28.3939</v>
+        <v>28.2083</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.16</v>
       </c>
       <c r="I413" t="n">
-        <v>0.4718</v>
+        <v>0.4314</v>
       </c>
       <c r="J413" t="n">
-        <v>13.6822</v>
+        <v>12.5106</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.98</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.1146</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="J414" t="n">
-        <v>-3.3234</v>
+        <v>-2.552</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.95</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.2167</v>
+        <v>-0.1799</v>
       </c>
       <c r="J415" t="n">
-        <v>-6.2843</v>
+        <v>-5.2171</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.95</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.2167</v>
+        <v>-0.1799</v>
       </c>
       <c r="J416" t="n">
-        <v>-6.2843</v>
+        <v>-5.2171</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.35</v>
       </c>
       <c r="I417" t="n">
-        <v>0.6741</v>
+        <v>0.6168</v>
       </c>
       <c r="J417" t="n">
-        <v>19.5489</v>
+        <v>17.8872</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.14</v>
       </c>
       <c r="I418" t="n">
-        <v>0.3272</v>
+        <v>0.2748</v>
       </c>
       <c r="J418" t="n">
-        <v>9.488799999999999</v>
+        <v>7.9692</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>1.1</v>
       </c>
       <c r="I419" t="n">
-        <v>0.2518</v>
+        <v>0.2054</v>
       </c>
       <c r="J419" t="n">
-        <v>7.3022</v>
+        <v>5.9566</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.89</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.1586</v>
+        <v>-0.1385</v>
       </c>
       <c r="J420" t="n">
-        <v>-4.5994</v>
+        <v>-4.0165</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.54</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.4893</v>
+        <v>-0.4896</v>
       </c>
       <c r="J421" t="n">
-        <v>-14.1897</v>
+        <v>-14.1984</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.22</v>
       </c>
       <c r="I422" t="n">
-        <v>0.4601</v>
+        <v>0.4017</v>
       </c>
       <c r="J422" t="n">
-        <v>12.4227</v>
+        <v>10.8459</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.21</v>
       </c>
       <c r="I423" t="n">
-        <v>0.4434</v>
+        <v>0.3856</v>
       </c>
       <c r="J423" t="n">
-        <v>11.9718</v>
+        <v>10.4112</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.07</v>
       </c>
       <c r="I424" t="n">
-        <v>0.187</v>
+        <v>0.1485</v>
       </c>
       <c r="J424" t="n">
-        <v>5.049</v>
+        <v>4.0095</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>0.95</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.0886</v>
+        <v>-0.0723</v>
       </c>
       <c r="J425" t="n">
-        <v>-2.3922</v>
+        <v>-1.9521</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.71</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.3412</v>
+        <v>-0.3262</v>
       </c>
       <c r="J426" t="n">
-        <v>-9.212400000000001</v>
+        <v>-8.807399999999999</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.26</v>
       </c>
       <c r="I427" t="n">
-        <v>0.6915</v>
+        <v>0.658</v>
       </c>
       <c r="J427" t="n">
-        <v>18.6705</v>
+        <v>17.766</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.24</v>
       </c>
       <c r="I428" t="n">
-        <v>0.6485</v>
+        <v>0.6129</v>
       </c>
       <c r="J428" t="n">
-        <v>17.5095</v>
+        <v>16.5483</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>1.19</v>
       </c>
       <c r="I429" t="n">
-        <v>0.538</v>
+        <v>0.4989</v>
       </c>
       <c r="J429" t="n">
-        <v>14.526</v>
+        <v>13.4703</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>1.1</v>
       </c>
       <c r="I430" t="n">
-        <v>0.3242</v>
+        <v>0.2872</v>
       </c>
       <c r="J430" t="n">
-        <v>8.753399999999999</v>
+        <v>7.7544</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.72</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.7615</v>
       </c>
       <c r="J431" t="n">
-        <v>-21.2166</v>
+        <v>-20.5605</v>
       </c>
     </row>
     <row r="432">
@@ -20549,10 +20549,10 @@
         <v>1.81</v>
       </c>
       <c r="I432" t="n">
-        <v>1.4785</v>
+        <v>1.5091</v>
       </c>
       <c r="J432" t="n">
-        <v>32.527</v>
+        <v>33.2002</v>
       </c>
     </row>
     <row r="433">
@@ -20589,10 +20589,10 @@
         <v>1.42</v>
       </c>
       <c r="I433" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9545</v>
       </c>
       <c r="J433" t="n">
-        <v>21.1244</v>
+        <v>20.999</v>
       </c>
     </row>
     <row r="434">
@@ -20629,10 +20629,10 @@
         <v>1.25</v>
       </c>
       <c r="I434" t="n">
-        <v>0.6357</v>
+        <v>0.6098</v>
       </c>
       <c r="J434" t="n">
-        <v>13.9854</v>
+        <v>13.4156</v>
       </c>
     </row>
     <row r="435">
@@ -20669,10 +20669,10 @@
         <v>1.11</v>
       </c>
       <c r="I435" t="n">
-        <v>0.3157</v>
+        <v>0.2839</v>
       </c>
       <c r="J435" t="n">
-        <v>6.9454</v>
+        <v>6.2458</v>
       </c>
     </row>
     <row r="436">
@@ -20709,10 +20709,10 @@
         <v>1.04</v>
       </c>
       <c r="I436" t="n">
-        <v>0.1168</v>
+        <v>0.0926</v>
       </c>
       <c r="J436" t="n">
-        <v>2.5696</v>
+        <v>2.0372</v>
       </c>
     </row>
     <row r="437">
@@ -20749,10 +20749,10 @@
         <v>0.87</v>
       </c>
       <c r="I437" t="n">
-        <v>-0.1448</v>
+        <v>-0.1286</v>
       </c>
       <c r="J437" t="n">
-        <v>-3.1856</v>
+        <v>-2.8292</v>
       </c>
     </row>
     <row r="438">
@@ -20789,10 +20789,10 @@
         <v>0.77</v>
       </c>
       <c r="I438" t="n">
-        <v>-0.2513</v>
+        <v>-0.237</v>
       </c>
       <c r="J438" t="n">
-        <v>-5.5286</v>
+        <v>-5.214</v>
       </c>
     </row>
     <row r="439">
@@ -20829,10 +20829,10 @@
         <v>0.72</v>
       </c>
       <c r="I439" t="n">
-        <v>-0.2991</v>
+        <v>-0.2855</v>
       </c>
       <c r="J439" t="n">
-        <v>-6.5802</v>
+        <v>-6.281</v>
       </c>
     </row>
     <row r="440">
@@ -20869,10 +20869,10 @@
         <v>0.64</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.3693</v>
+        <v>-0.3571</v>
       </c>
       <c r="J440" t="n">
-        <v>-8.124599999999999</v>
+        <v>-7.8562</v>
       </c>
     </row>
     <row r="441">
@@ -20909,10 +20909,10 @@
         <v>0.46</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.528</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="J441" t="n">
-        <v>-11.616</v>
+        <v>-11.6534</v>
       </c>
     </row>
     <row r="442">
@@ -20949,10 +20949,10 @@
         <v>1.3</v>
       </c>
       <c r="I442" t="n">
-        <v>0.6008</v>
+        <v>0.5423</v>
       </c>
       <c r="J442" t="n">
-        <v>17.4232</v>
+        <v>15.7267</v>
       </c>
     </row>
     <row r="443">
@@ -20989,10 +20989,10 @@
         <v>1.08</v>
       </c>
       <c r="I443" t="n">
-        <v>0.2145</v>
+        <v>0.1717</v>
       </c>
       <c r="J443" t="n">
-        <v>6.2205</v>
+        <v>4.9793</v>
       </c>
     </row>
     <row r="444">
@@ -21029,10 +21029,10 @@
         <v>0.98</v>
       </c>
       <c r="I444" t="n">
-        <v>-0.042</v>
+        <v>-0.0321</v>
       </c>
       <c r="J444" t="n">
-        <v>-1.218</v>
+        <v>-0.9308999999999999</v>
       </c>
     </row>
     <row r="445">
@@ -21069,10 +21069,10 @@
         <v>0.93</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.1105</v>
+        <v>-0.093</v>
       </c>
       <c r="J445" t="n">
-        <v>-3.2045</v>
+        <v>-2.697</v>
       </c>
     </row>
     <row r="446">
@@ -21109,10 +21109,10 @@
         <v>0.65</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.392</v>
+        <v>-0.3809</v>
       </c>
       <c r="J446" t="n">
-        <v>-11.368</v>
+        <v>-11.0461</v>
       </c>
     </row>
     <row r="447">
@@ -21149,10 +21149,10 @@
         <v>1.5</v>
       </c>
       <c r="I447" t="n">
-        <v>1.1257</v>
+        <v>1.1392</v>
       </c>
       <c r="J447" t="n">
-        <v>32.6453</v>
+        <v>33.0368</v>
       </c>
     </row>
     <row r="448">
@@ -21189,10 +21189,10 @@
         <v>1.14</v>
       </c>
       <c r="I448" t="n">
-        <v>0.4204</v>
+        <v>0.3815</v>
       </c>
       <c r="J448" t="n">
-        <v>12.1916</v>
+        <v>11.0635</v>
       </c>
     </row>
     <row r="449">
@@ -21229,10 +21229,10 @@
         <v>1.08</v>
       </c>
       <c r="I449" t="n">
-        <v>0.2706</v>
+        <v>0.2366</v>
       </c>
       <c r="J449" t="n">
-        <v>7.8474</v>
+        <v>6.8614</v>
       </c>
     </row>
     <row r="450">
@@ -21269,10 +21269,10 @@
         <v>0.96</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.1893</v>
+        <v>-0.1548</v>
       </c>
       <c r="J450" t="n">
-        <v>-5.4897</v>
+        <v>-4.4892</v>
       </c>
     </row>
     <row r="451">
@@ -21309,10 +21309,10 @@
         <v>0.88</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.4163</v>
+        <v>-0.3736</v>
       </c>
       <c r="J451" t="n">
-        <v>-12.0727</v>
+        <v>-10.8344</v>
       </c>
     </row>
     <row r="452">
@@ -21349,10 +21349,10 @@
         <v>1.34</v>
       </c>
       <c r="I452" t="n">
-        <v>0.668</v>
+        <v>0.6116</v>
       </c>
       <c r="J452" t="n">
-        <v>20.04</v>
+        <v>18.348</v>
       </c>
     </row>
     <row r="453">
@@ -21389,10 +21389,10 @@
         <v>1.08</v>
       </c>
       <c r="I453" t="n">
-        <v>0.2171</v>
+        <v>0.1738</v>
       </c>
       <c r="J453" t="n">
-        <v>6.513</v>
+        <v>5.214</v>
       </c>
     </row>
     <row r="454">
@@ -21429,10 +21429,10 @@
         <v>1.04</v>
       </c>
       <c r="I454" t="n">
-        <v>0.1285</v>
+        <v>0.0969</v>
       </c>
       <c r="J454" t="n">
-        <v>3.855</v>
+        <v>2.907</v>
       </c>
     </row>
     <row r="455">
@@ -21469,10 +21469,10 @@
         <v>0.72</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.3268</v>
+        <v>-0.3104</v>
       </c>
       <c r="J455" t="n">
-        <v>-9.804</v>
+        <v>-9.311999999999999</v>
       </c>
     </row>
     <row r="456">
@@ -21509,10 +21509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.3545</v>
+        <v>-0.34</v>
       </c>
       <c r="J456" t="n">
-        <v>-10.635</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="457">
@@ -21549,10 +21549,10 @@
         <v>1.34</v>
       </c>
       <c r="I457" t="n">
-        <v>0.8655</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="J457" t="n">
-        <v>25.965</v>
+        <v>25.329</v>
       </c>
     </row>
     <row r="458">
@@ -21589,10 +21589,10 @@
         <v>1.19</v>
       </c>
       <c r="I458" t="n">
-        <v>0.5432</v>
+        <v>0.5034</v>
       </c>
       <c r="J458" t="n">
-        <v>16.296</v>
+        <v>15.102</v>
       </c>
     </row>
     <row r="459">
@@ -21629,10 +21629,10 @@
         <v>0.98</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.1127</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J459" t="n">
-        <v>-3.381</v>
+        <v>-2.595</v>
       </c>
     </row>
     <row r="460">
@@ -21669,10 +21669,10 @@
         <v>0.96</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.183</v>
+        <v>-0.1488</v>
       </c>
       <c r="J460" t="n">
-        <v>-5.49</v>
+        <v>-4.464</v>
       </c>
     </row>
     <row r="461">
@@ -21709,10 +21709,10 @@
         <v>0.92</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.3029</v>
+        <v>-0.2616</v>
       </c>
       <c r="J461" t="n">
-        <v>-9.087</v>
+        <v>-7.848</v>
       </c>
     </row>
     <row r="462">
@@ -21749,10 +21749,10 @@
         <v>1.67</v>
       </c>
       <c r="I462" t="n">
-        <v>1.2974</v>
+        <v>1.3167</v>
       </c>
       <c r="J462" t="n">
-        <v>25.948</v>
+        <v>26.334</v>
       </c>
     </row>
     <row r="463">
@@ -21789,10 +21789,10 @@
         <v>1.42</v>
       </c>
       <c r="I463" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9513</v>
       </c>
       <c r="J463" t="n">
-        <v>19.122</v>
+        <v>19.026</v>
       </c>
     </row>
     <row r="464">
@@ -21829,10 +21829,10 @@
         <v>1.31</v>
       </c>
       <c r="I464" t="n">
-        <v>0.753</v>
+        <v>0.7335</v>
       </c>
       <c r="J464" t="n">
-        <v>15.06</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="465">
@@ -21869,10 +21869,10 @@
         <v>1.25</v>
       </c>
       <c r="I465" t="n">
-        <v>0.6318</v>
+        <v>0.6067</v>
       </c>
       <c r="J465" t="n">
-        <v>12.636</v>
+        <v>12.134</v>
       </c>
     </row>
     <row r="466">
@@ -21909,10 +21909,10 @@
         <v>1.12</v>
       </c>
       <c r="I466" t="n">
-        <v>0.3367</v>
+        <v>0.3046</v>
       </c>
       <c r="J466" t="n">
-        <v>6.734</v>
+        <v>6.092</v>
       </c>
     </row>
     <row r="467">
@@ -21949,10 +21949,10 @@
         <v>1.16</v>
       </c>
       <c r="I467" t="n">
-        <v>0.4496</v>
+        <v>0.4073</v>
       </c>
       <c r="J467" t="n">
-        <v>8.992000000000001</v>
+        <v>8.146000000000001</v>
       </c>
     </row>
     <row r="468">
@@ -21989,10 +21989,10 @@
         <v>0.97</v>
       </c>
       <c r="I468" t="n">
-        <v>-0.0276</v>
+        <v>-0.0172</v>
       </c>
       <c r="J468" t="n">
-        <v>-0.552</v>
+        <v>-0.344</v>
       </c>
     </row>
     <row r="469">
@@ -22029,10 +22029,10 @@
         <v>0.72</v>
       </c>
       <c r="I469" t="n">
-        <v>-0.3041</v>
+        <v>-0.2884</v>
       </c>
       <c r="J469" t="n">
-        <v>-6.082</v>
+        <v>-5.768</v>
       </c>
     </row>
     <row r="470">
@@ -22069,10 +22069,10 @@
         <v>0.58</v>
       </c>
       <c r="I470" t="n">
-        <v>-0.4301</v>
+        <v>-0.4211</v>
       </c>
       <c r="J470" t="n">
-        <v>-8.602</v>
+        <v>-8.422000000000001</v>
       </c>
     </row>
     <row r="471">
@@ -22109,10 +22109,10 @@
         <v>0.33</v>
       </c>
       <c r="I471" t="n">
-        <v>-0.6461</v>
+        <v>-0.668</v>
       </c>
       <c r="J471" t="n">
-        <v>-12.922</v>
+        <v>-13.36</v>
       </c>
     </row>
     <row r="472">
@@ -22149,10 +22149,10 @@
         <v>1.39</v>
       </c>
       <c r="I472" t="n">
-        <v>0.9536</v>
+        <v>0.9424</v>
       </c>
       <c r="J472" t="n">
-        <v>27.6544</v>
+        <v>27.3296</v>
       </c>
     </row>
     <row r="473">
@@ -22189,10 +22189,10 @@
         <v>1.36</v>
       </c>
       <c r="I473" t="n">
-        <v>0.8955</v>
+        <v>0.8769</v>
       </c>
       <c r="J473" t="n">
-        <v>25.9695</v>
+        <v>25.4301</v>
       </c>
     </row>
     <row r="474">
@@ -22229,10 +22229,10 @@
         <v>1.16</v>
       </c>
       <c r="I474" t="n">
-        <v>0.4674</v>
+        <v>0.4281</v>
       </c>
       <c r="J474" t="n">
-        <v>13.5546</v>
+        <v>12.4149</v>
       </c>
     </row>
     <row r="475">
@@ -22269,10 +22269,10 @@
         <v>0.91</v>
       </c>
       <c r="I475" t="n">
-        <v>-0.3371</v>
+        <v>-0.295</v>
       </c>
       <c r="J475" t="n">
-        <v>-9.7759</v>
+        <v>-8.555</v>
       </c>
     </row>
     <row r="476">
@@ -22309,10 +22309,10 @@
         <v>0.74</v>
       </c>
       <c r="I476" t="n">
-        <v>-0.7442</v>
+        <v>-0.7166</v>
       </c>
       <c r="J476" t="n">
-        <v>-21.5818</v>
+        <v>-20.7814</v>
       </c>
     </row>
     <row r="477">
@@ -22349,10 +22349,10 @@
         <v>1.2</v>
       </c>
       <c r="I477" t="n">
-        <v>0.4351</v>
+        <v>0.3776</v>
       </c>
       <c r="J477" t="n">
-        <v>12.6179</v>
+        <v>10.9504</v>
       </c>
     </row>
     <row r="478">
@@ -22389,10 +22389,10 @@
         <v>1.12</v>
       </c>
       <c r="I478" t="n">
-        <v>0.2921</v>
+        <v>0.2421</v>
       </c>
       <c r="J478" t="n">
-        <v>8.4709</v>
+        <v>7.0209</v>
       </c>
     </row>
     <row r="479">
@@ -22429,10 +22429,10 @@
         <v>0.99</v>
       </c>
       <c r="I479" t="n">
-        <v>-0.0249</v>
+        <v>-0.018</v>
       </c>
       <c r="J479" t="n">
-        <v>-0.7221</v>
+        <v>-0.522</v>
       </c>
     </row>
     <row r="480">
@@ -22469,10 +22469,10 @@
         <v>0.91</v>
       </c>
       <c r="I480" t="n">
-        <v>-0.1349</v>
+        <v>-0.1159</v>
       </c>
       <c r="J480" t="n">
-        <v>-3.9121</v>
+        <v>-3.3611</v>
       </c>
     </row>
     <row r="481">
@@ -22509,10 +22509,10 @@
         <v>0.75</v>
       </c>
       <c r="I481" t="n">
-        <v>-0.3004</v>
+        <v>-0.2825</v>
       </c>
       <c r="J481" t="n">
-        <v>-8.711600000000001</v>
+        <v>-8.192500000000001</v>
       </c>
     </row>
     <row r="482">
@@ -22549,10 +22549,10 @@
         <v>1.29</v>
       </c>
       <c r="I482" t="n">
-        <v>0.5838</v>
+        <v>0.5249</v>
       </c>
       <c r="J482" t="n">
-        <v>16.3464</v>
+        <v>14.6972</v>
       </c>
     </row>
     <row r="483">
@@ -22589,10 +22589,10 @@
         <v>1.14</v>
       </c>
       <c r="I483" t="n">
-        <v>0.3297</v>
+        <v>0.277</v>
       </c>
       <c r="J483" t="n">
-        <v>9.2316</v>
+        <v>7.756</v>
       </c>
     </row>
     <row r="484">
@@ -22629,10 +22629,10 @@
         <v>0.91</v>
       </c>
       <c r="I484" t="n">
-        <v>-0.1347</v>
+        <v>-0.1157</v>
       </c>
       <c r="J484" t="n">
-        <v>-3.7716</v>
+        <v>-3.2396</v>
       </c>
     </row>
     <row r="485">
@@ -22669,10 +22669,10 @@
         <v>0.83</v>
       </c>
       <c r="I485" t="n">
-        <v>-0.2215</v>
+        <v>-0.201</v>
       </c>
       <c r="J485" t="n">
-        <v>-6.202</v>
+        <v>-5.628</v>
       </c>
     </row>
     <row r="486">
@@ -22709,10 +22709,10 @@
         <v>0.79</v>
       </c>
       <c r="I486" t="n">
-        <v>-0.2616</v>
+        <v>-0.2419</v>
       </c>
       <c r="J486" t="n">
-        <v>-7.3248</v>
+        <v>-6.7732</v>
       </c>
     </row>
     <row r="487">
@@ -22749,10 +22749,10 @@
         <v>1.52</v>
       </c>
       <c r="I487" t="n">
-        <v>1.1694</v>
+        <v>1.1867</v>
       </c>
       <c r="J487" t="n">
-        <v>32.7432</v>
+        <v>33.2276</v>
       </c>
     </row>
     <row r="488">
@@ -22789,10 +22789,10 @@
         <v>1.14</v>
       </c>
       <c r="I488" t="n">
-        <v>0.4297</v>
+        <v>0.3883</v>
       </c>
       <c r="J488" t="n">
-        <v>12.0316</v>
+        <v>10.8724</v>
       </c>
     </row>
     <row r="489">
@@ -22829,10 +22829,10 @@
         <v>0.9</v>
       </c>
       <c r="I489" t="n">
-        <v>-0.3539</v>
+        <v>-0.3113</v>
       </c>
       <c r="J489" t="n">
-        <v>-9.9092</v>
+        <v>-8.7164</v>
       </c>
     </row>
     <row r="490">
@@ -22869,10 +22869,10 @@
         <v>0.87</v>
       </c>
       <c r="I490" t="n">
-        <v>-0.4315</v>
+        <v>-0.3885</v>
       </c>
       <c r="J490" t="n">
-        <v>-12.082</v>
+        <v>-10.878</v>
       </c>
     </row>
     <row r="491">
@@ -22909,10 +22909,10 @@
         <v>0.87</v>
       </c>
       <c r="I491" t="n">
-        <v>-0.4315</v>
+        <v>-0.3885</v>
       </c>
       <c r="J491" t="n">
-        <v>-12.082</v>
+        <v>-10.878</v>
       </c>
     </row>
     <row r="492">
@@ -22949,10 +22949,10 @@
         <v>1.53</v>
       </c>
       <c r="I492" t="n">
-        <v>1.14</v>
+        <v>1.1528</v>
       </c>
       <c r="J492" t="n">
-        <v>30.78</v>
+        <v>31.1256</v>
       </c>
     </row>
     <row r="493">
@@ -22989,10 +22989,10 @@
         <v>1.53</v>
       </c>
       <c r="I493" t="n">
-        <v>1.14</v>
+        <v>1.1528</v>
       </c>
       <c r="J493" t="n">
-        <v>30.78</v>
+        <v>31.1256</v>
       </c>
     </row>
     <row r="494">
@@ -23029,10 +23029,10 @@
         <v>1.18</v>
       </c>
       <c r="I494" t="n">
-        <v>0.4989</v>
+        <v>0.4655</v>
       </c>
       <c r="J494" t="n">
-        <v>13.4703</v>
+        <v>12.5685</v>
       </c>
     </row>
     <row r="495">
@@ -23069,10 +23069,10 @@
         <v>1.09</v>
       </c>
       <c r="I495" t="n">
-        <v>0.2799</v>
+        <v>0.2484</v>
       </c>
       <c r="J495" t="n">
-        <v>7.5573</v>
+        <v>6.7068</v>
       </c>
     </row>
     <row r="496">
@@ -23109,10 +23109,10 @@
         <v>0.79</v>
       </c>
       <c r="I496" t="n">
-        <v>-0.6521</v>
+        <v>-0.6206</v>
       </c>
       <c r="J496" t="n">
-        <v>-17.6067</v>
+        <v>-16.7562</v>
       </c>
     </row>
     <row r="497">
@@ -23149,10 +23149,10 @@
         <v>0.95</v>
       </c>
       <c r="I497" t="n">
-        <v>-0.0668</v>
+        <v>-0.0549</v>
       </c>
       <c r="J497" t="n">
-        <v>-1.8036</v>
+        <v>-1.4823</v>
       </c>
     </row>
     <row r="498">
@@ -23189,10 +23189,10 @@
         <v>0.9</v>
       </c>
       <c r="I498" t="n">
-        <v>-0.1299</v>
+        <v>-0.1147</v>
       </c>
       <c r="J498" t="n">
-        <v>-3.5073</v>
+        <v>-3.0969</v>
       </c>
     </row>
     <row r="499">
@@ -23229,10 +23229,10 @@
         <v>0.79</v>
       </c>
       <c r="I499" t="n">
-        <v>-0.2439</v>
+        <v>-0.2262</v>
       </c>
       <c r="J499" t="n">
-        <v>-6.5853</v>
+        <v>-6.1074</v>
       </c>
     </row>
     <row r="500">
@@ -23269,10 +23269,10 @@
         <v>0.75</v>
       </c>
       <c r="I500" t="n">
-        <v>-0.2816</v>
+        <v>-0.264</v>
       </c>
       <c r="J500" t="n">
-        <v>-7.6032</v>
+        <v>-7.128</v>
       </c>
     </row>
     <row r="501">
@@ -23309,10 +23309,10 @@
         <v>0.63</v>
       </c>
       <c r="I501" t="n">
-        <v>-0.3916</v>
+        <v>-0.3794</v>
       </c>
       <c r="J501" t="n">
-        <v>-10.5732</v>
+        <v>-10.2438</v>
       </c>
     </row>
     <row r="502">
@@ -23349,10 +23349,10 @@
         <v>1.39</v>
       </c>
       <c r="I502" t="n">
-        <v>0.968</v>
+        <v>0.9601</v>
       </c>
       <c r="J502" t="n">
-        <v>28.072</v>
+        <v>27.8429</v>
       </c>
     </row>
     <row r="503">
@@ -23389,10 +23389,10 @@
         <v>1.05</v>
       </c>
       <c r="I503" t="n">
-        <v>0.1912</v>
+        <v>0.1607</v>
       </c>
       <c r="J503" t="n">
-        <v>5.5448</v>
+        <v>4.6603</v>
       </c>
     </row>
     <row r="504">
@@ -23429,10 +23429,10 @@
         <v>1.02</v>
       </c>
       <c r="I504" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0718</v>
       </c>
       <c r="J504" t="n">
-        <v>2.6361</v>
+        <v>2.0822</v>
       </c>
     </row>
     <row r="505">
@@ -23469,10 +23469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I505" t="n">
-        <v>-0.2429</v>
+        <v>-0.2044</v>
       </c>
       <c r="J505" t="n">
-        <v>-7.0441</v>
+        <v>-5.9276</v>
       </c>
     </row>
     <row r="506">
@@ -23509,10 +23509,10 @@
         <v>0.93</v>
       </c>
       <c r="I506" t="n">
-        <v>-0.2722</v>
+        <v>-0.2321</v>
       </c>
       <c r="J506" t="n">
-        <v>-7.8938</v>
+        <v>-6.7309</v>
       </c>
     </row>
     <row r="507">
@@ -23549,10 +23549,10 @@
         <v>1.07</v>
       </c>
       <c r="I507" t="n">
-        <v>0.1987</v>
+        <v>0.1574</v>
       </c>
       <c r="J507" t="n">
-        <v>5.7623</v>
+        <v>4.5646</v>
       </c>
     </row>
     <row r="508">
@@ -23589,10 +23589,10 @@
         <v>1.06</v>
       </c>
       <c r="I508" t="n">
-        <v>0.177</v>
+        <v>0.1383</v>
       </c>
       <c r="J508" t="n">
-        <v>5.133</v>
+        <v>4.0107</v>
       </c>
     </row>
     <row r="509">
@@ -23629,10 +23629,10 @@
         <v>0.89</v>
       </c>
       <c r="I509" t="n">
-        <v>-0.1548</v>
+        <v>-0.1353</v>
       </c>
       <c r="J509" t="n">
-        <v>-4.4892</v>
+        <v>-3.9237</v>
       </c>
     </row>
     <row r="510">
@@ -23669,10 +23669,10 @@
         <v>0.89</v>
       </c>
       <c r="I510" t="n">
-        <v>-0.1548</v>
+        <v>-0.1353</v>
       </c>
       <c r="J510" t="n">
-        <v>-4.4892</v>
+        <v>-3.9237</v>
       </c>
     </row>
     <row r="511">
@@ -23709,10 +23709,10 @@
         <v>0.89</v>
       </c>
       <c r="I511" t="n">
-        <v>-0.1548</v>
+        <v>-0.1353</v>
       </c>
       <c r="J511" t="n">
-        <v>-4.4892</v>
+        <v>-3.9237</v>
       </c>
     </row>
     <row r="512">
@@ -23749,10 +23749,10 @@
         <v>1.42</v>
       </c>
       <c r="I512" t="n">
-        <v>0.9948</v>
+        <v>0.9906</v>
       </c>
       <c r="J512" t="n">
-        <v>27.8544</v>
+        <v>27.7368</v>
       </c>
     </row>
     <row r="513">
@@ -23789,10 +23789,10 @@
         <v>1.19</v>
       </c>
       <c r="I513" t="n">
-        <v>0.5285</v>
+        <v>0.4918</v>
       </c>
       <c r="J513" t="n">
-        <v>14.798</v>
+        <v>13.7704</v>
       </c>
     </row>
     <row r="514">
@@ -23829,10 +23829,10 @@
         <v>1.16</v>
       </c>
       <c r="I514" t="n">
-        <v>0.4615</v>
+        <v>0.4246</v>
       </c>
       <c r="J514" t="n">
-        <v>12.922</v>
+        <v>11.8888</v>
       </c>
     </row>
     <row r="515">
@@ -23869,10 +23869,10 @@
         <v>1.13</v>
       </c>
       <c r="I515" t="n">
-        <v>0.3921</v>
+        <v>0.3559</v>
       </c>
       <c r="J515" t="n">
-        <v>10.9788</v>
+        <v>9.965199999999999</v>
       </c>
     </row>
     <row r="516">
@@ -23909,10 +23909,10 @@
         <v>0.88</v>
       </c>
       <c r="I516" t="n">
-        <v>-0.4245</v>
+        <v>-0.3826</v>
       </c>
       <c r="J516" t="n">
-        <v>-11.886</v>
+        <v>-10.7128</v>
       </c>
     </row>
     <row r="517">
@@ -23949,10 +23949,10 @@
         <v>1.32</v>
       </c>
       <c r="I517" t="n">
-        <v>0.6552</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="J517" t="n">
-        <v>18.3456</v>
+        <v>16.8364</v>
       </c>
     </row>
     <row r="518">
@@ -23989,10 +23989,10 @@
         <v>1.14</v>
       </c>
       <c r="I518" t="n">
-        <v>0.3471</v>
+        <v>0.2941</v>
       </c>
       <c r="J518" t="n">
-        <v>9.7188</v>
+        <v>8.2348</v>
       </c>
     </row>
     <row r="519">
@@ -24029,10 +24029,10 @@
         <v>0.78</v>
       </c>
       <c r="I519" t="n">
-        <v>-0.2645</v>
+        <v>-0.2451</v>
       </c>
       <c r="J519" t="n">
-        <v>-7.406</v>
+        <v>-6.8628</v>
       </c>
     </row>
     <row r="520">
@@ -24069,10 +24069,10 @@
         <v>0.7</v>
       </c>
       <c r="I520" t="n">
-        <v>-0.3402</v>
+        <v>-0.3244</v>
       </c>
       <c r="J520" t="n">
-        <v>-9.525600000000001</v>
+        <v>-9.0832</v>
       </c>
     </row>
     <row r="521">
@@ -24109,10 +24109,10 @@
         <v>0.66</v>
       </c>
       <c r="I521" t="n">
-        <v>-0.3767</v>
+        <v>-0.3637</v>
       </c>
       <c r="J521" t="n">
-        <v>-10.5476</v>
+        <v>-10.1836</v>
       </c>
     </row>
     <row r="522">
@@ -24149,10 +24149,10 @@
         <v>0.85</v>
       </c>
       <c r="I522" t="n">
-        <v>-0.1464</v>
+        <v>-0.1268</v>
       </c>
       <c r="J522" t="n">
-        <v>-2.928</v>
+        <v>-2.536</v>
       </c>
     </row>
     <row r="523">
@@ -24189,10 +24189,10 @@
         <v>0.8</v>
       </c>
       <c r="I523" t="n">
-        <v>-0.2027</v>
+        <v>-0.1861</v>
       </c>
       <c r="J523" t="n">
-        <v>-4.054</v>
+        <v>-3.722</v>
       </c>
     </row>
     <row r="524">
@@ -24229,10 +24229,10 @@
         <v>0.76</v>
       </c>
       <c r="I524" t="n">
-        <v>-0.2451</v>
+        <v>-0.2309</v>
       </c>
       <c r="J524" t="n">
-        <v>-4.902</v>
+        <v>-4.618</v>
       </c>
     </row>
     <row r="525">
@@ -24269,10 +24269,10 @@
         <v>0.51</v>
       </c>
       <c r="I525" t="n">
-        <v>-0.4728</v>
+        <v>-0.4684</v>
       </c>
       <c r="J525" t="n">
-        <v>-9.456</v>
+        <v>-9.368</v>
       </c>
     </row>
     <row r="526">
@@ -24309,10 +24309,10 @@
         <v>0.13</v>
       </c>
       <c r="I526" t="n">
-        <v>-0.8065</v>
+        <v>-0.8626</v>
       </c>
       <c r="J526" t="n">
-        <v>-16.13</v>
+        <v>-17.252</v>
       </c>
     </row>
     <row r="527">
@@ -24349,10 +24349,10 @@
         <v>1.91</v>
       </c>
       <c r="I527" t="n">
-        <v>1.5781</v>
+        <v>1.6156</v>
       </c>
       <c r="J527" t="n">
-        <v>31.562</v>
+        <v>32.312</v>
       </c>
     </row>
     <row r="528">
@@ -24389,10 +24389,10 @@
         <v>1.58</v>
       </c>
       <c r="I528" t="n">
-        <v>1.1719</v>
+        <v>1.1882</v>
       </c>
       <c r="J528" t="n">
-        <v>23.438</v>
+        <v>23.764</v>
       </c>
     </row>
     <row r="529">
@@ -24429,10 +24429,10 @@
         <v>1.42</v>
       </c>
       <c r="I529" t="n">
-        <v>0.9492</v>
+        <v>0.947</v>
       </c>
       <c r="J529" t="n">
-        <v>18.984</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="530">
@@ -24469,10 +24469,10 @@
         <v>1.11</v>
       </c>
       <c r="I530" t="n">
-        <v>0.3006</v>
+        <v>0.268</v>
       </c>
       <c r="J530" t="n">
-        <v>6.012</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="531">
@@ -24509,10 +24509,10 @@
         <v>1.1</v>
       </c>
       <c r="I531" t="n">
-        <v>0.2747</v>
+        <v>0.2422</v>
       </c>
       <c r="J531" t="n">
-        <v>5.494</v>
+        <v>4.844</v>
       </c>
     </row>
   </sheetData>
